--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -1153,81 +1153,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1242,6 +1167,129 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1261,59 +1309,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1632,13 +1632,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1868,13 +1868,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="81"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1902,10 +1902,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="82"/>
+      <c r="D11" s="57"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1917,10 +1917,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="107" t="s">
+      <c r="C12" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="107"/>
+      <c r="D12" s="85"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1932,10 +1932,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="108" t="s">
+      <c r="C13" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="108"/>
+      <c r="D13" s="86"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1945,10 +1945,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="77" t="s">
+      <c r="C14" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="77"/>
+      <c r="D14" s="60"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -1958,10 +1958,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="77" t="s">
+      <c r="C15" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="77"/>
+      <c r="D15" s="60"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -1971,10 +1971,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="77" t="s">
+      <c r="C16" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="77"/>
+      <c r="D16" s="60"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -1986,10 +1986,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="103" t="s">
+      <c r="C17" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="103"/>
+      <c r="D17" s="87"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -1999,10 +1999,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="104" t="s">
+      <c r="C18" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="104"/>
+      <c r="D18" s="88"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2014,10 +2014,10 @@
       <c r="B19" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="105" t="s">
+      <c r="C19" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="105"/>
+      <c r="D19" s="89"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2038,13 +2038,13 @@
       <c r="B21" s="25"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="79" t="s">
+      <c r="A22" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="79"/>
-      <c r="C22" s="79"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2072,10 +2072,10 @@
       <c r="B23" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="106" t="s">
+      <c r="C23" s="90" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="106"/>
+      <c r="D23" s="90"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2087,10 +2087,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="77" t="s">
+      <c r="C24" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="77"/>
+      <c r="D24" s="60"/>
       <c r="E24" s="30">
         <v>2485</v>
       </c>
@@ -2102,10 +2102,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="77" t="s">
+      <c r="C25" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="77"/>
+      <c r="D25" s="60"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2115,10 +2115,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="102" t="s">
+      <c r="C26" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="103"/>
+      <c r="D26" s="87"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2130,10 +2130,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="104" t="s">
+      <c r="C27" s="88" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="104"/>
+      <c r="D27" s="88"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2143,10 +2143,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="91" t="s">
+      <c r="C28" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="91"/>
+      <c r="D28" s="92"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2168,13 +2168,13 @@
       <c r="B30" s="25"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="79" t="s">
+      <c r="A31" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
-      <c r="D31" s="79"/>
-      <c r="E31" s="79"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="61"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2202,10 +2202,10 @@
       <c r="B32" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="76" t="s">
+      <c r="C32" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="76"/>
+      <c r="D32" s="62"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2217,10 +2217,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="77" t="s">
+      <c r="C33" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="77"/>
+      <c r="D33" s="60"/>
       <c r="E33" s="34">
         <v>2485</v>
       </c>
@@ -2230,10 +2230,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="77" t="s">
+      <c r="C34" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="77"/>
+      <c r="D34" s="60"/>
       <c r="E34" s="34">
         <v>118</v>
       </c>
@@ -2243,10 +2243,10 @@
       <c r="B35" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="99" t="s">
+      <c r="C35" s="93" t="s">
         <v>125</v>
       </c>
-      <c r="D35" s="100"/>
+      <c r="D35" s="94"/>
       <c r="E35" s="34">
         <v>170</v>
       </c>
@@ -2256,10 +2256,10 @@
       <c r="B36" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="99" t="s">
+      <c r="C36" s="93" t="s">
         <v>121</v>
       </c>
-      <c r="D36" s="101"/>
+      <c r="D36" s="95"/>
       <c r="E36" s="34">
         <v>800</v>
       </c>
@@ -2269,10 +2269,10 @@
       <c r="B37" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="102" t="s">
+      <c r="C37" s="91" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="77"/>
+      <c r="D37" s="60"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2294,11 +2294,11 @@
       <c r="B39" s="25"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="78" t="s">
+      <c r="A40" s="63" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="78"/>
-      <c r="C40" s="78"/>
+      <c r="B40" s="63"/>
+      <c r="C40" s="63"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2313,11 +2313,11 @@
       <c r="D41" s="38"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="75" t="s">
+      <c r="A42" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="75"/>
-      <c r="C42" s="75"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="51" t="s">
@@ -2363,16 +2363,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="74" t="s">
+      <c r="A47" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="74"/>
-      <c r="C47" s="74"/>
+      <c r="B47" s="65"/>
+      <c r="C47" s="65"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="74"/>
-      <c r="B48" s="74"/>
-      <c r="C48" s="74"/>
+      <c r="A48" s="65"/>
+      <c r="B48" s="65"/>
+      <c r="C48" s="65"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2421,11 +2421,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="75" t="s">
+      <c r="A54" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="75"/>
-      <c r="C54" s="75"/>
+      <c r="B54" s="64"/>
+      <c r="C54" s="64"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2460,11 +2460,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="75" t="s">
+      <c r="A58" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="75"/>
-      <c r="C58" s="75"/>
+      <c r="B58" s="64"/>
+      <c r="C58" s="64"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2488,11 +2488,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="75" t="s">
+      <c r="A61" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="75"/>
-      <c r="C61" s="75"/>
+      <c r="B61" s="64"/>
+      <c r="C61" s="64"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2516,11 +2516,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="72" t="s">
+      <c r="A64" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="72"/>
-      <c r="C64" s="72"/>
+      <c r="B64" s="66"/>
+      <c r="C64" s="66"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2597,11 +2597,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="72" t="s">
+      <c r="A72" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="72"/>
-      <c r="C72" s="72"/>
+      <c r="B72" s="66"/>
+      <c r="C72" s="66"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2651,167 +2651,167 @@
       <c r="B78" s="25"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="63" t="s">
+      <c r="A79" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="B79" s="63"/>
-      <c r="C79" s="63"/>
-      <c r="D79" s="63"/>
-      <c r="E79" s="63"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="67"/>
+      <c r="D79" s="67"/>
+      <c r="E79" s="67"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="B80" s="73"/>
-      <c r="C80" s="73" t="s">
+      <c r="B80" s="68"/>
+      <c r="C80" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="73"/>
+      <c r="D80" s="68"/>
       <c r="E80" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="95" t="s">
+      <c r="A81" s="96" t="s">
         <v>85</v>
       </c>
-      <c r="B81" s="95"/>
-      <c r="C81" s="58"/>
-      <c r="D81" s="58"/>
+      <c r="B81" s="96"/>
+      <c r="C81" s="70"/>
+      <c r="D81" s="70"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="58" t="s">
+      <c r="A82" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="58"/>
-      <c r="C82" s="96" t="s">
+      <c r="B82" s="70"/>
+      <c r="C82" s="97" t="s">
         <v>86</v>
       </c>
-      <c r="D82" s="96"/>
+      <c r="D82" s="97"/>
       <c r="E82" s="46">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="58"/>
-      <c r="B83" s="58"/>
-      <c r="C83" s="96" t="s">
+      <c r="A83" s="70"/>
+      <c r="B83" s="70"/>
+      <c r="C83" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="D83" s="96"/>
+      <c r="D83" s="97"/>
       <c r="E83" s="46">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="58"/>
-      <c r="B84" s="58"/>
-      <c r="C84" s="96" t="s">
+      <c r="A84" s="70"/>
+      <c r="B84" s="70"/>
+      <c r="C84" s="97" t="s">
         <v>88</v>
       </c>
-      <c r="D84" s="96"/>
+      <c r="D84" s="97"/>
       <c r="E84" s="46">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="58"/>
-      <c r="B85" s="58"/>
-      <c r="C85" s="97" t="s">
+      <c r="A85" s="70"/>
+      <c r="B85" s="70"/>
+      <c r="C85" s="98" t="s">
         <v>89</v>
       </c>
-      <c r="D85" s="97"/>
+      <c r="D85" s="98"/>
       <c r="E85" s="46">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="58"/>
-      <c r="B86" s="58"/>
-      <c r="C86" s="70" t="s">
+      <c r="A86" s="70"/>
+      <c r="B86" s="70"/>
+      <c r="C86" s="75" t="s">
         <v>90</v>
       </c>
-      <c r="D86" s="70"/>
+      <c r="D86" s="75"/>
       <c r="E86" s="46">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="58"/>
-      <c r="B87" s="58"/>
-      <c r="C87" s="97" t="s">
+      <c r="A87" s="70"/>
+      <c r="B87" s="70"/>
+      <c r="C87" s="98" t="s">
         <v>91</v>
       </c>
-      <c r="D87" s="97"/>
+      <c r="D87" s="98"/>
       <c r="E87" s="46">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="58"/>
-      <c r="B88" s="58"/>
-      <c r="C88" s="96" t="s">
+      <c r="A88" s="70"/>
+      <c r="B88" s="70"/>
+      <c r="C88" s="97" t="s">
         <v>92</v>
       </c>
-      <c r="D88" s="96"/>
+      <c r="D88" s="97"/>
       <c r="E88" s="46">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="58"/>
-      <c r="B89" s="58"/>
-      <c r="C89" s="70" t="s">
+      <c r="A89" s="70"/>
+      <c r="B89" s="70"/>
+      <c r="C89" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="D89" s="70"/>
+      <c r="D89" s="75"/>
       <c r="E89" s="46">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="58"/>
-      <c r="B90" s="58"/>
-      <c r="C90" s="70" t="s">
+      <c r="A90" s="70"/>
+      <c r="B90" s="70"/>
+      <c r="C90" s="75" t="s">
         <v>94</v>
       </c>
-      <c r="D90" s="70"/>
+      <c r="D90" s="75"/>
       <c r="E90" s="46">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="58"/>
-      <c r="B91" s="58"/>
-      <c r="C91" s="98" t="s">
+      <c r="A91" s="70"/>
+      <c r="B91" s="70"/>
+      <c r="C91" s="99" t="s">
         <v>95</v>
       </c>
-      <c r="D91" s="98"/>
+      <c r="D91" s="99"/>
       <c r="E91" s="46">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="67" t="s">
+      <c r="A92" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="B92" s="67"/>
-      <c r="C92" s="71"/>
-      <c r="D92" s="71"/>
+      <c r="B92" s="71"/>
+      <c r="C92" s="76"/>
+      <c r="D92" s="76"/>
       <c r="E92" s="47">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="66" t="s">
+      <c r="C93" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="D93" s="66"/>
+      <c r="D93" s="77"/>
       <c r="E93" s="48">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2819,113 +2819,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="63" t="s">
+      <c r="A95" s="67" t="s">
         <v>98</v>
       </c>
-      <c r="B95" s="63"/>
-      <c r="C95" s="63"/>
-      <c r="D95" s="63"/>
-      <c r="E95" s="63"/>
+      <c r="B95" s="67"/>
+      <c r="C95" s="67"/>
+      <c r="D95" s="67"/>
+      <c r="E95" s="67"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="63" t="s">
+      <c r="A96" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="B96" s="63"/>
-      <c r="C96" s="63" t="s">
+      <c r="B96" s="67"/>
+      <c r="C96" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="63"/>
+      <c r="D96" s="67"/>
       <c r="E96" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="56" t="s">
+      <c r="A97" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="B97" s="56"/>
-      <c r="C97" s="57"/>
-      <c r="D97" s="57"/>
+      <c r="B97" s="69"/>
+      <c r="C97" s="78"/>
+      <c r="D97" s="78"/>
       <c r="E97" s="48">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="58" t="s">
+      <c r="A98" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="58"/>
-      <c r="C98" s="69" t="s">
+      <c r="B98" s="70"/>
+      <c r="C98" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="D98" s="69"/>
+      <c r="D98" s="74"/>
       <c r="E98" s="49">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="58"/>
-      <c r="B99" s="58"/>
-      <c r="C99" s="59" t="s">
+      <c r="A99" s="70"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="72" t="s">
         <v>119</v>
       </c>
-      <c r="D99" s="59"/>
+      <c r="D99" s="72"/>
       <c r="E99" s="49">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="58"/>
-      <c r="B100" s="58"/>
-      <c r="C100" s="59" t="s">
+      <c r="A100" s="70"/>
+      <c r="B100" s="70"/>
+      <c r="C100" s="72" t="s">
         <v>117</v>
       </c>
-      <c r="D100" s="59"/>
+      <c r="D100" s="72"/>
       <c r="E100" s="49">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="58"/>
-      <c r="B101" s="58"/>
-      <c r="C101" s="59" t="s">
+      <c r="A101" s="70"/>
+      <c r="B101" s="70"/>
+      <c r="C101" s="72" t="s">
         <v>116</v>
       </c>
-      <c r="D101" s="59"/>
+      <c r="D101" s="72"/>
       <c r="E101" s="49">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="58"/>
-      <c r="B102" s="58"/>
-      <c r="C102" s="64" t="s">
+      <c r="A102" s="70"/>
+      <c r="B102" s="70"/>
+      <c r="C102" s="83" t="s">
         <v>101</v>
       </c>
-      <c r="D102" s="94"/>
+      <c r="D102" s="100"/>
       <c r="E102" s="49">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="58" t="s">
+      <c r="A103" s="70" t="s">
         <v>96</v>
       </c>
-      <c r="B103" s="58"/>
-      <c r="C103" s="57"/>
-      <c r="D103" s="57"/>
+      <c r="B103" s="70"/>
+      <c r="C103" s="78"/>
+      <c r="D103" s="78"/>
       <c r="E103" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="55" t="s">
+      <c r="C104" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="D104" s="55"/>
+      <c r="D104" s="81"/>
       <c r="E104" s="48">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2946,91 +2946,91 @@
       <c r="E106" s="50"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="62" t="s">
+      <c r="A107" s="82" t="s">
         <v>102</v>
       </c>
-      <c r="B107" s="62"/>
-      <c r="C107" s="62"/>
-      <c r="D107" s="62"/>
-      <c r="E107" s="62"/>
+      <c r="B107" s="82"/>
+      <c r="C107" s="82"/>
+      <c r="D107" s="82"/>
+      <c r="E107" s="82"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="63" t="s">
+      <c r="A108" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="B108" s="63"/>
-      <c r="C108" s="63" t="s">
+      <c r="B108" s="67"/>
+      <c r="C108" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="63"/>
+      <c r="D108" s="67"/>
       <c r="E108" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="56" t="s">
+      <c r="A109" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="B109" s="56"/>
-      <c r="C109" s="57"/>
-      <c r="D109" s="57"/>
+      <c r="B109" s="69"/>
+      <c r="C109" s="78"/>
+      <c r="D109" s="78"/>
       <c r="E109" s="48">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="85" t="s">
+      <c r="A110" s="101" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="86"/>
-      <c r="C110" s="91" t="s">
+      <c r="B110" s="102"/>
+      <c r="C110" s="92" t="s">
         <v>123</v>
       </c>
-      <c r="D110" s="91"/>
+      <c r="D110" s="92"/>
       <c r="E110" s="46">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="87"/>
-      <c r="B111" s="88"/>
-      <c r="C111" s="92" t="s">
+      <c r="A111" s="103"/>
+      <c r="B111" s="104"/>
+      <c r="C111" s="107" t="s">
         <v>122</v>
       </c>
-      <c r="D111" s="93"/>
+      <c r="D111" s="108"/>
       <c r="E111" s="46">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="89"/>
-      <c r="B112" s="90"/>
-      <c r="C112" s="64" t="s">
+      <c r="A112" s="105"/>
+      <c r="B112" s="106"/>
+      <c r="C112" s="83" t="s">
         <v>127</v>
       </c>
-      <c r="D112" s="94"/>
+      <c r="D112" s="100"/>
       <c r="E112" s="46">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="58" t="s">
+      <c r="A113" s="70" t="s">
         <v>96</v>
       </c>
-      <c r="B113" s="58"/>
-      <c r="C113" s="57"/>
-      <c r="D113" s="57"/>
+      <c r="B113" s="70"/>
+      <c r="C113" s="78"/>
+      <c r="D113" s="78"/>
       <c r="E113" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="55" t="s">
+      <c r="C114" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="D114" s="55"/>
+      <c r="D114" s="81"/>
       <c r="E114" s="48">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6782,42 +6782,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6831,35 +6824,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6899,13 +6899,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7140,13 +7140,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="81" t="s">
+      <c r="A10" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="B10" s="81"/>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
+      <c r="B10" s="56"/>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7174,10 +7174,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="82"/>
+      <c r="D11" s="57"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7189,10 +7189,10 @@
       <c r="B12" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="83" t="s">
+      <c r="C12" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="83"/>
+      <c r="D12" s="58"/>
       <c r="E12" s="53">
         <v>2485</v>
       </c>
@@ -7204,10 +7204,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="60" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="77"/>
+      <c r="D13" s="60"/>
       <c r="E13" s="30">
         <v>55</v>
       </c>
@@ -7219,10 +7219,10 @@
       <c r="B14" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="84" t="s">
+      <c r="C14" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="77"/>
+      <c r="D14" s="60"/>
       <c r="E14" s="30">
         <v>100</v>
       </c>
@@ -7243,13 +7243,13 @@
       <c r="B16" s="25"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="79" t="s">
+      <c r="A17" s="61" t="s">
         <v>107</v>
       </c>
-      <c r="B17" s="79"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="79"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7277,10 +7277,10 @@
       <c r="B18" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="76"/>
+      <c r="D18" s="62"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7292,10 +7292,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="77" t="s">
+      <c r="C19" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="77"/>
+      <c r="D19" s="60"/>
       <c r="E19" s="30">
         <v>2485</v>
       </c>
@@ -7303,8 +7303,8 @@
     <row r="20" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="77"/>
-      <c r="D20" s="77"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
       <c r="E20" s="30">
         <v>0</v>
       </c>
@@ -7326,13 +7326,13 @@
       <c r="B22" s="25"/>
     </row>
     <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="79" t="s">
+      <c r="A23" s="61" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="79"/>
-      <c r="C23" s="79"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="61"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
@@ -7360,10 +7360,10 @@
       <c r="B24" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="76" t="s">
+      <c r="C24" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="76"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="2" t="s">
         <v>12</v>
       </c>
@@ -7375,10 +7375,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="77" t="s">
+      <c r="C25" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="77"/>
+      <c r="D25" s="60"/>
       <c r="E25" s="34">
         <v>2485</v>
       </c>
@@ -7386,8 +7386,8 @@
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
-      <c r="C26" s="77"/>
-      <c r="D26" s="77"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="60"/>
       <c r="E26" s="30">
         <v>0</v>
       </c>
@@ -7409,11 +7409,11 @@
       <c r="B28" s="25"/>
     </row>
     <row r="29" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="78" t="s">
+      <c r="A29" s="63" t="s">
         <v>109</v>
       </c>
-      <c r="B29" s="78"/>
-      <c r="C29" s="78"/>
+      <c r="B29" s="63"/>
+      <c r="C29" s="63"/>
     </row>
     <row r="30" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -7428,11 +7428,11 @@
       <c r="D30" s="38"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="75" t="s">
+      <c r="A31" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="75"/>
-      <c r="C31" s="75"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
     </row>
     <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="51" t="s">
@@ -7478,16 +7478,16 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="74" t="s">
+      <c r="A36" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="74"/>
-      <c r="C36" s="74"/>
+      <c r="B36" s="65"/>
+      <c r="C36" s="65"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="74"/>
-      <c r="B37" s="74"/>
-      <c r="C37" s="74"/>
+      <c r="A37" s="65"/>
+      <c r="B37" s="65"/>
+      <c r="C37" s="65"/>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
@@ -7536,11 +7536,11 @@
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="75" t="s">
+      <c r="A43" s="64" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="75"/>
-      <c r="C43" s="75"/>
+      <c r="B43" s="64"/>
+      <c r="C43" s="64"/>
     </row>
     <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
@@ -7575,11 +7575,11 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="75" t="s">
+      <c r="A47" s="64" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="75"/>
-      <c r="C47" s="75"/>
+      <c r="B47" s="64"/>
+      <c r="C47" s="64"/>
     </row>
     <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
@@ -7603,11 +7603,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="75" t="s">
+      <c r="A50" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="75"/>
-      <c r="C50" s="75"/>
+      <c r="B50" s="64"/>
+      <c r="C50" s="64"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7631,11 +7631,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="72" t="s">
+      <c r="A53" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="72"/>
-      <c r="C53" s="72"/>
+      <c r="B53" s="66"/>
+      <c r="C53" s="66"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="17" t="s">
@@ -7712,11 +7712,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="72" t="s">
+      <c r="A61" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="B61" s="72"/>
-      <c r="C61" s="72"/>
+      <c r="B61" s="66"/>
+      <c r="C61" s="66"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
@@ -7766,91 +7766,91 @@
       <c r="B67" s="25"/>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="63" t="s">
+      <c r="A68" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="B68" s="63"/>
-      <c r="C68" s="63"/>
-      <c r="D68" s="63"/>
-      <c r="E68" s="63"/>
+      <c r="B68" s="67"/>
+      <c r="C68" s="67"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="67"/>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="73" t="s">
+      <c r="A69" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="B69" s="73"/>
-      <c r="C69" s="73" t="s">
+      <c r="B69" s="68"/>
+      <c r="C69" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D69" s="73"/>
+      <c r="D69" s="68"/>
       <c r="E69" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="56" t="s">
+      <c r="A70" s="69" t="s">
         <v>111</v>
       </c>
-      <c r="B70" s="56"/>
-      <c r="C70" s="58"/>
-      <c r="D70" s="58"/>
+      <c r="B70" s="69"/>
+      <c r="C70" s="70"/>
+      <c r="D70" s="70"/>
       <c r="E70" s="48">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="67" t="s">
+      <c r="A71" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="67"/>
-      <c r="C71" s="59" t="s">
+      <c r="B71" s="71"/>
+      <c r="C71" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="D71" s="59"/>
+      <c r="D71" s="72"/>
       <c r="E71" s="46">
         <v>600</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="224" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="67"/>
-      <c r="B72" s="67"/>
-      <c r="C72" s="68" t="s">
+      <c r="A72" s="71"/>
+      <c r="B72" s="71"/>
+      <c r="C72" s="73" t="s">
         <v>131</v>
       </c>
-      <c r="D72" s="69"/>
+      <c r="D72" s="74"/>
       <c r="E72" s="46">
         <v>422.2</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="91" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="67"/>
-      <c r="B73" s="67"/>
-      <c r="C73" s="68" t="s">
+      <c r="A73" s="71"/>
+      <c r="B73" s="71"/>
+      <c r="C73" s="73" t="s">
         <v>132</v>
       </c>
-      <c r="D73" s="70"/>
+      <c r="D73" s="75"/>
       <c r="E73" s="46">
         <v>424.5</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="67" t="s">
+      <c r="A74" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="B74" s="67"/>
-      <c r="C74" s="71"/>
-      <c r="D74" s="71"/>
+      <c r="B74" s="71"/>
+      <c r="C74" s="76"/>
+      <c r="D74" s="76"/>
       <c r="E74" s="47">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C75" s="66" t="s">
+      <c r="C75" s="77" t="s">
         <v>97</v>
       </c>
-      <c r="D75" s="66"/>
+      <c r="D75" s="77"/>
       <c r="E75" s="48">
         <f>(E15+E70)-SUM(E71:E74)</f>
         <v>133</v>
@@ -7858,34 +7858,34 @@
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="63" t="s">
+      <c r="A77" s="67" t="s">
         <v>112</v>
       </c>
-      <c r="B77" s="63"/>
-      <c r="C77" s="63"/>
-      <c r="D77" s="63"/>
-      <c r="E77" s="63"/>
+      <c r="B77" s="67"/>
+      <c r="C77" s="67"/>
+      <c r="D77" s="67"/>
+      <c r="E77" s="67"/>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="63" t="s">
+      <c r="A78" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="B78" s="63"/>
-      <c r="C78" s="63" t="s">
+      <c r="B78" s="67"/>
+      <c r="C78" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D78" s="63"/>
+      <c r="D78" s="67"/>
       <c r="E78" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="56" t="s">
+      <c r="A79" s="69" t="s">
         <v>113</v>
       </c>
-      <c r="B79" s="56"/>
-      <c r="C79" s="57"/>
-      <c r="D79" s="57"/>
+      <c r="B79" s="69"/>
+      <c r="C79" s="78"/>
+      <c r="D79" s="78"/>
       <c r="E79" s="48">
         <f>E75</f>
         <v>133</v>
@@ -7894,10 +7894,10 @@
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="54"/>
       <c r="B80" s="54"/>
-      <c r="C80" s="60" t="s">
+      <c r="C80" s="79" t="s">
         <v>135</v>
       </c>
-      <c r="D80" s="61"/>
+      <c r="D80" s="80"/>
       <c r="E80" s="49">
         <v>0</v>
       </c>
@@ -7907,10 +7907,10 @@
         <v>67</v>
       </c>
       <c r="B81" s="7"/>
-      <c r="C81" s="59" t="s">
+      <c r="C81" s="72" t="s">
         <v>124</v>
       </c>
-      <c r="D81" s="59"/>
+      <c r="D81" s="72"/>
       <c r="E81" s="49">
         <v>0</v>
       </c>
@@ -7918,8 +7918,8 @@
     <row r="82" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="7"/>
       <c r="B82" s="7"/>
-      <c r="C82" s="64"/>
-      <c r="D82" s="65"/>
+      <c r="C82" s="83"/>
+      <c r="D82" s="84"/>
       <c r="E82" s="49">
         <v>0</v>
       </c>
@@ -7927,29 +7927,29 @@
     <row r="83" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="7"/>
       <c r="B83" s="7"/>
-      <c r="C83" s="65"/>
-      <c r="D83" s="65"/>
+      <c r="C83" s="84"/>
+      <c r="D83" s="84"/>
       <c r="E83" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="58" t="s">
+      <c r="A84" s="70" t="s">
         <v>96</v>
       </c>
-      <c r="B84" s="58"/>
-      <c r="C84" s="57"/>
-      <c r="D84" s="57"/>
+      <c r="B84" s="70"/>
+      <c r="C84" s="78"/>
+      <c r="D84" s="78"/>
       <c r="E84" s="46">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="55" t="s">
+      <c r="C85" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="D85" s="55"/>
+      <c r="D85" s="81"/>
       <c r="E85" s="48">
         <f>(E21+E79)-SUM(E80:E84)</f>
         <v>1447</v>
@@ -7970,69 +7970,69 @@
       <c r="E87" s="50"/>
     </row>
     <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="62" t="s">
+      <c r="A88" s="82" t="s">
         <v>114</v>
       </c>
-      <c r="B88" s="62"/>
-      <c r="C88" s="62"/>
-      <c r="D88" s="62"/>
-      <c r="E88" s="62"/>
+      <c r="B88" s="82"/>
+      <c r="C88" s="82"/>
+      <c r="D88" s="82"/>
+      <c r="E88" s="82"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="63" t="s">
+      <c r="A89" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="B89" s="63"/>
-      <c r="C89" s="63" t="s">
+      <c r="B89" s="67"/>
+      <c r="C89" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="63"/>
+      <c r="D89" s="67"/>
       <c r="E89" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="56" t="s">
+      <c r="A90" s="69" t="s">
         <v>115</v>
       </c>
-      <c r="B90" s="56"/>
-      <c r="C90" s="57"/>
-      <c r="D90" s="57"/>
+      <c r="B90" s="69"/>
+      <c r="C90" s="78"/>
+      <c r="D90" s="78"/>
       <c r="E90" s="48">
         <f>E85</f>
         <v>1447</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="58" t="s">
+      <c r="A91" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="58"/>
-      <c r="C91" s="59" t="s">
+      <c r="B91" s="70"/>
+      <c r="C91" s="72" t="s">
         <v>124</v>
       </c>
-      <c r="D91" s="59"/>
+      <c r="D91" s="72"/>
       <c r="E91" s="46">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="58" t="s">
+      <c r="A92" s="70" t="s">
         <v>96</v>
       </c>
-      <c r="B92" s="58"/>
-      <c r="C92" s="57"/>
-      <c r="D92" s="57"/>
+      <c r="B92" s="70"/>
+      <c r="C92" s="78"/>
+      <c r="D92" s="78"/>
       <c r="E92" s="46">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="55" t="s">
+      <c r="C93" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="D93" s="55"/>
+      <c r="D93" s="81"/>
       <c r="E93" s="48">
         <f>(E27+E90)-SUM(E91:E92)</f>
         <v>2761</v>
@@ -11784,45 +11784,13 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A36:C37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="A71:B73"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
     <mergeCell ref="C80:D80"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="A88:E88"/>
@@ -11833,13 +11801,45 @@
     <mergeCell ref="C83:D83"/>
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="A71:B73"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="A36:C37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E70">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146FE8E4-594E-FA43-A345-64BB457516B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7C3833-F576-EE46-BAAB-D4C92C9E45F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -989,7 +989,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1150,8 +1150,80 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1167,129 +1239,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1309,11 +1258,59 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1632,13 +1629,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1868,13 +1865,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="56"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
+      <c r="B10" s="80"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="80"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1902,10 +1899,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="57"/>
+      <c r="D11" s="81"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1917,10 +1914,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="85" t="s">
+      <c r="C12" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="85"/>
+      <c r="D12" s="106"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1932,10 +1929,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="C13" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="86"/>
+      <c r="D13" s="107"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1945,10 +1942,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="60" t="s">
+      <c r="C14" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="60"/>
+      <c r="D14" s="76"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -1958,10 +1955,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="60" t="s">
+      <c r="C15" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="60"/>
+      <c r="D15" s="76"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -1971,10 +1968,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="76" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="60"/>
+      <c r="D16" s="76"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -1986,10 +1983,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="87" t="s">
+      <c r="C17" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="87"/>
+      <c r="D17" s="102"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -1999,10 +1996,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="88" t="s">
+      <c r="C18" s="103" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="88"/>
+      <c r="D18" s="103"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2014,10 +2011,10 @@
       <c r="B19" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="89" t="s">
+      <c r="C19" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="89"/>
+      <c r="D19" s="104"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2038,13 +2035,13 @@
       <c r="B21" s="25"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="78"/>
+      <c r="D22" s="78"/>
+      <c r="E22" s="78"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2072,10 +2069,10 @@
       <c r="B23" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="90" t="s">
+      <c r="C23" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="90"/>
+      <c r="D23" s="105"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2087,10 +2084,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="60"/>
+      <c r="D24" s="76"/>
       <c r="E24" s="30">
         <v>2485</v>
       </c>
@@ -2102,10 +2099,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="60" t="s">
+      <c r="C25" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="60"/>
+      <c r="D25" s="76"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2115,10 +2112,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="91" t="s">
+      <c r="C26" s="101" t="s">
         <v>120</v>
       </c>
-      <c r="D26" s="87"/>
+      <c r="D26" s="102"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2130,10 +2127,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="88" t="s">
+      <c r="C27" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="88"/>
+      <c r="D27" s="103"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2143,10 +2140,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="92" t="s">
+      <c r="C28" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="92"/>
+      <c r="D28" s="90"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2168,13 +2165,13 @@
       <c r="B30" s="25"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="61" t="s">
+      <c r="A31" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="78"/>
+      <c r="D31" s="78"/>
+      <c r="E31" s="78"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2202,10 +2199,10 @@
       <c r="B32" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="62" t="s">
+      <c r="C32" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="62"/>
+      <c r="D32" s="75"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2217,10 +2214,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="60" t="s">
+      <c r="C33" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="60"/>
+      <c r="D33" s="76"/>
       <c r="E33" s="34">
         <v>2485</v>
       </c>
@@ -2230,10 +2227,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="60" t="s">
+      <c r="C34" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="60"/>
+      <c r="D34" s="76"/>
       <c r="E34" s="34">
         <v>118</v>
       </c>
@@ -2243,10 +2240,10 @@
       <c r="B35" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="93" t="s">
+      <c r="C35" s="98" t="s">
         <v>125</v>
       </c>
-      <c r="D35" s="94"/>
+      <c r="D35" s="99"/>
       <c r="E35" s="34">
         <v>170</v>
       </c>
@@ -2256,10 +2253,10 @@
       <c r="B36" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="93" t="s">
+      <c r="C36" s="98" t="s">
         <v>121</v>
       </c>
-      <c r="D36" s="95"/>
+      <c r="D36" s="100"/>
       <c r="E36" s="34">
         <v>800</v>
       </c>
@@ -2269,10 +2266,10 @@
       <c r="B37" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="91" t="s">
+      <c r="C37" s="101" t="s">
         <v>126</v>
       </c>
-      <c r="D37" s="60"/>
+      <c r="D37" s="76"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2294,11 +2291,11 @@
       <c r="B39" s="25"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="63" t="s">
+      <c r="A40" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="63"/>
-      <c r="C40" s="63"/>
+      <c r="B40" s="77"/>
+      <c r="C40" s="77"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2313,11 +2310,11 @@
       <c r="D41" s="38"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="64" t="s">
+      <c r="A42" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="64"/>
-      <c r="C42" s="64"/>
+      <c r="B42" s="74"/>
+      <c r="C42" s="74"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="51" t="s">
@@ -2363,16 +2360,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="65" t="s">
+      <c r="A47" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="65"/>
-      <c r="C47" s="65"/>
+      <c r="B47" s="73"/>
+      <c r="C47" s="73"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="65"/>
-      <c r="B48" s="65"/>
-      <c r="C48" s="65"/>
+      <c r="A48" s="73"/>
+      <c r="B48" s="73"/>
+      <c r="C48" s="73"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2421,11 +2418,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="64" t="s">
+      <c r="A54" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="64"/>
-      <c r="C54" s="64"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="74"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2460,11 +2457,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="64" t="s">
+      <c r="A58" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="64"/>
-      <c r="C58" s="64"/>
+      <c r="B58" s="74"/>
+      <c r="C58" s="74"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2488,11 +2485,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="64" t="s">
+      <c r="A61" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="64"/>
-      <c r="C61" s="64"/>
+      <c r="B61" s="74"/>
+      <c r="C61" s="74"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2516,11 +2513,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="66" t="s">
+      <c r="A64" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="66"/>
-      <c r="C64" s="66"/>
+      <c r="B64" s="71"/>
+      <c r="C64" s="71"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2597,11 +2594,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="66" t="s">
+      <c r="A72" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="66"/>
-      <c r="C72" s="66"/>
+      <c r="B72" s="71"/>
+      <c r="C72" s="71"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2651,167 +2648,167 @@
       <c r="B78" s="25"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="67" t="s">
+      <c r="A79" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="B79" s="67"/>
-      <c r="C79" s="67"/>
-      <c r="D79" s="67"/>
-      <c r="E79" s="67"/>
+      <c r="B79" s="62"/>
+      <c r="C79" s="62"/>
+      <c r="D79" s="62"/>
+      <c r="E79" s="62"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="68" t="s">
+      <c r="A80" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="B80" s="68"/>
-      <c r="C80" s="68" t="s">
+      <c r="B80" s="72"/>
+      <c r="C80" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="68"/>
+      <c r="D80" s="72"/>
       <c r="E80" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="96" t="s">
+      <c r="A81" s="94" t="s">
         <v>85</v>
       </c>
-      <c r="B81" s="96"/>
-      <c r="C81" s="70"/>
-      <c r="D81" s="70"/>
+      <c r="B81" s="94"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="70" t="s">
+      <c r="A82" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="70"/>
-      <c r="C82" s="97" t="s">
+      <c r="B82" s="57"/>
+      <c r="C82" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="D82" s="97"/>
+      <c r="D82" s="95"/>
       <c r="E82" s="46">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="70"/>
-      <c r="B83" s="70"/>
-      <c r="C83" s="97" t="s">
+      <c r="A83" s="57"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="D83" s="97"/>
+      <c r="D83" s="95"/>
       <c r="E83" s="46">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="70"/>
-      <c r="B84" s="70"/>
-      <c r="C84" s="97" t="s">
+      <c r="A84" s="57"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="95" t="s">
         <v>88</v>
       </c>
-      <c r="D84" s="97"/>
+      <c r="D84" s="95"/>
       <c r="E84" s="46">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="70"/>
-      <c r="B85" s="70"/>
-      <c r="C85" s="98" t="s">
+      <c r="A85" s="57"/>
+      <c r="B85" s="57"/>
+      <c r="C85" s="96" t="s">
         <v>89</v>
       </c>
-      <c r="D85" s="98"/>
+      <c r="D85" s="96"/>
       <c r="E85" s="46">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="70"/>
-      <c r="B86" s="70"/>
-      <c r="C86" s="75" t="s">
+      <c r="A86" s="57"/>
+      <c r="B86" s="57"/>
+      <c r="C86" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="D86" s="75"/>
+      <c r="D86" s="69"/>
       <c r="E86" s="46">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="70"/>
-      <c r="B87" s="70"/>
-      <c r="C87" s="98" t="s">
+      <c r="A87" s="57"/>
+      <c r="B87" s="57"/>
+      <c r="C87" s="96" t="s">
         <v>91</v>
       </c>
-      <c r="D87" s="98"/>
+      <c r="D87" s="96"/>
       <c r="E87" s="46">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="70"/>
-      <c r="B88" s="70"/>
-      <c r="C88" s="97" t="s">
+      <c r="A88" s="57"/>
+      <c r="B88" s="57"/>
+      <c r="C88" s="95" t="s">
         <v>92</v>
       </c>
-      <c r="D88" s="97"/>
+      <c r="D88" s="95"/>
       <c r="E88" s="46">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="70"/>
-      <c r="B89" s="70"/>
-      <c r="C89" s="75" t="s">
+      <c r="A89" s="57"/>
+      <c r="B89" s="57"/>
+      <c r="C89" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="D89" s="75"/>
+      <c r="D89" s="69"/>
       <c r="E89" s="46">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="70"/>
-      <c r="B90" s="70"/>
-      <c r="C90" s="75" t="s">
+      <c r="A90" s="57"/>
+      <c r="B90" s="57"/>
+      <c r="C90" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="D90" s="75"/>
+      <c r="D90" s="69"/>
       <c r="E90" s="46">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="70"/>
-      <c r="B91" s="70"/>
-      <c r="C91" s="99" t="s">
+      <c r="A91" s="57"/>
+      <c r="B91" s="57"/>
+      <c r="C91" s="97" t="s">
         <v>95</v>
       </c>
-      <c r="D91" s="99"/>
+      <c r="D91" s="97"/>
       <c r="E91" s="46">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="71" t="s">
+      <c r="A92" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="B92" s="71"/>
-      <c r="C92" s="76"/>
-      <c r="D92" s="76"/>
+      <c r="B92" s="66"/>
+      <c r="C92" s="70"/>
+      <c r="D92" s="70"/>
       <c r="E92" s="47">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="77" t="s">
+      <c r="C93" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="D93" s="77"/>
+      <c r="D93" s="65"/>
       <c r="E93" s="48">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2819,113 +2816,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="67" t="s">
+      <c r="A95" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="B95" s="67"/>
-      <c r="C95" s="67"/>
-      <c r="D95" s="67"/>
-      <c r="E95" s="67"/>
+      <c r="B95" s="62"/>
+      <c r="C95" s="62"/>
+      <c r="D95" s="62"/>
+      <c r="E95" s="62"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="67" t="s">
+      <c r="A96" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="B96" s="67"/>
-      <c r="C96" s="67" t="s">
+      <c r="B96" s="62"/>
+      <c r="C96" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="67"/>
+      <c r="D96" s="62"/>
       <c r="E96" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="69" t="s">
+      <c r="A97" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="B97" s="69"/>
-      <c r="C97" s="78"/>
-      <c r="D97" s="78"/>
+      <c r="B97" s="55"/>
+      <c r="C97" s="56"/>
+      <c r="D97" s="56"/>
       <c r="E97" s="48">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="70" t="s">
+      <c r="A98" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="70"/>
-      <c r="C98" s="74" t="s">
+      <c r="B98" s="57"/>
+      <c r="C98" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="D98" s="74"/>
+      <c r="D98" s="68"/>
       <c r="E98" s="49">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="70"/>
-      <c r="B99" s="70"/>
-      <c r="C99" s="72" t="s">
+      <c r="A99" s="57"/>
+      <c r="B99" s="57"/>
+      <c r="C99" s="58" t="s">
         <v>119</v>
       </c>
-      <c r="D99" s="72"/>
+      <c r="D99" s="58"/>
       <c r="E99" s="49">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="70"/>
-      <c r="B100" s="70"/>
-      <c r="C100" s="72" t="s">
+      <c r="A100" s="57"/>
+      <c r="B100" s="57"/>
+      <c r="C100" s="58" t="s">
         <v>117</v>
       </c>
-      <c r="D100" s="72"/>
+      <c r="D100" s="58"/>
       <c r="E100" s="49">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="70"/>
-      <c r="B101" s="70"/>
-      <c r="C101" s="72" t="s">
+      <c r="A101" s="57"/>
+      <c r="B101" s="57"/>
+      <c r="C101" s="58" t="s">
         <v>116</v>
       </c>
-      <c r="D101" s="72"/>
+      <c r="D101" s="58"/>
       <c r="E101" s="49">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="70"/>
-      <c r="B102" s="70"/>
-      <c r="C102" s="83" t="s">
+      <c r="A102" s="57"/>
+      <c r="B102" s="57"/>
+      <c r="C102" s="63" t="s">
         <v>101</v>
       </c>
-      <c r="D102" s="100"/>
+      <c r="D102" s="93"/>
       <c r="E102" s="49">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="70" t="s">
+      <c r="A103" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="B103" s="70"/>
-      <c r="C103" s="78"/>
-      <c r="D103" s="78"/>
+      <c r="B103" s="57"/>
+      <c r="C103" s="56"/>
+      <c r="D103" s="56"/>
       <c r="E103" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="81" t="s">
+      <c r="C104" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="D104" s="81"/>
+      <c r="D104" s="54"/>
       <c r="E104" s="48">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2946,91 +2943,91 @@
       <c r="E106" s="50"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="82" t="s">
+      <c r="A107" s="61" t="s">
         <v>102</v>
       </c>
-      <c r="B107" s="82"/>
-      <c r="C107" s="82"/>
-      <c r="D107" s="82"/>
-      <c r="E107" s="82"/>
+      <c r="B107" s="61"/>
+      <c r="C107" s="61"/>
+      <c r="D107" s="61"/>
+      <c r="E107" s="61"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="67" t="s">
+      <c r="A108" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="B108" s="67"/>
-      <c r="C108" s="67" t="s">
+      <c r="B108" s="62"/>
+      <c r="C108" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="67"/>
+      <c r="D108" s="62"/>
       <c r="E108" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="69" t="s">
+      <c r="A109" s="55" t="s">
         <v>103</v>
       </c>
-      <c r="B109" s="69"/>
-      <c r="C109" s="78"/>
-      <c r="D109" s="78"/>
+      <c r="B109" s="55"/>
+      <c r="C109" s="56"/>
+      <c r="D109" s="56"/>
       <c r="E109" s="48">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="101" t="s">
+      <c r="A110" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="102"/>
-      <c r="C110" s="92" t="s">
+      <c r="B110" s="85"/>
+      <c r="C110" s="90" t="s">
         <v>123</v>
       </c>
-      <c r="D110" s="92"/>
+      <c r="D110" s="90"/>
       <c r="E110" s="46">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="103"/>
-      <c r="B111" s="104"/>
-      <c r="C111" s="107" t="s">
+      <c r="A111" s="86"/>
+      <c r="B111" s="87"/>
+      <c r="C111" s="91" t="s">
         <v>122</v>
       </c>
-      <c r="D111" s="108"/>
+      <c r="D111" s="92"/>
       <c r="E111" s="46">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="105"/>
-      <c r="B112" s="106"/>
-      <c r="C112" s="83" t="s">
+      <c r="A112" s="88"/>
+      <c r="B112" s="89"/>
+      <c r="C112" s="63" t="s">
         <v>127</v>
       </c>
-      <c r="D112" s="100"/>
+      <c r="D112" s="93"/>
       <c r="E112" s="46">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="70" t="s">
+      <c r="A113" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="B113" s="70"/>
-      <c r="C113" s="78"/>
-      <c r="D113" s="78"/>
+      <c r="B113" s="57"/>
+      <c r="C113" s="56"/>
+      <c r="D113" s="56"/>
       <c r="E113" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="81" t="s">
+      <c r="C114" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="D114" s="81"/>
+      <c r="D114" s="54"/>
       <c r="E114" s="48">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6782,35 +6779,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6824,42 +6828,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6899,13 +6896,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="79" t="s">
         <v>104</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7140,13 +7137,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="56" t="s">
+      <c r="A10" s="80" t="s">
         <v>105</v>
       </c>
-      <c r="B10" s="56"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
+      <c r="B10" s="80"/>
+      <c r="C10" s="80"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="80"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7174,10 +7171,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="57"/>
+      <c r="D11" s="81"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7189,10 +7186,10 @@
       <c r="B12" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="58"/>
+      <c r="D12" s="82"/>
       <c r="E12" s="53">
         <v>2485</v>
       </c>
@@ -7204,10 +7201,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="60" t="s">
+      <c r="C13" s="76" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="60"/>
+      <c r="D13" s="76"/>
       <c r="E13" s="30">
         <v>55</v>
       </c>
@@ -7219,10 +7216,10 @@
       <c r="B14" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="83" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="60"/>
+      <c r="D14" s="76"/>
       <c r="E14" s="30">
         <v>100</v>
       </c>
@@ -7243,13 +7240,13 @@
       <c r="B16" s="25"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="78" t="s">
         <v>107</v>
       </c>
-      <c r="B17" s="61"/>
-      <c r="C17" s="61"/>
-      <c r="D17" s="61"/>
-      <c r="E17" s="61"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="78"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7277,10 +7274,10 @@
       <c r="B18" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="62" t="s">
+      <c r="C18" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="62"/>
+      <c r="D18" s="75"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7292,10 +7289,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="60" t="s">
+      <c r="C19" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="60"/>
+      <c r="D19" s="76"/>
       <c r="E19" s="30">
         <v>2485</v>
       </c>
@@ -7303,8 +7300,8 @@
     <row r="20" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
       <c r="E20" s="30">
         <v>0</v>
       </c>
@@ -7326,13 +7323,13 @@
       <c r="B22" s="25"/>
     </row>
     <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="61" t="s">
+      <c r="A23" s="78" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="61"/>
-      <c r="C23" s="61"/>
-      <c r="D23" s="61"/>
-      <c r="E23" s="61"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="78"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
@@ -7360,10 +7357,10 @@
       <c r="B24" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="62"/>
+      <c r="D24" s="75"/>
       <c r="E24" s="2" t="s">
         <v>12</v>
       </c>
@@ -7375,10 +7372,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="60" t="s">
+      <c r="C25" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="60"/>
+      <c r="D25" s="76"/>
       <c r="E25" s="34">
         <v>2485</v>
       </c>
@@ -7386,8 +7383,8 @@
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="60"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="76"/>
       <c r="E26" s="30">
         <v>0</v>
       </c>
@@ -7409,11 +7406,11 @@
       <c r="B28" s="25"/>
     </row>
     <row r="29" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="63" t="s">
+      <c r="A29" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="B29" s="63"/>
-      <c r="C29" s="63"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="77"/>
     </row>
     <row r="30" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -7428,11 +7425,11 @@
       <c r="D30" s="38"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="64" t="s">
+      <c r="A31" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="64"/>
-      <c r="C31" s="64"/>
+      <c r="B31" s="74"/>
+      <c r="C31" s="74"/>
     </row>
     <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="51" t="s">
@@ -7478,16 +7475,16 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="65" t="s">
+      <c r="A36" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="65"/>
-      <c r="C36" s="65"/>
+      <c r="B36" s="73"/>
+      <c r="C36" s="73"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="65"/>
-      <c r="B37" s="65"/>
-      <c r="C37" s="65"/>
+      <c r="A37" s="73"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="73"/>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
@@ -7536,11 +7533,11 @@
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="64" t="s">
+      <c r="A43" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="64"/>
-      <c r="C43" s="64"/>
+      <c r="B43" s="74"/>
+      <c r="C43" s="74"/>
     </row>
     <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
@@ -7575,11 +7572,11 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="64" t="s">
+      <c r="A47" s="74" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="64"/>
-      <c r="C47" s="64"/>
+      <c r="B47" s="74"/>
+      <c r="C47" s="74"/>
     </row>
     <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
@@ -7603,11 +7600,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="64" t="s">
+      <c r="A50" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="64"/>
-      <c r="C50" s="64"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="74"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7631,11 +7628,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="66" t="s">
+      <c r="A53" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="66"/>
-      <c r="C53" s="66"/>
+      <c r="B53" s="71"/>
+      <c r="C53" s="71"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="17" t="s">
@@ -7712,11 +7709,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="66" t="s">
+      <c r="A61" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="B61" s="66"/>
-      <c r="C61" s="66"/>
+      <c r="B61" s="71"/>
+      <c r="C61" s="71"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
@@ -7766,91 +7763,91 @@
       <c r="B67" s="25"/>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="67" t="s">
+      <c r="A68" s="62" t="s">
         <v>110</v>
       </c>
-      <c r="B68" s="67"/>
-      <c r="C68" s="67"/>
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
+      <c r="B68" s="62"/>
+      <c r="C68" s="62"/>
+      <c r="D68" s="62"/>
+      <c r="E68" s="62"/>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="68" t="s">
+      <c r="A69" s="72" t="s">
         <v>84</v>
       </c>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68" t="s">
+      <c r="B69" s="72"/>
+      <c r="C69" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="D69" s="68"/>
+      <c r="D69" s="72"/>
       <c r="E69" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="69" t="s">
+      <c r="A70" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="B70" s="69"/>
-      <c r="C70" s="70"/>
-      <c r="D70" s="70"/>
+      <c r="B70" s="55"/>
+      <c r="C70" s="57"/>
+      <c r="D70" s="57"/>
       <c r="E70" s="48">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="71" t="s">
+      <c r="A71" s="66" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="71"/>
-      <c r="C71" s="72" t="s">
+      <c r="B71" s="66"/>
+      <c r="C71" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="D71" s="72"/>
+      <c r="D71" s="58"/>
       <c r="E71" s="46">
         <v>600</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="224" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="71"/>
-      <c r="B72" s="71"/>
-      <c r="C72" s="73" t="s">
+      <c r="A72" s="66"/>
+      <c r="B72" s="66"/>
+      <c r="C72" s="67" t="s">
         <v>131</v>
       </c>
-      <c r="D72" s="74"/>
+      <c r="D72" s="68"/>
       <c r="E72" s="46">
         <v>422.2</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="91" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="71"/>
-      <c r="B73" s="71"/>
-      <c r="C73" s="73" t="s">
+      <c r="A73" s="66"/>
+      <c r="B73" s="66"/>
+      <c r="C73" s="67" t="s">
         <v>132</v>
       </c>
-      <c r="D73" s="75"/>
+      <c r="D73" s="69"/>
       <c r="E73" s="46">
         <v>424.5</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="71" t="s">
+      <c r="A74" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="B74" s="71"/>
-      <c r="C74" s="76"/>
-      <c r="D74" s="76"/>
+      <c r="B74" s="66"/>
+      <c r="C74" s="70"/>
+      <c r="D74" s="70"/>
       <c r="E74" s="47">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C75" s="77" t="s">
+      <c r="C75" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="D75" s="77"/>
+      <c r="D75" s="65"/>
       <c r="E75" s="48">
         <f>(E15+E70)-SUM(E71:E74)</f>
         <v>133</v>
@@ -7858,98 +7855,98 @@
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="67" t="s">
+      <c r="A77" s="62" t="s">
         <v>112</v>
       </c>
-      <c r="B77" s="67"/>
-      <c r="C77" s="67"/>
-      <c r="D77" s="67"/>
-      <c r="E77" s="67"/>
+      <c r="B77" s="62"/>
+      <c r="C77" s="62"/>
+      <c r="D77" s="62"/>
+      <c r="E77" s="62"/>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="67" t="s">
+      <c r="A78" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="B78" s="67"/>
-      <c r="C78" s="67" t="s">
+      <c r="B78" s="62"/>
+      <c r="C78" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D78" s="67"/>
+      <c r="D78" s="62"/>
       <c r="E78" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="69" t="s">
+      <c r="A79" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="B79" s="69"/>
-      <c r="C79" s="78"/>
-      <c r="D79" s="78"/>
+      <c r="B79" s="55"/>
+      <c r="C79" s="56"/>
+      <c r="D79" s="56"/>
       <c r="E79" s="48">
         <f>E75</f>
         <v>133</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="54"/>
-      <c r="B80" s="54"/>
-      <c r="C80" s="79" t="s">
+      <c r="A80" s="84" t="s">
+        <v>67</v>
+      </c>
+      <c r="B80" s="85"/>
+      <c r="C80" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="D80" s="80"/>
+      <c r="D80" s="60"/>
       <c r="E80" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B81" s="7"/>
-      <c r="C81" s="72" t="s">
+      <c r="A81" s="86"/>
+      <c r="B81" s="87"/>
+      <c r="C81" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="D81" s="72"/>
+      <c r="D81" s="58"/>
       <c r="E81" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="7"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="83"/>
-      <c r="D82" s="84"/>
+      <c r="A82" s="86"/>
+      <c r="B82" s="87"/>
+      <c r="C82" s="63"/>
+      <c r="D82" s="64"/>
       <c r="E82" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="7"/>
-      <c r="B83" s="7"/>
-      <c r="C83" s="84"/>
-      <c r="D83" s="84"/>
+      <c r="A83" s="88"/>
+      <c r="B83" s="89"/>
+      <c r="C83" s="64"/>
+      <c r="D83" s="64"/>
       <c r="E83" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="70" t="s">
+      <c r="A84" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="B84" s="70"/>
-      <c r="C84" s="78"/>
-      <c r="D84" s="78"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="56"/>
+      <c r="D84" s="56"/>
       <c r="E84" s="46">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="81" t="s">
+      <c r="C85" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="D85" s="81"/>
+      <c r="D85" s="54"/>
       <c r="E85" s="48">
         <f>(E21+E79)-SUM(E80:E84)</f>
         <v>1447</v>
@@ -7970,69 +7967,69 @@
       <c r="E87" s="50"/>
     </row>
     <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="82" t="s">
+      <c r="A88" s="61" t="s">
         <v>114</v>
       </c>
-      <c r="B88" s="82"/>
-      <c r="C88" s="82"/>
-      <c r="D88" s="82"/>
-      <c r="E88" s="82"/>
+      <c r="B88" s="61"/>
+      <c r="C88" s="61"/>
+      <c r="D88" s="61"/>
+      <c r="E88" s="61"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="67" t="s">
+      <c r="A89" s="62" t="s">
         <v>84</v>
       </c>
-      <c r="B89" s="67"/>
-      <c r="C89" s="67" t="s">
+      <c r="B89" s="62"/>
+      <c r="C89" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="67"/>
+      <c r="D89" s="62"/>
       <c r="E89" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="69" t="s">
+      <c r="A90" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="B90" s="69"/>
-      <c r="C90" s="78"/>
-      <c r="D90" s="78"/>
+      <c r="B90" s="55"/>
+      <c r="C90" s="56"/>
+      <c r="D90" s="56"/>
       <c r="E90" s="48">
         <f>E85</f>
         <v>1447</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="70" t="s">
+      <c r="A91" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="70"/>
-      <c r="C91" s="72" t="s">
+      <c r="B91" s="57"/>
+      <c r="C91" s="58" t="s">
         <v>124</v>
       </c>
-      <c r="D91" s="72"/>
+      <c r="D91" s="58"/>
       <c r="E91" s="46">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="57" t="s">
         <v>96</v>
       </c>
-      <c r="B92" s="70"/>
-      <c r="C92" s="78"/>
-      <c r="D92" s="78"/>
+      <c r="B92" s="57"/>
+      <c r="C92" s="56"/>
+      <c r="D92" s="56"/>
       <c r="E92" s="46">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="81" t="s">
+      <c r="C93" s="54" t="s">
         <v>97</v>
       </c>
-      <c r="D93" s="81"/>
+      <c r="D93" s="54"/>
       <c r="E93" s="48">
         <f>(E27+E90)-SUM(E91:E92)</f>
         <v>2761</v>
@@ -11783,14 +11780,46 @@
       <c r="B1029" s="25"/>
     </row>
   </sheetData>
-  <mergeCells count="56">
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
+  <mergeCells count="57">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A36:C37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="A71:B73"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
     <mergeCell ref="C80:D80"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="A88:E88"/>
@@ -11801,45 +11830,14 @@
     <mergeCell ref="C83:D83"/>
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="C84:D84"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A71:B73"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="A36:C37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A80:B83"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E70">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7C3833-F576-EE46-BAAB-D4C92C9E45F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B0DF77-6E2B-194F-AF46-B898235432E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
     <sheet name="July 2026- September 2026" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -294,9 +293,6 @@
     <t>Monthly Total</t>
   </si>
   <si>
-    <t>Debts Or Credits For the Comming April 20th - May 19th 2026</t>
-  </si>
-  <si>
     <t>Principal</t>
   </si>
   <si>
@@ -374,9 +370,6 @@
     </r>
   </si>
   <si>
-    <t>Debts Or Credits For the Coming May 20th - June 17th 2026</t>
-  </si>
-  <si>
     <t>Balance Brought Forward From April 2026</t>
   </si>
   <si>
@@ -394,9 +387,6 @@
    ~ UNISEX MAGIC FOR ALL ICONS UT (SHORT SLEEVE GRAPHIC T-SHIRT) 484758 3XL - $99</t>
   </si>
   <si>
-    <t>Debts Or Credits For the Comming June 18th - July 19th 2026</t>
-  </si>
-  <si>
     <t>Balance Brought Forward From May 2026</t>
   </si>
   <si>
@@ -418,19 +408,10 @@
     <t>Fixed Expense For the Year 2026 July - September 2026</t>
   </si>
   <si>
-    <t>Debts Or Credits For the Comming July 20th - August 19th 2026</t>
-  </si>
-  <si>
     <t>Blance Brough Forward From June 2026</t>
   </si>
   <si>
-    <t>Debts Or Credits For the Coming August 20th - September 17th 2026</t>
-  </si>
-  <si>
     <t>Balance Brought Forward From July 2026</t>
-  </si>
-  <si>
-    <t>Debts Or Credits For the Comming September 18th - October 19th 2026</t>
   </si>
   <si>
     <t>Balance Brought Forward From August 2026</t>
@@ -594,6 +575,15 @@
     <t>Cancel hair cut for this current month.</t>
   </si>
   <si>
+    <t>06th Aug 2026</t>
+  </si>
+  <si>
+    <t>Borrow $100</t>
+  </si>
+  <si>
+    <t>~ Payback $100 to Mom</t>
+  </si>
+  <si>
     <t>~ Food
 ~ Snack And Drinks
    ~ Ok Store 20/07 - $15
@@ -607,23 +597,33 @@
    ~ Ustore 27/07 - $24.9
    ~ OK Store 29/07 - $28.5
    ~ Buy a coke at Kwai Chung Eldery Hospital 05/08 - $6.5
-   ~ Best Mart 360 05/08 - $26.9</t>
+   ~ Best Mart 360 05/08 - $26.9
+   ~ Ustore 09/08 - $24.9</t>
   </si>
   <si>
     <t>~ OK Store buy additional 1 packet cigarette 20/07 - $78
 ~ Additional transport fees for e-cigarette 20/07 - $40
-~ Microsoft Office 365 1 year subscribtion 30/07 - $299
+~ HKTVmall - Microsoft Office 365 1 year subscribtion 30/07 - $299
 ~ Round Trip to Kowloon East Hospital 03/08 - $4
 ~ Round Trip to Kwai Chung Eldery Hospital 05/08 - $3.5</t>
   </si>
   <si>
-    <t>06th Aug 2026</t>
-  </si>
-  <si>
-    <t>Borrow $100</t>
-  </si>
-  <si>
-    <t>~ Payback $100 to Mom</t>
+    <t>Debts Or Expenses For the Comming April 20th - May 19th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Coming May 20th - June 17th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Comming June 18th - July 19th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Comming July 20th - August 19th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Coming August 20th - September 17th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Comming September 18th - October 19th 2026</t>
   </si>
 </sst>
 </file>
@@ -1150,44 +1150,59 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1201,43 +1216,28 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1258,17 +1258,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1282,35 +1303,14 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1629,13 +1629,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1687,7 +1687,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="9">
-        <v>103.4</v>
+        <v>78.5</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>133</v>
+        <v>108.1</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1865,13 +1865,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="80" t="s">
+      <c r="A10" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="80"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="80"/>
-      <c r="E10" s="80"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1899,10 +1899,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="81" t="s">
+      <c r="C11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="81"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1914,10 +1914,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="106" t="s">
+      <c r="C12" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="106"/>
+      <c r="D12" s="90"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1929,10 +1929,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="107" t="s">
+      <c r="C13" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="107"/>
+      <c r="D13" s="91"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1942,10 +1942,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="76"/>
+      <c r="D14" s="59"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -1955,10 +1955,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="76" t="s">
+      <c r="C15" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="76"/>
+      <c r="D15" s="59"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -1968,10 +1968,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="76"/>
+      <c r="D16" s="59"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -1983,10 +1983,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="102" t="s">
+      <c r="C17" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="102"/>
+      <c r="D17" s="92"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -1996,10 +1996,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="103" t="s">
+      <c r="C18" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="103"/>
+      <c r="D18" s="93"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2011,10 +2011,10 @@
       <c r="B19" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="104" t="s">
+      <c r="C19" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="104"/>
+      <c r="D19" s="94"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2035,13 +2035,13 @@
       <c r="B21" s="25"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="78" t="s">
+      <c r="A22" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="78"/>
-      <c r="C22" s="78"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2069,10 +2069,10 @@
       <c r="B23" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="105" t="s">
+      <c r="C23" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="105"/>
+      <c r="D23" s="95"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2084,10 +2084,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="76" t="s">
+      <c r="C24" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="76"/>
+      <c r="D24" s="59"/>
       <c r="E24" s="30">
         <v>2485</v>
       </c>
@@ -2099,10 +2099,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="76" t="s">
+      <c r="C25" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="76"/>
+      <c r="D25" s="59"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2112,10 +2112,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="101" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" s="102"/>
+      <c r="C26" s="96" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="92"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2127,10 +2127,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="103" t="s">
+      <c r="C27" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="103"/>
+      <c r="D27" s="93"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2140,10 +2140,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="90" t="s">
+      <c r="C28" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="90"/>
+      <c r="D28" s="97"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2165,13 +2165,13 @@
       <c r="B30" s="25"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="78" t="s">
+      <c r="A31" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="78"/>
-      <c r="C31" s="78"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2199,10 +2199,10 @@
       <c r="B32" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="75" t="s">
+      <c r="C32" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="75"/>
+      <c r="D32" s="61"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2214,10 +2214,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="76" t="s">
+      <c r="C33" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="76"/>
+      <c r="D33" s="59"/>
       <c r="E33" s="34">
         <v>2485</v>
       </c>
@@ -2227,10 +2227,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="76"/>
+      <c r="D34" s="59"/>
       <c r="E34" s="34">
         <v>118</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>24</v>
       </c>
       <c r="C35" s="98" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D35" s="99"/>
       <c r="E35" s="34">
@@ -2254,7 +2254,7 @@
         <v>80</v>
       </c>
       <c r="C36" s="98" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D36" s="100"/>
       <c r="E36" s="34">
@@ -2266,10 +2266,10 @@
       <c r="B37" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="101" t="s">
-        <v>126</v>
-      </c>
-      <c r="D37" s="76"/>
+      <c r="C37" s="96" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37" s="59"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2291,11 +2291,11 @@
       <c r="B39" s="25"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="77" t="s">
+      <c r="A40" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="77"/>
-      <c r="C40" s="77"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="62"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2310,18 +2310,18 @@
       <c r="D41" s="38"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="74" t="s">
+      <c r="A42" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="74"/>
-      <c r="C42" s="74"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="63"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="51" t="s">
         <v>17</v>
       </c>
       <c r="B43" s="51" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C43" s="34">
         <v>78</v>
@@ -2360,16 +2360,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="73" t="s">
+      <c r="A47" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="73"/>
-      <c r="C47" s="73"/>
+      <c r="B47" s="64"/>
+      <c r="C47" s="64"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="73"/>
-      <c r="B48" s="73"/>
-      <c r="C48" s="73"/>
+      <c r="A48" s="64"/>
+      <c r="B48" s="64"/>
+      <c r="C48" s="64"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2418,11 +2418,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="74" t="s">
+      <c r="A54" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="74"/>
-      <c r="C54" s="74"/>
+      <c r="B54" s="63"/>
+      <c r="C54" s="63"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2457,11 +2457,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="74" t="s">
+      <c r="A58" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="74"/>
-      <c r="C58" s="74"/>
+      <c r="B58" s="63"/>
+      <c r="C58" s="63"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2485,11 +2485,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="74" t="s">
+      <c r="A61" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="74"/>
-      <c r="C61" s="74"/>
+      <c r="B61" s="63"/>
+      <c r="C61" s="63"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2513,11 +2513,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="71" t="s">
+      <c r="A64" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="71"/>
-      <c r="C64" s="71"/>
+      <c r="B64" s="65"/>
+      <c r="C64" s="65"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2594,11 +2594,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="71" t="s">
+      <c r="A72" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="71"/>
-      <c r="C72" s="71"/>
+      <c r="B72" s="65"/>
+      <c r="C72" s="65"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2648,167 +2648,167 @@
       <c r="B78" s="25"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="62" t="s">
+      <c r="A79" s="66" t="s">
+        <v>130</v>
+      </c>
+      <c r="B79" s="66"/>
+      <c r="C79" s="66"/>
+      <c r="D79" s="66"/>
+      <c r="E79" s="66"/>
+    </row>
+    <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="B79" s="62"/>
-      <c r="C79" s="62"/>
-      <c r="D79" s="62"/>
-      <c r="E79" s="62"/>
-    </row>
-    <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="72" t="s">
-        <v>84</v>
-      </c>
-      <c r="B80" s="72"/>
-      <c r="C80" s="72" t="s">
+      <c r="B80" s="67"/>
+      <c r="C80" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="72"/>
+      <c r="D80" s="67"/>
       <c r="E80" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="94" t="s">
-        <v>85</v>
-      </c>
-      <c r="B81" s="94"/>
-      <c r="C81" s="57"/>
-      <c r="D81" s="57"/>
+      <c r="A81" s="101" t="s">
+        <v>84</v>
+      </c>
+      <c r="B81" s="101"/>
+      <c r="C81" s="69"/>
+      <c r="D81" s="69"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="57" t="s">
+      <c r="A82" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="57"/>
-      <c r="C82" s="95" t="s">
-        <v>86</v>
-      </c>
-      <c r="D82" s="95"/>
+      <c r="B82" s="69"/>
+      <c r="C82" s="102" t="s">
+        <v>85</v>
+      </c>
+      <c r="D82" s="102"/>
       <c r="E82" s="46">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="57"/>
-      <c r="B83" s="57"/>
-      <c r="C83" s="95" t="s">
-        <v>87</v>
-      </c>
-      <c r="D83" s="95"/>
+      <c r="A83" s="69"/>
+      <c r="B83" s="69"/>
+      <c r="C83" s="102" t="s">
+        <v>86</v>
+      </c>
+      <c r="D83" s="102"/>
       <c r="E83" s="46">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="57"/>
-      <c r="B84" s="57"/>
-      <c r="C84" s="95" t="s">
-        <v>88</v>
-      </c>
-      <c r="D84" s="95"/>
+      <c r="A84" s="69"/>
+      <c r="B84" s="69"/>
+      <c r="C84" s="102" t="s">
+        <v>87</v>
+      </c>
+      <c r="D84" s="102"/>
       <c r="E84" s="46">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="57"/>
-      <c r="B85" s="57"/>
-      <c r="C85" s="96" t="s">
-        <v>89</v>
-      </c>
-      <c r="D85" s="96"/>
+      <c r="A85" s="69"/>
+      <c r="B85" s="69"/>
+      <c r="C85" s="103" t="s">
+        <v>88</v>
+      </c>
+      <c r="D85" s="103"/>
       <c r="E85" s="46">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="57"/>
-      <c r="B86" s="57"/>
-      <c r="C86" s="69" t="s">
-        <v>90</v>
-      </c>
-      <c r="D86" s="69"/>
+      <c r="A86" s="69"/>
+      <c r="B86" s="69"/>
+      <c r="C86" s="74" t="s">
+        <v>89</v>
+      </c>
+      <c r="D86" s="74"/>
       <c r="E86" s="46">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="57"/>
-      <c r="B87" s="57"/>
-      <c r="C87" s="96" t="s">
-        <v>91</v>
-      </c>
-      <c r="D87" s="96"/>
+      <c r="A87" s="69"/>
+      <c r="B87" s="69"/>
+      <c r="C87" s="103" t="s">
+        <v>90</v>
+      </c>
+      <c r="D87" s="103"/>
       <c r="E87" s="46">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="57"/>
-      <c r="B88" s="57"/>
-      <c r="C88" s="95" t="s">
-        <v>92</v>
-      </c>
-      <c r="D88" s="95"/>
+      <c r="A88" s="69"/>
+      <c r="B88" s="69"/>
+      <c r="C88" s="102" t="s">
+        <v>91</v>
+      </c>
+      <c r="D88" s="102"/>
       <c r="E88" s="46">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="57"/>
-      <c r="B89" s="57"/>
-      <c r="C89" s="69" t="s">
-        <v>93</v>
-      </c>
-      <c r="D89" s="69"/>
+      <c r="A89" s="69"/>
+      <c r="B89" s="69"/>
+      <c r="C89" s="74" t="s">
+        <v>92</v>
+      </c>
+      <c r="D89" s="74"/>
       <c r="E89" s="46">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="57"/>
-      <c r="B90" s="57"/>
-      <c r="C90" s="69" t="s">
-        <v>94</v>
-      </c>
-      <c r="D90" s="69"/>
+      <c r="A90" s="69"/>
+      <c r="B90" s="69"/>
+      <c r="C90" s="74" t="s">
+        <v>93</v>
+      </c>
+      <c r="D90" s="74"/>
       <c r="E90" s="46">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="57"/>
-      <c r="B91" s="57"/>
-      <c r="C91" s="97" t="s">
-        <v>95</v>
-      </c>
-      <c r="D91" s="97"/>
+      <c r="A91" s="69"/>
+      <c r="B91" s="69"/>
+      <c r="C91" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="D91" s="104"/>
       <c r="E91" s="46">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="66" t="s">
-        <v>96</v>
-      </c>
-      <c r="B92" s="66"/>
-      <c r="C92" s="70"/>
-      <c r="D92" s="70"/>
+      <c r="A92" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="B92" s="70"/>
+      <c r="C92" s="75"/>
+      <c r="D92" s="75"/>
       <c r="E92" s="47">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="65" t="s">
-        <v>97</v>
-      </c>
-      <c r="D93" s="65"/>
+      <c r="C93" s="76" t="s">
+        <v>96</v>
+      </c>
+      <c r="D93" s="76"/>
       <c r="E93" s="48">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2816,113 +2816,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="62" t="s">
-        <v>98</v>
-      </c>
-      <c r="B95" s="62"/>
-      <c r="C95" s="62"/>
-      <c r="D95" s="62"/>
-      <c r="E95" s="62"/>
+      <c r="A95" s="66" t="s">
+        <v>131</v>
+      </c>
+      <c r="B95" s="66"/>
+      <c r="C95" s="66"/>
+      <c r="D95" s="66"/>
+      <c r="E95" s="66"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="62" t="s">
-        <v>84</v>
-      </c>
-      <c r="B96" s="62"/>
-      <c r="C96" s="62" t="s">
+      <c r="A96" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="B96" s="66"/>
+      <c r="C96" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="62"/>
+      <c r="D96" s="66"/>
       <c r="E96" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="55" t="s">
-        <v>99</v>
-      </c>
-      <c r="B97" s="55"/>
-      <c r="C97" s="56"/>
-      <c r="D97" s="56"/>
+      <c r="A97" s="68" t="s">
+        <v>97</v>
+      </c>
+      <c r="B97" s="68"/>
+      <c r="C97" s="77"/>
+      <c r="D97" s="77"/>
       <c r="E97" s="48">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="57" t="s">
+      <c r="A98" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="57"/>
-      <c r="C98" s="68" t="s">
-        <v>100</v>
-      </c>
-      <c r="D98" s="68"/>
+      <c r="B98" s="69"/>
+      <c r="C98" s="73" t="s">
+        <v>98</v>
+      </c>
+      <c r="D98" s="73"/>
       <c r="E98" s="49">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="57"/>
-      <c r="B99" s="57"/>
-      <c r="C99" s="58" t="s">
-        <v>119</v>
-      </c>
-      <c r="D99" s="58"/>
+      <c r="A99" s="69"/>
+      <c r="B99" s="69"/>
+      <c r="C99" s="71" t="s">
+        <v>113</v>
+      </c>
+      <c r="D99" s="71"/>
       <c r="E99" s="49">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="57"/>
-      <c r="B100" s="57"/>
-      <c r="C100" s="58" t="s">
-        <v>117</v>
-      </c>
-      <c r="D100" s="58"/>
+      <c r="A100" s="69"/>
+      <c r="B100" s="69"/>
+      <c r="C100" s="71" t="s">
+        <v>111</v>
+      </c>
+      <c r="D100" s="71"/>
       <c r="E100" s="49">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="57"/>
-      <c r="B101" s="57"/>
-      <c r="C101" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="D101" s="58"/>
+      <c r="A101" s="69"/>
+      <c r="B101" s="69"/>
+      <c r="C101" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="D101" s="71"/>
       <c r="E101" s="49">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="57"/>
-      <c r="B102" s="57"/>
-      <c r="C102" s="63" t="s">
-        <v>101</v>
-      </c>
-      <c r="D102" s="93"/>
+      <c r="A102" s="69"/>
+      <c r="B102" s="69"/>
+      <c r="C102" s="82" t="s">
+        <v>99</v>
+      </c>
+      <c r="D102" s="105"/>
       <c r="E102" s="49">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="57" t="s">
-        <v>96</v>
-      </c>
-      <c r="B103" s="57"/>
-      <c r="C103" s="56"/>
-      <c r="D103" s="56"/>
+      <c r="A103" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="B103" s="69"/>
+      <c r="C103" s="77"/>
+      <c r="D103" s="77"/>
       <c r="E103" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="D104" s="54"/>
+      <c r="C104" s="80" t="s">
+        <v>96</v>
+      </c>
+      <c r="D104" s="80"/>
       <c r="E104" s="48">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2943,34 +2943,34 @@
       <c r="E106" s="50"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="61" t="s">
-        <v>102</v>
-      </c>
-      <c r="B107" s="61"/>
-      <c r="C107" s="61"/>
-      <c r="D107" s="61"/>
-      <c r="E107" s="61"/>
+      <c r="A107" s="81" t="s">
+        <v>132</v>
+      </c>
+      <c r="B107" s="81"/>
+      <c r="C107" s="81"/>
+      <c r="D107" s="81"/>
+      <c r="E107" s="81"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="62" t="s">
-        <v>84</v>
-      </c>
-      <c r="B108" s="62"/>
-      <c r="C108" s="62" t="s">
+      <c r="A108" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="B108" s="66"/>
+      <c r="C108" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="62"/>
+      <c r="D108" s="66"/>
       <c r="E108" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="55" t="s">
-        <v>103</v>
-      </c>
-      <c r="B109" s="55"/>
-      <c r="C109" s="56"/>
-      <c r="D109" s="56"/>
+      <c r="A109" s="68" t="s">
+        <v>100</v>
+      </c>
+      <c r="B109" s="68"/>
+      <c r="C109" s="77"/>
+      <c r="D109" s="77"/>
       <c r="E109" s="48">
         <f>E104</f>
         <v>228.5</v>
@@ -2981,10 +2981,10 @@
         <v>67</v>
       </c>
       <c r="B110" s="85"/>
-      <c r="C110" s="90" t="s">
-        <v>123</v>
-      </c>
-      <c r="D110" s="90"/>
+      <c r="C110" s="97" t="s">
+        <v>117</v>
+      </c>
+      <c r="D110" s="97"/>
       <c r="E110" s="46">
         <v>870.3</v>
       </c>
@@ -2992,10 +2992,10 @@
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="86"/>
       <c r="B111" s="87"/>
-      <c r="C111" s="91" t="s">
-        <v>122</v>
-      </c>
-      <c r="D111" s="92"/>
+      <c r="C111" s="106" t="s">
+        <v>116</v>
+      </c>
+      <c r="D111" s="107"/>
       <c r="E111" s="46">
         <v>1428</v>
       </c>
@@ -3003,31 +3003,31 @@
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="88"/>
       <c r="B112" s="89"/>
-      <c r="C112" s="63" t="s">
-        <v>127</v>
-      </c>
-      <c r="D112" s="93"/>
+      <c r="C112" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="D112" s="105"/>
       <c r="E112" s="46">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="57" t="s">
-        <v>96</v>
-      </c>
-      <c r="B113" s="57"/>
-      <c r="C113" s="56"/>
-      <c r="D113" s="56"/>
+      <c r="A113" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="B113" s="69"/>
+      <c r="C113" s="77"/>
+      <c r="D113" s="77"/>
       <c r="E113" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="D114" s="54"/>
+      <c r="C114" s="80" t="s">
+        <v>96</v>
+      </c>
+      <c r="D114" s="80"/>
       <c r="E114" s="48">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6779,42 +6779,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6828,35 +6821,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6896,13 +6896,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="79" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="A1" s="54" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="C4" s="9">
         <f>'April 2026 - June 2026'!C4</f>
-        <v>103.4</v>
+        <v>78.5</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>133</v>
+        <v>108.1</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7137,13 +7137,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="80" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" s="80"/>
-      <c r="C10" s="80"/>
-      <c r="D10" s="80"/>
-      <c r="E10" s="80"/>
+      <c r="A10" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7171,55 +7171,55 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="81" t="s">
+      <c r="C11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="81"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="52" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B12" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="82" t="s">
+      <c r="C12" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="82"/>
+      <c r="D12" s="57"/>
       <c r="E12" s="53">
         <v>2485</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="76" t="s">
-        <v>130</v>
-      </c>
-      <c r="D13" s="76"/>
+      <c r="C13" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="59"/>
       <c r="E13" s="30">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="51" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="83" t="s">
-        <v>134</v>
-      </c>
-      <c r="D14" s="76"/>
+      <c r="C14" s="58" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="59"/>
       <c r="E14" s="30">
         <v>100</v>
       </c>
@@ -7240,13 +7240,13 @@
       <c r="B16" s="25"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="78" t="s">
-        <v>107</v>
-      </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
+      <c r="A17" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7274,10 +7274,10 @@
       <c r="B18" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="75" t="s">
+      <c r="C18" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="75"/>
+      <c r="D18" s="61"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7289,10 +7289,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="76" t="s">
+      <c r="C19" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="76"/>
+      <c r="D19" s="59"/>
       <c r="E19" s="30">
         <v>2485</v>
       </c>
@@ -7300,8 +7300,8 @@
     <row r="20" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="76"/>
-      <c r="D20" s="76"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
       <c r="E20" s="30">
         <v>0</v>
       </c>
@@ -7323,13 +7323,13 @@
       <c r="B22" s="25"/>
     </row>
     <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="78" t="s">
-        <v>108</v>
-      </c>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
+      <c r="A23" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
@@ -7357,25 +7357,25 @@
       <c r="B24" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="75" t="s">
+      <c r="C24" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="75"/>
+      <c r="D24" s="61"/>
       <c r="E24" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="76" t="s">
+      <c r="C25" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="76"/>
+      <c r="D25" s="59"/>
       <c r="E25" s="34">
         <v>2485</v>
       </c>
@@ -7383,8 +7383,8 @@
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
       <c r="E26" s="30">
         <v>0</v>
       </c>
@@ -7406,11 +7406,11 @@
       <c r="B28" s="25"/>
     </row>
     <row r="29" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="77" t="s">
-        <v>109</v>
-      </c>
-      <c r="B29" s="77"/>
-      <c r="C29" s="77"/>
+      <c r="A29" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="B29" s="62"/>
+      <c r="C29" s="62"/>
     </row>
     <row r="30" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -7425,18 +7425,18 @@
       <c r="D30" s="38"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="74" t="s">
+      <c r="A31" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="74"/>
-      <c r="C31" s="74"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
     </row>
     <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="51" t="s">
         <v>17</v>
       </c>
       <c r="B32" s="51" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="C32" s="34">
         <v>78</v>
@@ -7475,16 +7475,16 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="73" t="s">
+      <c r="A36" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="73"/>
-      <c r="C36" s="73"/>
+      <c r="B36" s="64"/>
+      <c r="C36" s="64"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="73"/>
-      <c r="B37" s="73"/>
-      <c r="C37" s="73"/>
+      <c r="A37" s="64"/>
+      <c r="B37" s="64"/>
+      <c r="C37" s="64"/>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
@@ -7533,11 +7533,11 @@
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="74" t="s">
+      <c r="A43" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="74"/>
-      <c r="C43" s="74"/>
+      <c r="B43" s="63"/>
+      <c r="C43" s="63"/>
     </row>
     <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
@@ -7572,11 +7572,11 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="74" t="s">
+      <c r="A47" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="74"/>
-      <c r="C47" s="74"/>
+      <c r="B47" s="63"/>
+      <c r="C47" s="63"/>
     </row>
     <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
@@ -7600,11 +7600,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="74" t="s">
+      <c r="A50" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="74"/>
-      <c r="C50" s="74"/>
+      <c r="B50" s="63"/>
+      <c r="C50" s="63"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7628,11 +7628,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="71" t="s">
+      <c r="A53" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="71"/>
-      <c r="C53" s="71"/>
+      <c r="B53" s="65"/>
+      <c r="C53" s="65"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="17" t="s">
@@ -7709,11 +7709,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="71" t="s">
+      <c r="A61" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="B61" s="71"/>
-      <c r="C61" s="71"/>
+      <c r="B61" s="65"/>
+      <c r="C61" s="65"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
@@ -7763,129 +7763,129 @@
       <c r="B67" s="25"/>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="62" t="s">
-        <v>110</v>
-      </c>
-      <c r="B68" s="62"/>
-      <c r="C68" s="62"/>
-      <c r="D68" s="62"/>
-      <c r="E68" s="62"/>
+      <c r="A68" s="66" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="66"/>
+      <c r="C68" s="66"/>
+      <c r="D68" s="66"/>
+      <c r="E68" s="66"/>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="72" t="s">
-        <v>84</v>
-      </c>
-      <c r="B69" s="72"/>
-      <c r="C69" s="72" t="s">
+      <c r="A69" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="B69" s="67"/>
+      <c r="C69" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D69" s="72"/>
+      <c r="D69" s="67"/>
       <c r="E69" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="B70" s="55"/>
-      <c r="C70" s="57"/>
-      <c r="D70" s="57"/>
+      <c r="A70" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="B70" s="68"/>
+      <c r="C70" s="69"/>
+      <c r="D70" s="69"/>
       <c r="E70" s="48">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="66" t="s">
+      <c r="A71" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="66"/>
-      <c r="C71" s="58" t="s">
-        <v>128</v>
-      </c>
-      <c r="D71" s="58"/>
+      <c r="B71" s="70"/>
+      <c r="C71" s="71" t="s">
+        <v>122</v>
+      </c>
+      <c r="D71" s="71"/>
       <c r="E71" s="46">
         <v>600</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="224" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="66"/>
-      <c r="B72" s="66"/>
-      <c r="C72" s="67" t="s">
-        <v>131</v>
-      </c>
-      <c r="D72" s="68"/>
+    <row r="72" spans="1:8" ht="251" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="70"/>
+      <c r="B72" s="70"/>
+      <c r="C72" s="72" t="s">
+        <v>128</v>
+      </c>
+      <c r="D72" s="73"/>
       <c r="E72" s="46">
-        <v>422.2</v>
+        <v>447.1</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="91" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="66"/>
-      <c r="B73" s="66"/>
-      <c r="C73" s="67" t="s">
-        <v>132</v>
-      </c>
-      <c r="D73" s="69"/>
+      <c r="A73" s="70"/>
+      <c r="B73" s="70"/>
+      <c r="C73" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="D73" s="74"/>
       <c r="E73" s="46">
         <v>424.5</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="66" t="s">
-        <v>96</v>
-      </c>
-      <c r="B74" s="66"/>
-      <c r="C74" s="70"/>
-      <c r="D74" s="70"/>
+      <c r="A74" s="70" t="s">
+        <v>95</v>
+      </c>
+      <c r="B74" s="70"/>
+      <c r="C74" s="75"/>
+      <c r="D74" s="75"/>
       <c r="E74" s="47">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C75" s="65" t="s">
-        <v>97</v>
-      </c>
-      <c r="D75" s="65"/>
+      <c r="C75" s="76" t="s">
+        <v>96</v>
+      </c>
+      <c r="D75" s="76"/>
       <c r="E75" s="48">
         <f>(E15+E70)-SUM(E71:E74)</f>
-        <v>133</v>
+        <v>108.09999999999991</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="62" t="s">
-        <v>112</v>
-      </c>
-      <c r="B77" s="62"/>
-      <c r="C77" s="62"/>
-      <c r="D77" s="62"/>
-      <c r="E77" s="62"/>
+      <c r="A77" s="66" t="s">
+        <v>134</v>
+      </c>
+      <c r="B77" s="66"/>
+      <c r="C77" s="66"/>
+      <c r="D77" s="66"/>
+      <c r="E77" s="66"/>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="62" t="s">
-        <v>84</v>
-      </c>
-      <c r="B78" s="62"/>
-      <c r="C78" s="62" t="s">
+      <c r="A78" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="B78" s="66"/>
+      <c r="C78" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="D78" s="62"/>
+      <c r="D78" s="66"/>
       <c r="E78" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="B79" s="55"/>
-      <c r="C79" s="56"/>
-      <c r="D79" s="56"/>
+      <c r="A79" s="68" t="s">
+        <v>108</v>
+      </c>
+      <c r="B79" s="68"/>
+      <c r="C79" s="77"/>
+      <c r="D79" s="77"/>
       <c r="E79" s="48">
         <f>E75</f>
-        <v>133</v>
+        <v>108.09999999999991</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7893,10 +7893,10 @@
         <v>67</v>
       </c>
       <c r="B80" s="85"/>
-      <c r="C80" s="59" t="s">
-        <v>135</v>
-      </c>
-      <c r="D80" s="60"/>
+      <c r="C80" s="78" t="s">
+        <v>127</v>
+      </c>
+      <c r="D80" s="79"/>
       <c r="E80" s="49">
         <v>0</v>
       </c>
@@ -7904,10 +7904,10 @@
     <row r="81" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="86"/>
       <c r="B81" s="87"/>
-      <c r="C81" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="D81" s="58"/>
+      <c r="C81" s="71" t="s">
+        <v>118</v>
+      </c>
+      <c r="D81" s="71"/>
       <c r="E81" s="49">
         <v>0</v>
       </c>
@@ -7915,8 +7915,8 @@
     <row r="82" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="86"/>
       <c r="B82" s="87"/>
-      <c r="C82" s="63"/>
-      <c r="D82" s="64"/>
+      <c r="C82" s="82"/>
+      <c r="D82" s="83"/>
       <c r="E82" s="49">
         <v>0</v>
       </c>
@@ -7924,32 +7924,32 @@
     <row r="83" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="88"/>
       <c r="B83" s="89"/>
-      <c r="C83" s="64"/>
-      <c r="D83" s="64"/>
+      <c r="C83" s="83"/>
+      <c r="D83" s="83"/>
       <c r="E83" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="57" t="s">
-        <v>96</v>
-      </c>
-      <c r="B84" s="57"/>
-      <c r="C84" s="56"/>
-      <c r="D84" s="56"/>
+      <c r="A84" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="B84" s="69"/>
+      <c r="C84" s="77"/>
+      <c r="D84" s="77"/>
       <c r="E84" s="46">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="D85" s="54"/>
+      <c r="C85" s="80" t="s">
+        <v>96</v>
+      </c>
+      <c r="D85" s="80"/>
       <c r="E85" s="48">
         <f>(E21+E79)-SUM(E80:E84)</f>
-        <v>1447</v>
+        <v>1422.1</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7967,72 +7967,72 @@
       <c r="E87" s="50"/>
     </row>
     <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="61" t="s">
-        <v>114</v>
-      </c>
-      <c r="B88" s="61"/>
-      <c r="C88" s="61"/>
-      <c r="D88" s="61"/>
-      <c r="E88" s="61"/>
+      <c r="A88" s="81" t="s">
+        <v>135</v>
+      </c>
+      <c r="B88" s="81"/>
+      <c r="C88" s="81"/>
+      <c r="D88" s="81"/>
+      <c r="E88" s="81"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="62" t="s">
-        <v>84</v>
-      </c>
-      <c r="B89" s="62"/>
-      <c r="C89" s="62" t="s">
+      <c r="A89" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="B89" s="66"/>
+      <c r="C89" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="62"/>
+      <c r="D89" s="66"/>
       <c r="E89" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="55" t="s">
-        <v>115</v>
-      </c>
-      <c r="B90" s="55"/>
-      <c r="C90" s="56"/>
-      <c r="D90" s="56"/>
+      <c r="A90" s="68" t="s">
+        <v>109</v>
+      </c>
+      <c r="B90" s="68"/>
+      <c r="C90" s="77"/>
+      <c r="D90" s="77"/>
       <c r="E90" s="48">
         <f>E85</f>
-        <v>1447</v>
+        <v>1422.1</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="57" t="s">
+      <c r="A91" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="57"/>
-      <c r="C91" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="D91" s="58"/>
+      <c r="B91" s="69"/>
+      <c r="C91" s="71" t="s">
+        <v>118</v>
+      </c>
+      <c r="D91" s="71"/>
       <c r="E91" s="46">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="57" t="s">
-        <v>96</v>
-      </c>
-      <c r="B92" s="57"/>
-      <c r="C92" s="56"/>
-      <c r="D92" s="56"/>
+      <c r="A92" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="B92" s="69"/>
+      <c r="C92" s="77"/>
+      <c r="D92" s="77"/>
       <c r="E92" s="46">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="D93" s="54"/>
+      <c r="C93" s="80" t="s">
+        <v>96</v>
+      </c>
+      <c r="D93" s="80"/>
       <c r="E93" s="48">
         <f>(E27+E90)-SUM(E91:E92)</f>
-        <v>2761</v>
+        <v>2736.1</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11781,45 +11781,13 @@
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A36:C37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="A71:B73"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
     <mergeCell ref="C80:D80"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="A88:E88"/>
@@ -11831,13 +11799,45 @@
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="C84:D84"/>
     <mergeCell ref="A80:B83"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="A71:B73"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="A36:C37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E70">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
@@ -11858,13 +11858,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B0DF77-6E2B-194F-AF46-B898235432E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFFD06C-959E-B548-8952-E56EA2455CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -601,29 +601,30 @@
    ~ Ustore 09/08 - $24.9</t>
   </si>
   <si>
+    <t>Debts Or Expenses For the Comming April 20th - May 19th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Coming May 20th - June 17th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Comming June 18th - July 19th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Comming July 20th - August 19th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Coming August 20th - September 17th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Comming September 18th - October 19th 2026</t>
+  </si>
+  <si>
     <t>~ OK Store buy additional 1 packet cigarette 20/07 - $78
 ~ Additional transport fees for e-cigarette 20/07 - $40
 ~ HKTVmall - Microsoft Office 365 1 year subscribtion 30/07 - $299
 ~ Round Trip to Kowloon East Hospital 03/08 - $4
-~ Round Trip to Kwai Chung Eldery Hospital 05/08 - $3.5</t>
-  </si>
-  <si>
-    <t>Debts Or Expenses For the Comming April 20th - May 19th 2026</t>
-  </si>
-  <si>
-    <t>Debts Or Expenses For the Coming May 20th - June 17th 2026</t>
-  </si>
-  <si>
-    <t>Debts Or Expenses For the Comming June 18th - July 19th 2026</t>
-  </si>
-  <si>
-    <t>Debts Or Expenses For the Comming July 20th - August 19th 2026</t>
-  </si>
-  <si>
-    <t>Debts Or Expenses For the Coming August 20th - September 17th 2026</t>
-  </si>
-  <si>
-    <t>Debts Or Expenses For the Comming September 18th - October 19th 2026</t>
+~ Round Trip to Kwai Chung Eldery Hospital 05/08 - $3.5
+~ Round Trip to Kwai Chung Eldery Hospital 16/08 - $3.5</t>
   </si>
 </sst>
 </file>
@@ -1780,7 +1781,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="9">
-        <v>17.3</v>
+        <v>13.8</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -1812,7 +1813,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>108.1</v>
+        <v>104.6</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -2649,7 +2650,7 @@
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="66" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B79" s="66"/>
       <c r="C79" s="66"/>
@@ -2817,7 +2818,7 @@
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="66" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B95" s="66"/>
       <c r="C95" s="66"/>
@@ -2944,7 +2945,7 @@
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="81" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B107" s="81"/>
       <c r="C107" s="81"/>
@@ -7052,7 +7053,7 @@
       </c>
       <c r="C7" s="9">
         <f>'April 2026 - June 2026'!C7</f>
-        <v>17.3</v>
+        <v>13.8</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -7084,7 +7085,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>108.1</v>
+        <v>104.6</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7764,7 +7765,7 @@
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="66" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B68" s="66"/>
       <c r="C68" s="66"/>
@@ -7820,15 +7821,15 @@
         <v>447.1</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="91" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="114" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="70"/>
       <c r="B73" s="70"/>
       <c r="C73" s="72" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D73" s="74"/>
       <c r="E73" s="46">
-        <v>424.5</v>
+        <v>428</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7850,13 +7851,13 @@
       <c r="D75" s="76"/>
       <c r="E75" s="48">
         <f>(E15+E70)-SUM(E71:E74)</f>
-        <v>108.09999999999991</v>
+        <v>104.59999999999991</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B77" s="66"/>
       <c r="C77" s="66"/>
@@ -7885,7 +7886,7 @@
       <c r="D79" s="77"/>
       <c r="E79" s="48">
         <f>E75</f>
-        <v>108.09999999999991</v>
+        <v>104.59999999999991</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7949,7 +7950,7 @@
       <c r="D85" s="80"/>
       <c r="E85" s="48">
         <f>(E21+E79)-SUM(E80:E84)</f>
-        <v>1422.1</v>
+        <v>1418.6</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7968,7 +7969,7 @@
     </row>
     <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="81" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B88" s="81"/>
       <c r="C88" s="81"/>
@@ -7997,7 +7998,7 @@
       <c r="D90" s="77"/>
       <c r="E90" s="48">
         <f>E85</f>
-        <v>1422.1</v>
+        <v>1418.6</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -8032,7 +8033,7 @@
       <c r="D93" s="80"/>
       <c r="E93" s="48">
         <f>(E27+E90)-SUM(E91:E92)</f>
-        <v>2736.1</v>
+        <v>2732.6</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFFD06C-959E-B548-8952-E56EA2455CB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167E12DA-65A3-BF45-A821-29924DE54012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="137">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -619,12 +619,17 @@
     <t>Debts Or Expenses For the Comming September 18th - October 19th 2026</t>
   </si>
   <si>
+    <t>~ Additional transport fees for e-cigarette 20/08 - $40
+~ Round Trip to Kowloon East Hospital 31/08 - $4</t>
+  </si>
+  <si>
     <t>~ OK Store buy additional 1 packet cigarette 20/07 - $78
 ~ Additional transport fees for e-cigarette 20/07 - $40
 ~ HKTVmall - Microsoft Office 365 1 year subscribtion 30/07 - $299
 ~ Round Trip to Kowloon East Hospital 03/08 - $4
 ~ Round Trip to Kwai Chung Eldery Hospital 05/08 - $3.5
-~ Round Trip to Kwai Chung Eldery Hospital 16/08 - $3.5</t>
+~ Round Trip to Kwai Chung Eldery Hospital 16/08 - $3.5
+~ OK Store buy additional 1 packet cigarette 18/08 - $78</t>
   </si>
 </sst>
 </file>
@@ -1688,7 +1693,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="9">
-        <v>78.5</v>
+        <v>0.5</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -1813,7 +1818,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>104.6</v>
+        <v>26.6</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -6957,7 +6962,7 @@
       </c>
       <c r="C4" s="9">
         <f>'April 2026 - June 2026'!C4</f>
-        <v>78.5</v>
+        <v>0.5</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -7085,7 +7090,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>104.6</v>
+        <v>26.6</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7821,15 +7826,15 @@
         <v>447.1</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="114" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="133" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="70"/>
       <c r="B73" s="70"/>
       <c r="C73" s="72" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D73" s="74"/>
       <c r="E73" s="46">
-        <v>428</v>
+        <v>506</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7851,7 +7856,7 @@
       <c r="D75" s="76"/>
       <c r="E75" s="48">
         <f>(E15+E70)-SUM(E71:E74)</f>
-        <v>104.59999999999991</v>
+        <v>26.599999999999909</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -7886,10 +7891,10 @@
       <c r="D79" s="77"/>
       <c r="E79" s="48">
         <f>E75</f>
-        <v>104.59999999999991</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26.599999999999909</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="84" t="s">
         <v>67</v>
       </c>
@@ -7913,16 +7918,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="86"/>
       <c r="B82" s="87"/>
-      <c r="C82" s="82"/>
+      <c r="C82" s="82" t="s">
+        <v>135</v>
+      </c>
       <c r="D82" s="83"/>
       <c r="E82" s="49">
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="88"/>
       <c r="B83" s="89"/>
       <c r="C83" s="83"/>
@@ -7950,7 +7957,7 @@
       <c r="D85" s="80"/>
       <c r="E85" s="48">
         <f>(E21+E79)-SUM(E80:E84)</f>
-        <v>1418.6</v>
+        <v>1340.6</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7998,7 +8005,7 @@
       <c r="D90" s="77"/>
       <c r="E90" s="48">
         <f>E85</f>
-        <v>1418.6</v>
+        <v>1340.6</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
@@ -8033,7 +8040,7 @@
       <c r="D93" s="80"/>
       <c r="E93" s="48">
         <f>(E27+E90)-SUM(E91:E92)</f>
-        <v>2732.6</v>
+        <v>2654.6</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167E12DA-65A3-BF45-A821-29924DE54012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E465D28D-F29C-7446-9EFC-EF5BD2ACC7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="140">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -578,10 +578,45 @@
     <t>06th Aug 2026</t>
   </si>
   <si>
-    <t>Borrow $100</t>
-  </si>
-  <si>
-    <t>~ Payback $100 to Mom</t>
+    <t>Debts Or Expenses For the Comming April 20th - May 19th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Coming May 20th - June 17th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Comming June 18th - July 19th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Comming July 20th - August 19th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Coming August 20th - September 17th 2026</t>
+  </si>
+  <si>
+    <t>Debts Or Expenses For the Comming September 18th - October 19th 2026</t>
+  </si>
+  <si>
+    <t>~ Additional transport fees for e-cigarette 20/08 - $40
+~ Round Trip to Kowloon East Hospital 31/08 - $4</t>
+  </si>
+  <si>
+    <t>~ OK Store buy additional 1 packet cigarette 20/07 - $78
+~ Additional transport fees for e-cigarette 20/07 - $40
+~ HKTVmall - Microsoft Office 365 1 year subscribtion 30/07 - $299
+~ Round Trip to Kowloon East Hospital 03/08 - $4
+~ Round Trip to Kwai Chung Eldery Hospital 05/08 - $3.5
+~ Round Trip to Kwai Chung Eldery Hospital 16/08 - $3.5
+~ OK Store buy additional 1 packet cigarette 18/08 - $78</t>
+  </si>
+  <si>
+    <t>20th August 2026</t>
+  </si>
+  <si>
+    <t>20th September 2026</t>
+  </si>
+  <si>
+    <t>1. Borrow $100
+2. Use Mother Credit Card for shopping HKTVmall. $670.4</t>
   </si>
   <si>
     <t>~ Food
@@ -598,38 +633,17 @@
    ~ OK Store 29/07 - $28.5
    ~ Buy a coke at Kwai Chung Eldery Hospital 05/08 - $6.5
    ~ Best Mart 360 05/08 - $26.9
-   ~ Ustore 09/08 - $24.9</t>
-  </si>
-  <si>
-    <t>Debts Or Expenses For the Comming April 20th - May 19th 2026</t>
-  </si>
-  <si>
-    <t>Debts Or Expenses For the Coming May 20th - June 17th 2026</t>
-  </si>
-  <si>
-    <t>Debts Or Expenses For the Comming June 18th - July 19th 2026</t>
-  </si>
-  <si>
-    <t>Debts Or Expenses For the Comming July 20th - August 19th 2026</t>
-  </si>
-  <si>
-    <t>Debts Or Expenses For the Coming August 20th - September 17th 2026</t>
-  </si>
-  <si>
-    <t>Debts Or Expenses For the Comming September 18th - October 19th 2026</t>
-  </si>
-  <si>
-    <t>~ Additional transport fees for e-cigarette 20/08 - $40
-~ Round Trip to Kowloon East Hospital 31/08 - $4</t>
-  </si>
-  <si>
-    <t>~ OK Store buy additional 1 packet cigarette 20/07 - $78
-~ Additional transport fees for e-cigarette 20/07 - $40
-~ HKTVmall - Microsoft Office 365 1 year subscribtion 30/07 - $299
-~ Round Trip to Kowloon East Hospital 03/08 - $4
-~ Round Trip to Kwai Chung Eldery Hospital 05/08 - $3.5
-~ Round Trip to Kwai Chung Eldery Hospital 16/08 - $3.5
-~ OK Store buy additional 1 packet cigarette 18/08 - $78</t>
+   ~ Ustore 09/08 - $24.9
+   ~ HKTVmall 18/08 - $670.4</t>
+  </si>
+  <si>
+    <t>Partial Food And Snack Prepaid on the Previous Month
+~ Food
+~ Snack And Drinks</t>
+  </si>
+  <si>
+    <t>~ Payback $100 to Mom
+~ Payback $670.4 to Mom (HKTVmall Online Shopping)</t>
   </si>
 </sst>
 </file>
@@ -995,7 +1009,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1156,95 +1170,17 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1264,29 +1200,74 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1297,25 +1278,55 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1635,13 +1646,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1871,13 +1882,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1905,10 +1916,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="56"/>
+      <c r="D11" s="99"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1920,10 +1931,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="90" t="s">
+      <c r="C12" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="90"/>
+      <c r="D12" s="100"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1935,10 +1946,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="91" t="s">
+      <c r="C13" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="91"/>
+      <c r="D13" s="101"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1948,10 +1959,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="59"/>
+      <c r="D14" s="86"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -1961,10 +1972,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="59"/>
+      <c r="D15" s="86"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -1974,10 +1985,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="59"/>
+      <c r="D16" s="86"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -1989,10 +2000,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="92"/>
+      <c r="D17" s="91"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2002,10 +2013,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="93" t="s">
+      <c r="C18" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="93"/>
+      <c r="D18" s="92"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2017,10 +2028,10 @@
       <c r="B19" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="94" t="s">
+      <c r="C19" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="94"/>
+      <c r="D19" s="95"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2041,13 +2052,13 @@
       <c r="B21" s="25"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
+      <c r="B22" s="93"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2075,10 +2086,10 @@
       <c r="B23" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="95" t="s">
+      <c r="C23" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="95"/>
+      <c r="D23" s="96"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2090,10 +2101,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="59"/>
+      <c r="D24" s="86"/>
       <c r="E24" s="30">
         <v>2485</v>
       </c>
@@ -2105,10 +2116,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="59"/>
+      <c r="D25" s="86"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2118,10 +2129,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="96" t="s">
+      <c r="C26" s="90" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="92"/>
+      <c r="D26" s="91"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2133,10 +2144,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="93" t="s">
+      <c r="C27" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="93"/>
+      <c r="D27" s="92"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2146,10 +2157,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="97" t="s">
+      <c r="C28" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="97"/>
+      <c r="D28" s="64"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2171,13 +2182,13 @@
       <c r="B30" s="25"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="60" t="s">
+      <c r="A31" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="60"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2205,10 +2216,10 @@
       <c r="B32" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="61" t="s">
+      <c r="C32" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="61"/>
+      <c r="D32" s="94"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2220,10 +2231,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="59"/>
+      <c r="D33" s="86"/>
       <c r="E33" s="34">
         <v>2485</v>
       </c>
@@ -2233,10 +2244,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="59" t="s">
+      <c r="C34" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="59"/>
+      <c r="D34" s="86"/>
       <c r="E34" s="34">
         <v>118</v>
       </c>
@@ -2246,10 +2257,10 @@
       <c r="B35" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="98" t="s">
+      <c r="C35" s="87" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="99"/>
+      <c r="D35" s="88"/>
       <c r="E35" s="34">
         <v>170</v>
       </c>
@@ -2259,10 +2270,10 @@
       <c r="B36" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="98" t="s">
+      <c r="C36" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="100"/>
+      <c r="D36" s="89"/>
       <c r="E36" s="34">
         <v>800</v>
       </c>
@@ -2272,10 +2283,10 @@
       <c r="B37" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="96" t="s">
+      <c r="C37" s="90" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="59"/>
+      <c r="D37" s="86"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2297,11 +2308,11 @@
       <c r="B39" s="25"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="62" t="s">
+      <c r="A40" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="62"/>
-      <c r="C40" s="62"/>
+      <c r="B40" s="84"/>
+      <c r="C40" s="84"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2316,11 +2327,11 @@
       <c r="D41" s="38"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="63" t="s">
+      <c r="A42" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="63"/>
-      <c r="C42" s="63"/>
+      <c r="B42" s="81"/>
+      <c r="C42" s="81"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="51" t="s">
@@ -2366,16 +2377,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="64" t="s">
+      <c r="A47" s="85" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="64"/>
-      <c r="C47" s="64"/>
+      <c r="B47" s="85"/>
+      <c r="C47" s="85"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="64"/>
-      <c r="B48" s="64"/>
-      <c r="C48" s="64"/>
+      <c r="A48" s="85"/>
+      <c r="B48" s="85"/>
+      <c r="C48" s="85"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2424,11 +2435,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="63" t="s">
+      <c r="A54" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="63"/>
-      <c r="C54" s="63"/>
+      <c r="B54" s="81"/>
+      <c r="C54" s="81"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2463,11 +2474,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="63" t="s">
+      <c r="A58" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="63"/>
-      <c r="C58" s="63"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="81"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2491,11 +2502,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="63" t="s">
+      <c r="A61" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="63"/>
-      <c r="C61" s="63"/>
+      <c r="B61" s="81"/>
+      <c r="C61" s="81"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2519,11 +2530,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="65" t="s">
+      <c r="A64" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="65"/>
-      <c r="C64" s="65"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="82"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2600,11 +2611,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="65" t="s">
+      <c r="A72" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="65"/>
-      <c r="C72" s="65"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="82"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2654,167 +2665,167 @@
       <c r="B78" s="25"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="66" t="s">
-        <v>129</v>
-      </c>
-      <c r="B79" s="66"/>
-      <c r="C79" s="66"/>
-      <c r="D79" s="66"/>
-      <c r="E79" s="66"/>
+      <c r="A79" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="B79" s="70"/>
+      <c r="C79" s="70"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="67" t="s">
+      <c r="A80" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="67"/>
-      <c r="C80" s="67" t="s">
+      <c r="B80" s="83"/>
+      <c r="C80" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="67"/>
+      <c r="D80" s="83"/>
       <c r="E80" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="101" t="s">
+      <c r="A81" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="101"/>
-      <c r="C81" s="69"/>
-      <c r="D81" s="69"/>
+      <c r="B81" s="76"/>
+      <c r="C81" s="54"/>
+      <c r="D81" s="54"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="69" t="s">
+      <c r="A82" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="69"/>
-      <c r="C82" s="102" t="s">
+      <c r="B82" s="54"/>
+      <c r="C82" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="102"/>
+      <c r="D82" s="77"/>
       <c r="E82" s="46">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="69"/>
-      <c r="B83" s="69"/>
-      <c r="C83" s="102" t="s">
+      <c r="A83" s="54"/>
+      <c r="B83" s="54"/>
+      <c r="C83" s="77" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="102"/>
+      <c r="D83" s="77"/>
       <c r="E83" s="46">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="69"/>
-      <c r="B84" s="69"/>
-      <c r="C84" s="102" t="s">
+      <c r="A84" s="54"/>
+      <c r="B84" s="54"/>
+      <c r="C84" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="102"/>
+      <c r="D84" s="77"/>
       <c r="E84" s="46">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="69"/>
-      <c r="B85" s="69"/>
-      <c r="C85" s="103" t="s">
+      <c r="A85" s="54"/>
+      <c r="B85" s="54"/>
+      <c r="C85" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="103"/>
+      <c r="D85" s="78"/>
       <c r="E85" s="46">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="69"/>
-      <c r="B86" s="69"/>
-      <c r="C86" s="74" t="s">
+      <c r="A86" s="54"/>
+      <c r="B86" s="54"/>
+      <c r="C86" s="79" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="74"/>
+      <c r="D86" s="79"/>
       <c r="E86" s="46">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="69"/>
-      <c r="B87" s="69"/>
-      <c r="C87" s="103" t="s">
+      <c r="A87" s="54"/>
+      <c r="B87" s="54"/>
+      <c r="C87" s="78" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="103"/>
+      <c r="D87" s="78"/>
       <c r="E87" s="46">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="69"/>
-      <c r="B88" s="69"/>
-      <c r="C88" s="102" t="s">
+      <c r="A88" s="54"/>
+      <c r="B88" s="54"/>
+      <c r="C88" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="102"/>
+      <c r="D88" s="77"/>
       <c r="E88" s="46">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="69"/>
-      <c r="B89" s="69"/>
-      <c r="C89" s="74" t="s">
+      <c r="A89" s="54"/>
+      <c r="B89" s="54"/>
+      <c r="C89" s="79" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="74"/>
+      <c r="D89" s="79"/>
       <c r="E89" s="46">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="69"/>
-      <c r="B90" s="69"/>
-      <c r="C90" s="74" t="s">
+      <c r="A90" s="54"/>
+      <c r="B90" s="54"/>
+      <c r="C90" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="74"/>
+      <c r="D90" s="79"/>
       <c r="E90" s="46">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="69"/>
-      <c r="B91" s="69"/>
-      <c r="C91" s="104" t="s">
+      <c r="A91" s="54"/>
+      <c r="B91" s="54"/>
+      <c r="C91" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="104"/>
+      <c r="D91" s="80"/>
       <c r="E91" s="46">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="70"/>
-      <c r="C92" s="75"/>
-      <c r="D92" s="75"/>
+      <c r="B92" s="73"/>
+      <c r="C92" s="74"/>
+      <c r="D92" s="74"/>
       <c r="E92" s="47">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="76" t="s">
+      <c r="C93" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="76"/>
+      <c r="D93" s="75"/>
       <c r="E93" s="48">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2822,113 +2833,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="66" t="s">
-        <v>130</v>
-      </c>
-      <c r="B95" s="66"/>
-      <c r="C95" s="66"/>
-      <c r="D95" s="66"/>
-      <c r="E95" s="66"/>
+      <c r="A95" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="B95" s="70"/>
+      <c r="C95" s="70"/>
+      <c r="D95" s="70"/>
+      <c r="E95" s="70"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="66" t="s">
+      <c r="A96" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="66"/>
-      <c r="C96" s="66" t="s">
+      <c r="B96" s="70"/>
+      <c r="C96" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="66"/>
+      <c r="D96" s="70"/>
       <c r="E96" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="68" t="s">
+      <c r="A97" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="68"/>
-      <c r="C97" s="77"/>
-      <c r="D97" s="77"/>
+      <c r="B97" s="57"/>
+      <c r="C97" s="55"/>
+      <c r="D97" s="55"/>
       <c r="E97" s="48">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="69" t="s">
+      <c r="A98" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="69"/>
-      <c r="C98" s="73" t="s">
+      <c r="B98" s="54"/>
+      <c r="C98" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="73"/>
+      <c r="D98" s="71"/>
       <c r="E98" s="49">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="69"/>
-      <c r="B99" s="69"/>
-      <c r="C99" s="71" t="s">
+      <c r="A99" s="54"/>
+      <c r="B99" s="54"/>
+      <c r="C99" s="72" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="71"/>
+      <c r="D99" s="72"/>
       <c r="E99" s="49">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="69"/>
-      <c r="B100" s="69"/>
-      <c r="C100" s="71" t="s">
+      <c r="A100" s="54"/>
+      <c r="B100" s="54"/>
+      <c r="C100" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="71"/>
+      <c r="D100" s="72"/>
       <c r="E100" s="49">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="69"/>
-      <c r="B101" s="69"/>
-      <c r="C101" s="71" t="s">
+      <c r="A101" s="54"/>
+      <c r="B101" s="54"/>
+      <c r="C101" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="71"/>
+      <c r="D101" s="72"/>
       <c r="E101" s="49">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="69"/>
-      <c r="B102" s="69"/>
-      <c r="C102" s="82" t="s">
+      <c r="A102" s="54"/>
+      <c r="B102" s="54"/>
+      <c r="C102" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="105"/>
+      <c r="D102" s="68"/>
       <c r="E102" s="49">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="69" t="s">
+      <c r="A103" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="69"/>
-      <c r="C103" s="77"/>
-      <c r="D103" s="77"/>
+      <c r="B103" s="54"/>
+      <c r="C103" s="55"/>
+      <c r="D103" s="55"/>
       <c r="E103" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="80" t="s">
+      <c r="C104" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="80"/>
+      <c r="D104" s="56"/>
       <c r="E104" s="48">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2949,91 +2960,91 @@
       <c r="E106" s="50"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="81" t="s">
-        <v>131</v>
-      </c>
-      <c r="B107" s="81"/>
-      <c r="C107" s="81"/>
-      <c r="D107" s="81"/>
-      <c r="E107" s="81"/>
+      <c r="A107" s="69" t="s">
+        <v>128</v>
+      </c>
+      <c r="B107" s="69"/>
+      <c r="C107" s="69"/>
+      <c r="D107" s="69"/>
+      <c r="E107" s="69"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="66" t="s">
+      <c r="A108" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="66"/>
-      <c r="C108" s="66" t="s">
+      <c r="B108" s="70"/>
+      <c r="C108" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="66"/>
+      <c r="D108" s="70"/>
       <c r="E108" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="68" t="s">
+      <c r="A109" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="68"/>
-      <c r="C109" s="77"/>
-      <c r="D109" s="77"/>
+      <c r="B109" s="57"/>
+      <c r="C109" s="55"/>
+      <c r="D109" s="55"/>
       <c r="E109" s="48">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="84" t="s">
+      <c r="A110" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="85"/>
-      <c r="C110" s="97" t="s">
+      <c r="B110" s="59"/>
+      <c r="C110" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="97"/>
+      <c r="D110" s="64"/>
       <c r="E110" s="46">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="86"/>
-      <c r="B111" s="87"/>
-      <c r="C111" s="106" t="s">
+      <c r="A111" s="60"/>
+      <c r="B111" s="61"/>
+      <c r="C111" s="65" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="107"/>
+      <c r="D111" s="66"/>
       <c r="E111" s="46">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="88"/>
-      <c r="B112" s="89"/>
-      <c r="C112" s="82" t="s">
+      <c r="A112" s="62"/>
+      <c r="B112" s="63"/>
+      <c r="C112" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="105"/>
+      <c r="D112" s="68"/>
       <c r="E112" s="46">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="69" t="s">
+      <c r="A113" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="69"/>
-      <c r="C113" s="77"/>
-      <c r="D113" s="77"/>
+      <c r="B113" s="54"/>
+      <c r="C113" s="55"/>
+      <c r="D113" s="55"/>
       <c r="E113" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="80" t="s">
+      <c r="C114" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="80"/>
+      <c r="D114" s="56"/>
       <c r="E114" s="48">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6785,35 +6796,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6827,42 +6845,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6902,13 +6913,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="97" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7143,13 +7154,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="98" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7177,10 +7188,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="56"/>
+      <c r="D11" s="99"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7192,10 +7203,10 @@
       <c r="B12" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="57"/>
+      <c r="D12" s="105"/>
       <c r="E12" s="53">
         <v>2485</v>
       </c>
@@ -7207,27 +7218,27 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="86" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="59"/>
+      <c r="D13" s="86"/>
       <c r="E13" s="30">
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="51" t="s">
         <v>125</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="58" t="s">
-        <v>126</v>
-      </c>
-      <c r="D14" s="59"/>
+      <c r="C14" s="90" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="86"/>
       <c r="E14" s="30">
-        <v>100</v>
+        <v>770.4</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7239,20 +7250,20 @@
       </c>
       <c r="E15" s="27">
         <f>SUM(E12:E14)</f>
-        <v>2640</v>
+        <v>3310.4</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="25"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="93" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7280,25 +7291,25 @@
       <c r="B18" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="61"/>
+      <c r="D18" s="94"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
-        <v>32</v>
+      <c r="A19" s="51" t="s">
+        <v>134</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="59"/>
+      <c r="D19" s="86"/>
       <c r="E19" s="30">
         <v>2485</v>
       </c>
@@ -7306,8 +7317,8 @@
     <row r="20" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="86"/>
       <c r="E20" s="30">
         <v>0</v>
       </c>
@@ -7329,13 +7340,13 @@
       <c r="B22" s="25"/>
     </row>
     <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="60" t="s">
+      <c r="A23" s="93" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="60"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="93"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
@@ -7363,25 +7374,25 @@
       <c r="B24" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="61"/>
+      <c r="D24" s="94"/>
       <c r="E24" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
-        <v>103</v>
+      <c r="A25" s="51" t="s">
+        <v>135</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="59"/>
+      <c r="D25" s="86"/>
       <c r="E25" s="34">
         <v>2485</v>
       </c>
@@ -7389,8 +7400,8 @@
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
       <c r="E26" s="30">
         <v>0</v>
       </c>
@@ -7412,11 +7423,11 @@
       <c r="B28" s="25"/>
     </row>
     <row r="29" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="62" t="s">
+      <c r="A29" s="84" t="s">
         <v>106</v>
       </c>
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
+      <c r="B29" s="84"/>
+      <c r="C29" s="84"/>
     </row>
     <row r="30" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -7431,11 +7442,11 @@
       <c r="D30" s="38"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="81"/>
     </row>
     <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="51" t="s">
@@ -7481,16 +7492,16 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="64" t="s">
+      <c r="A36" s="85" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="64"/>
-      <c r="C36" s="64"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="85"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="64"/>
-      <c r="B37" s="64"/>
-      <c r="C37" s="64"/>
+      <c r="A37" s="85"/>
+      <c r="B37" s="85"/>
+      <c r="C37" s="85"/>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
@@ -7539,11 +7550,11 @@
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="63" t="s">
+      <c r="A43" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="63"/>
-      <c r="C43" s="63"/>
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
     </row>
     <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
@@ -7578,11 +7589,11 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="63" t="s">
+      <c r="A47" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="63"/>
-      <c r="C47" s="63"/>
+      <c r="B47" s="81"/>
+      <c r="C47" s="81"/>
     </row>
     <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
@@ -7606,11 +7617,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="63" t="s">
+      <c r="A50" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="63"/>
-      <c r="C50" s="63"/>
+      <c r="B50" s="81"/>
+      <c r="C50" s="81"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7634,11 +7645,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="65" t="s">
+      <c r="A53" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="65"/>
-      <c r="C53" s="65"/>
+      <c r="B53" s="82"/>
+      <c r="C53" s="82"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="17" t="s">
@@ -7715,11 +7726,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="65" t="s">
+      <c r="A61" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="B61" s="65"/>
-      <c r="C61" s="65"/>
+      <c r="B61" s="82"/>
+      <c r="C61" s="82"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
@@ -7769,91 +7780,91 @@
       <c r="B67" s="25"/>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="66" t="s">
-        <v>132</v>
-      </c>
-      <c r="B68" s="66"/>
-      <c r="C68" s="66"/>
-      <c r="D68" s="66"/>
-      <c r="E68" s="66"/>
+      <c r="A68" s="70" t="s">
+        <v>129</v>
+      </c>
+      <c r="B68" s="70"/>
+      <c r="C68" s="70"/>
+      <c r="D68" s="70"/>
+      <c r="E68" s="70"/>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="67" t="s">
+      <c r="A69" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="B69" s="67"/>
-      <c r="C69" s="67" t="s">
+      <c r="B69" s="83"/>
+      <c r="C69" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="D69" s="67"/>
+      <c r="D69" s="83"/>
       <c r="E69" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="68" t="s">
+      <c r="A70" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="B70" s="68"/>
-      <c r="C70" s="69"/>
-      <c r="D70" s="69"/>
+      <c r="B70" s="57"/>
+      <c r="C70" s="54"/>
+      <c r="D70" s="54"/>
       <c r="E70" s="48">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="70" t="s">
+      <c r="A71" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="70"/>
-      <c r="C71" s="71" t="s">
+      <c r="B71" s="73"/>
+      <c r="C71" s="72" t="s">
         <v>122</v>
       </c>
-      <c r="D71" s="71"/>
+      <c r="D71" s="72"/>
       <c r="E71" s="46">
         <v>600</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="251" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="70"/>
-      <c r="B72" s="70"/>
-      <c r="C72" s="72" t="s">
-        <v>128</v>
-      </c>
-      <c r="D72" s="73"/>
+    <row r="72" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="73"/>
+      <c r="B72" s="73"/>
+      <c r="C72" s="104" t="s">
+        <v>137</v>
+      </c>
+      <c r="D72" s="71"/>
       <c r="E72" s="46">
-        <v>447.1</v>
+        <v>1117.5</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="133" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="70"/>
-      <c r="B73" s="70"/>
-      <c r="C73" s="72" t="s">
-        <v>136</v>
-      </c>
-      <c r="D73" s="74"/>
+      <c r="A73" s="73"/>
+      <c r="B73" s="73"/>
+      <c r="C73" s="104" t="s">
+        <v>133</v>
+      </c>
+      <c r="D73" s="79"/>
       <c r="E73" s="46">
         <v>506</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="70" t="s">
+      <c r="A74" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="B74" s="70"/>
-      <c r="C74" s="75"/>
-      <c r="D74" s="75"/>
+      <c r="B74" s="73"/>
+      <c r="C74" s="74"/>
+      <c r="D74" s="74"/>
       <c r="E74" s="47">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C75" s="76" t="s">
+      <c r="C75" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="D75" s="76"/>
+      <c r="D75" s="75"/>
       <c r="E75" s="48">
         <f>(E15+E70)-SUM(E71:E74)</f>
         <v>26.599999999999909</v>
@@ -7861,100 +7872,100 @@
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="66" t="s">
-        <v>133</v>
-      </c>
-      <c r="B77" s="66"/>
-      <c r="C77" s="66"/>
-      <c r="D77" s="66"/>
-      <c r="E77" s="66"/>
+      <c r="A77" s="70" t="s">
+        <v>130</v>
+      </c>
+      <c r="B77" s="70"/>
+      <c r="C77" s="70"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="70"/>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="66" t="s">
+      <c r="A78" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="B78" s="66"/>
-      <c r="C78" s="66" t="s">
+      <c r="B78" s="70"/>
+      <c r="C78" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="D78" s="66"/>
+      <c r="D78" s="70"/>
       <c r="E78" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="68" t="s">
+      <c r="A79" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="B79" s="68"/>
-      <c r="C79" s="77"/>
-      <c r="D79" s="77"/>
+      <c r="B79" s="57"/>
+      <c r="C79" s="55"/>
+      <c r="D79" s="55"/>
       <c r="E79" s="48">
         <f>E75</f>
         <v>26.599999999999909</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="84" t="s">
+    <row r="80" spans="1:8" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="B80" s="85"/>
-      <c r="C80" s="78" t="s">
-        <v>127</v>
-      </c>
-      <c r="D80" s="79"/>
+      <c r="B80" s="59"/>
+      <c r="C80" s="106" t="s">
+        <v>139</v>
+      </c>
+      <c r="D80" s="102"/>
       <c r="E80" s="49">
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="86"/>
-      <c r="B81" s="87"/>
-      <c r="C81" s="71" t="s">
-        <v>118</v>
-      </c>
-      <c r="D81" s="71"/>
+    <row r="81" spans="1:5" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="60"/>
+      <c r="B81" s="61"/>
+      <c r="C81" s="72" t="s">
+        <v>138</v>
+      </c>
+      <c r="D81" s="72"/>
       <c r="E81" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="86"/>
-      <c r="B82" s="87"/>
-      <c r="C82" s="82" t="s">
-        <v>135</v>
-      </c>
-      <c r="D82" s="83"/>
+      <c r="A82" s="60"/>
+      <c r="B82" s="61"/>
+      <c r="C82" s="67" t="s">
+        <v>132</v>
+      </c>
+      <c r="D82" s="103"/>
       <c r="E82" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="88"/>
-      <c r="B83" s="89"/>
-      <c r="C83" s="83"/>
-      <c r="D83" s="83"/>
+      <c r="A83" s="62"/>
+      <c r="B83" s="63"/>
+      <c r="C83" s="103"/>
+      <c r="D83" s="103"/>
       <c r="E83" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="69" t="s">
+      <c r="A84" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="69"/>
-      <c r="C84" s="77"/>
-      <c r="D84" s="77"/>
+      <c r="B84" s="54"/>
+      <c r="C84" s="55"/>
+      <c r="D84" s="55"/>
       <c r="E84" s="46">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="80" t="s">
+      <c r="C85" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D85" s="80"/>
+      <c r="D85" s="56"/>
       <c r="E85" s="48">
         <f>(E21+E79)-SUM(E80:E84)</f>
         <v>1340.6</v>
@@ -7975,69 +7986,69 @@
       <c r="E87" s="50"/>
     </row>
     <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="81" t="s">
-        <v>134</v>
-      </c>
-      <c r="B88" s="81"/>
-      <c r="C88" s="81"/>
-      <c r="D88" s="81"/>
-      <c r="E88" s="81"/>
+      <c r="A88" s="69" t="s">
+        <v>131</v>
+      </c>
+      <c r="B88" s="69"/>
+      <c r="C88" s="69"/>
+      <c r="D88" s="69"/>
+      <c r="E88" s="69"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="66" t="s">
+      <c r="A89" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="66"/>
-      <c r="C89" s="66" t="s">
+      <c r="B89" s="70"/>
+      <c r="C89" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="66"/>
+      <c r="D89" s="70"/>
       <c r="E89" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="68" t="s">
+      <c r="A90" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="B90" s="68"/>
-      <c r="C90" s="77"/>
-      <c r="D90" s="77"/>
+      <c r="B90" s="57"/>
+      <c r="C90" s="55"/>
+      <c r="D90" s="55"/>
       <c r="E90" s="48">
         <f>E85</f>
         <v>1340.6</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="69" t="s">
+      <c r="A91" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="69"/>
-      <c r="C91" s="71" t="s">
+      <c r="B91" s="54"/>
+      <c r="C91" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="D91" s="71"/>
+      <c r="D91" s="72"/>
       <c r="E91" s="46">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="69" t="s">
+      <c r="A92" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="69"/>
-      <c r="C92" s="77"/>
-      <c r="D92" s="77"/>
+      <c r="B92" s="54"/>
+      <c r="C92" s="55"/>
+      <c r="D92" s="55"/>
       <c r="E92" s="46">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="80" t="s">
+      <c r="C93" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="80"/>
+      <c r="D93" s="56"/>
       <c r="E93" s="48">
         <f>(E27+E90)-SUM(E91:E92)</f>
         <v>2654.6</v>
@@ -11789,13 +11800,45 @@
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A36:C37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="A71:B73"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
     <mergeCell ref="C80:D80"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="A88:E88"/>
@@ -11807,45 +11850,13 @@
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="C84:D84"/>
     <mergeCell ref="A80:B83"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A71:B73"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="A36:C37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E70">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E465D28D-F29C-7446-9EFC-EF5BD2ACC7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5BB5F4-128D-444B-A661-9FCBA1E671B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1170,17 +1170,95 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1200,41 +1278,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1245,88 +1317,16 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1646,13 +1646,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1882,13 +1882,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="98" t="s">
+      <c r="A10" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1916,10 +1916,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="99" t="s">
+      <c r="C11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="99"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1931,10 +1931,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="100" t="s">
+      <c r="C12" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="100"/>
+      <c r="D12" s="90"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1946,10 +1946,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="101" t="s">
+      <c r="C13" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="101"/>
+      <c r="D13" s="91"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1959,10 +1959,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="86" t="s">
+      <c r="C14" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="86"/>
+      <c r="D14" s="59"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -1972,10 +1972,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="86" t="s">
+      <c r="C15" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="86"/>
+      <c r="D15" s="59"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -1985,10 +1985,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="86" t="s">
+      <c r="C16" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="86"/>
+      <c r="D16" s="59"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2000,10 +2000,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="91" t="s">
+      <c r="C17" s="92" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="91"/>
+      <c r="D17" s="92"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2013,10 +2013,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="92" t="s">
+      <c r="C18" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="92"/>
+      <c r="D18" s="93"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2028,10 +2028,10 @@
       <c r="B19" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="95" t="s">
+      <c r="C19" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="95"/>
+      <c r="D19" s="94"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2052,13 +2052,13 @@
       <c r="B21" s="25"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="93" t="s">
+      <c r="A22" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="93"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2086,10 +2086,10 @@
       <c r="B23" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="96" t="s">
+      <c r="C23" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="96"/>
+      <c r="D23" s="95"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2101,10 +2101,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="86" t="s">
+      <c r="C24" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="86"/>
+      <c r="D24" s="59"/>
       <c r="E24" s="30">
         <v>2485</v>
       </c>
@@ -2116,10 +2116,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="86"/>
+      <c r="D25" s="59"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2129,10 +2129,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="90" t="s">
+      <c r="C26" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="91"/>
+      <c r="D26" s="92"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2144,10 +2144,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="92" t="s">
+      <c r="C27" s="93" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="92"/>
+      <c r="D27" s="93"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2157,10 +2157,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="96" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="64"/>
+      <c r="D28" s="96"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2182,13 +2182,13 @@
       <c r="B30" s="25"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="93" t="s">
+      <c r="A31" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="93"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="93"/>
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2216,10 +2216,10 @@
       <c r="B32" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="94" t="s">
+      <c r="C32" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="94"/>
+      <c r="D32" s="61"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2231,10 +2231,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="86" t="s">
+      <c r="C33" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="86"/>
+      <c r="D33" s="59"/>
       <c r="E33" s="34">
         <v>2485</v>
       </c>
@@ -2244,10 +2244,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="86" t="s">
+      <c r="C34" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="86"/>
+      <c r="D34" s="59"/>
       <c r="E34" s="34">
         <v>118</v>
       </c>
@@ -2257,10 +2257,10 @@
       <c r="B35" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="87" t="s">
+      <c r="C35" s="97" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="88"/>
+      <c r="D35" s="98"/>
       <c r="E35" s="34">
         <v>170</v>
       </c>
@@ -2270,10 +2270,10 @@
       <c r="B36" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="87" t="s">
+      <c r="C36" s="97" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="89"/>
+      <c r="D36" s="99"/>
       <c r="E36" s="34">
         <v>800</v>
       </c>
@@ -2283,10 +2283,10 @@
       <c r="B37" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="90" t="s">
+      <c r="C37" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="86"/>
+      <c r="D37" s="59"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2308,11 +2308,11 @@
       <c r="B39" s="25"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="84" t="s">
+      <c r="A40" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="84"/>
-      <c r="C40" s="84"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="62"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2327,11 +2327,11 @@
       <c r="D41" s="38"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="81" t="s">
+      <c r="A42" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="81"/>
-      <c r="C42" s="81"/>
+      <c r="B42" s="63"/>
+      <c r="C42" s="63"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="51" t="s">
@@ -2377,16 +2377,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="85" t="s">
+      <c r="A47" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="85"/>
-      <c r="C47" s="85"/>
+      <c r="B47" s="64"/>
+      <c r="C47" s="64"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="85"/>
-      <c r="B48" s="85"/>
-      <c r="C48" s="85"/>
+      <c r="A48" s="64"/>
+      <c r="B48" s="64"/>
+      <c r="C48" s="64"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2435,11 +2435,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="81" t="s">
+      <c r="A54" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="81"/>
-      <c r="C54" s="81"/>
+      <c r="B54" s="63"/>
+      <c r="C54" s="63"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2474,11 +2474,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="81" t="s">
+      <c r="A58" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="81"/>
-      <c r="C58" s="81"/>
+      <c r="B58" s="63"/>
+      <c r="C58" s="63"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2502,11 +2502,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="81" t="s">
+      <c r="A61" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="81"/>
-      <c r="C61" s="81"/>
+      <c r="B61" s="63"/>
+      <c r="C61" s="63"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2530,11 +2530,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="82" t="s">
+      <c r="A64" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="82"/>
-      <c r="C64" s="82"/>
+      <c r="B64" s="65"/>
+      <c r="C64" s="65"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2611,11 +2611,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="82" t="s">
+      <c r="A72" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="82"/>
-      <c r="C72" s="82"/>
+      <c r="B72" s="65"/>
+      <c r="C72" s="65"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="19">
-        <v>100</v>
+        <v>770.4</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="C75" s="19">
         <f>SUM(C73:C74)</f>
-        <v>100</v>
+        <v>770.4</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2665,167 +2665,167 @@
       <c r="B78" s="25"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="70" t="s">
+      <c r="A79" s="66" t="s">
         <v>126</v>
       </c>
-      <c r="B79" s="70"/>
-      <c r="C79" s="70"/>
-      <c r="D79" s="70"/>
-      <c r="E79" s="70"/>
+      <c r="B79" s="66"/>
+      <c r="C79" s="66"/>
+      <c r="D79" s="66"/>
+      <c r="E79" s="66"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="83" t="s">
+      <c r="A80" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="83"/>
-      <c r="C80" s="83" t="s">
+      <c r="B80" s="67"/>
+      <c r="C80" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="83"/>
+      <c r="D80" s="67"/>
       <c r="E80" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="76" t="s">
+      <c r="A81" s="100" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="76"/>
-      <c r="C81" s="54"/>
-      <c r="D81" s="54"/>
+      <c r="B81" s="100"/>
+      <c r="C81" s="69"/>
+      <c r="D81" s="69"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="54" t="s">
+      <c r="A82" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="54"/>
-      <c r="C82" s="77" t="s">
+      <c r="B82" s="69"/>
+      <c r="C82" s="101" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="77"/>
+      <c r="D82" s="101"/>
       <c r="E82" s="46">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="54"/>
-      <c r="B83" s="54"/>
-      <c r="C83" s="77" t="s">
+      <c r="A83" s="69"/>
+      <c r="B83" s="69"/>
+      <c r="C83" s="101" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="77"/>
+      <c r="D83" s="101"/>
       <c r="E83" s="46">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="54"/>
-      <c r="B84" s="54"/>
-      <c r="C84" s="77" t="s">
+      <c r="A84" s="69"/>
+      <c r="B84" s="69"/>
+      <c r="C84" s="101" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="77"/>
+      <c r="D84" s="101"/>
       <c r="E84" s="46">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="54"/>
-      <c r="B85" s="54"/>
-      <c r="C85" s="78" t="s">
+      <c r="A85" s="69"/>
+      <c r="B85" s="69"/>
+      <c r="C85" s="102" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="78"/>
+      <c r="D85" s="102"/>
       <c r="E85" s="46">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="54"/>
-      <c r="B86" s="54"/>
-      <c r="C86" s="79" t="s">
+      <c r="A86" s="69"/>
+      <c r="B86" s="69"/>
+      <c r="C86" s="74" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="79"/>
+      <c r="D86" s="74"/>
       <c r="E86" s="46">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="54"/>
-      <c r="B87" s="54"/>
-      <c r="C87" s="78" t="s">
+      <c r="A87" s="69"/>
+      <c r="B87" s="69"/>
+      <c r="C87" s="102" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="78"/>
+      <c r="D87" s="102"/>
       <c r="E87" s="46">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="54"/>
-      <c r="B88" s="54"/>
-      <c r="C88" s="77" t="s">
+      <c r="A88" s="69"/>
+      <c r="B88" s="69"/>
+      <c r="C88" s="101" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="77"/>
+      <c r="D88" s="101"/>
       <c r="E88" s="46">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="54"/>
-      <c r="B89" s="54"/>
-      <c r="C89" s="79" t="s">
+      <c r="A89" s="69"/>
+      <c r="B89" s="69"/>
+      <c r="C89" s="74" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="79"/>
+      <c r="D89" s="74"/>
       <c r="E89" s="46">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="54"/>
-      <c r="B90" s="54"/>
-      <c r="C90" s="79" t="s">
+      <c r="A90" s="69"/>
+      <c r="B90" s="69"/>
+      <c r="C90" s="74" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="79"/>
+      <c r="D90" s="74"/>
       <c r="E90" s="46">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="54"/>
-      <c r="B91" s="54"/>
-      <c r="C91" s="80" t="s">
+      <c r="A91" s="69"/>
+      <c r="B91" s="69"/>
+      <c r="C91" s="103" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="80"/>
+      <c r="D91" s="103"/>
       <c r="E91" s="46">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="73" t="s">
+      <c r="A92" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="73"/>
-      <c r="C92" s="74"/>
-      <c r="D92" s="74"/>
+      <c r="B92" s="70"/>
+      <c r="C92" s="75"/>
+      <c r="D92" s="75"/>
       <c r="E92" s="47">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="75" t="s">
+      <c r="C93" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="75"/>
+      <c r="D93" s="76"/>
       <c r="E93" s="48">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2833,113 +2833,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="70" t="s">
+      <c r="A95" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="B95" s="70"/>
-      <c r="C95" s="70"/>
-      <c r="D95" s="70"/>
-      <c r="E95" s="70"/>
+      <c r="B95" s="66"/>
+      <c r="C95" s="66"/>
+      <c r="D95" s="66"/>
+      <c r="E95" s="66"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="70" t="s">
+      <c r="A96" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="70"/>
-      <c r="C96" s="70" t="s">
+      <c r="B96" s="66"/>
+      <c r="C96" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="70"/>
+      <c r="D96" s="66"/>
       <c r="E96" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="57" t="s">
+      <c r="A97" s="68" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="57"/>
-      <c r="C97" s="55"/>
-      <c r="D97" s="55"/>
+      <c r="B97" s="68"/>
+      <c r="C97" s="77"/>
+      <c r="D97" s="77"/>
       <c r="E97" s="48">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="54" t="s">
+      <c r="A98" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="54"/>
-      <c r="C98" s="71" t="s">
+      <c r="B98" s="69"/>
+      <c r="C98" s="73" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="71"/>
+      <c r="D98" s="73"/>
       <c r="E98" s="49">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="54"/>
-      <c r="B99" s="54"/>
-      <c r="C99" s="72" t="s">
+      <c r="A99" s="69"/>
+      <c r="B99" s="69"/>
+      <c r="C99" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="72"/>
+      <c r="D99" s="71"/>
       <c r="E99" s="49">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="54"/>
-      <c r="B100" s="54"/>
-      <c r="C100" s="72" t="s">
+      <c r="A100" s="69"/>
+      <c r="B100" s="69"/>
+      <c r="C100" s="71" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="72"/>
+      <c r="D100" s="71"/>
       <c r="E100" s="49">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="54"/>
-      <c r="B101" s="54"/>
-      <c r="C101" s="72" t="s">
+      <c r="A101" s="69"/>
+      <c r="B101" s="69"/>
+      <c r="C101" s="71" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="72"/>
+      <c r="D101" s="71"/>
       <c r="E101" s="49">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="54"/>
-      <c r="B102" s="54"/>
-      <c r="C102" s="67" t="s">
+      <c r="A102" s="69"/>
+      <c r="B102" s="69"/>
+      <c r="C102" s="82" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="68"/>
+      <c r="D102" s="104"/>
       <c r="E102" s="49">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="54" t="s">
+      <c r="A103" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="54"/>
-      <c r="C103" s="55"/>
-      <c r="D103" s="55"/>
+      <c r="B103" s="69"/>
+      <c r="C103" s="77"/>
+      <c r="D103" s="77"/>
       <c r="E103" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="56" t="s">
+      <c r="C104" s="80" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="56"/>
+      <c r="D104" s="80"/>
       <c r="E104" s="48">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2960,91 +2960,91 @@
       <c r="E106" s="50"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="69" t="s">
+      <c r="A107" s="81" t="s">
         <v>128</v>
       </c>
-      <c r="B107" s="69"/>
-      <c r="C107" s="69"/>
-      <c r="D107" s="69"/>
-      <c r="E107" s="69"/>
+      <c r="B107" s="81"/>
+      <c r="C107" s="81"/>
+      <c r="D107" s="81"/>
+      <c r="E107" s="81"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="70" t="s">
+      <c r="A108" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="70"/>
-      <c r="C108" s="70" t="s">
+      <c r="B108" s="66"/>
+      <c r="C108" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="70"/>
+      <c r="D108" s="66"/>
       <c r="E108" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="57" t="s">
+      <c r="A109" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="57"/>
-      <c r="C109" s="55"/>
-      <c r="D109" s="55"/>
+      <c r="B109" s="68"/>
+      <c r="C109" s="77"/>
+      <c r="D109" s="77"/>
       <c r="E109" s="48">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="58" t="s">
+      <c r="A110" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="59"/>
-      <c r="C110" s="64" t="s">
+      <c r="B110" s="85"/>
+      <c r="C110" s="96" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="64"/>
+      <c r="D110" s="96"/>
       <c r="E110" s="46">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="60"/>
-      <c r="B111" s="61"/>
-      <c r="C111" s="65" t="s">
+      <c r="A111" s="86"/>
+      <c r="B111" s="87"/>
+      <c r="C111" s="105" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="66"/>
+      <c r="D111" s="106"/>
       <c r="E111" s="46">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="62"/>
-      <c r="B112" s="63"/>
-      <c r="C112" s="67" t="s">
+      <c r="A112" s="88"/>
+      <c r="B112" s="89"/>
+      <c r="C112" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="68"/>
+      <c r="D112" s="104"/>
       <c r="E112" s="46">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="54" t="s">
+      <c r="A113" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="54"/>
-      <c r="C113" s="55"/>
-      <c r="D113" s="55"/>
+      <c r="B113" s="69"/>
+      <c r="C113" s="77"/>
+      <c r="D113" s="77"/>
       <c r="E113" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="56" t="s">
+      <c r="C114" s="80" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="56"/>
+      <c r="D114" s="80"/>
       <c r="E114" s="48">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6796,42 +6796,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6845,35 +6838,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6913,13 +6913,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7154,13 +7154,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="98" t="s">
+      <c r="A10" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7188,10 +7188,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="99" t="s">
+      <c r="C11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="99"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7203,10 +7203,10 @@
       <c r="B12" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="105" t="s">
+      <c r="C12" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="105"/>
+      <c r="D12" s="57"/>
       <c r="E12" s="53">
         <v>2485</v>
       </c>
@@ -7218,10 +7218,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="C13" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="86"/>
+      <c r="D13" s="59"/>
       <c r="E13" s="30">
         <v>55</v>
       </c>
@@ -7233,10 +7233,10 @@
       <c r="B14" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="90" t="s">
+      <c r="C14" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="D14" s="86"/>
+      <c r="D14" s="59"/>
       <c r="E14" s="30">
         <v>770.4</v>
       </c>
@@ -7257,13 +7257,13 @@
       <c r="B16" s="25"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="93" t="s">
+      <c r="A17" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7291,10 +7291,10 @@
       <c r="B18" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="94" t="s">
+      <c r="C18" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="94"/>
+      <c r="D18" s="61"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7306,10 +7306,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="86" t="s">
+      <c r="C19" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="86"/>
+      <c r="D19" s="59"/>
       <c r="E19" s="30">
         <v>2485</v>
       </c>
@@ -7317,8 +7317,8 @@
     <row r="20" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
       <c r="E20" s="30">
         <v>0</v>
       </c>
@@ -7340,13 +7340,13 @@
       <c r="B22" s="25"/>
     </row>
     <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="93" t="s">
+      <c r="A23" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="93"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="93"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
@@ -7374,10 +7374,10 @@
       <c r="B24" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="94" t="s">
+      <c r="C24" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="94"/>
+      <c r="D24" s="61"/>
       <c r="E24" s="2" t="s">
         <v>12</v>
       </c>
@@ -7389,10 +7389,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="86"/>
+      <c r="D25" s="59"/>
       <c r="E25" s="34">
         <v>2485</v>
       </c>
@@ -7400,8 +7400,8 @@
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
       <c r="E26" s="30">
         <v>0</v>
       </c>
@@ -7423,11 +7423,11 @@
       <c r="B28" s="25"/>
     </row>
     <row r="29" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="84" t="s">
+      <c r="A29" s="62" t="s">
         <v>106</v>
       </c>
-      <c r="B29" s="84"/>
-      <c r="C29" s="84"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="62"/>
     </row>
     <row r="30" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -7442,11 +7442,11 @@
       <c r="D30" s="38"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="81" t="s">
+      <c r="A31" s="63" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="81"/>
-      <c r="C31" s="81"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
     </row>
     <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="51" t="s">
@@ -7492,16 +7492,16 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="85" t="s">
+      <c r="A36" s="64" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="85"/>
-      <c r="C36" s="85"/>
+      <c r="B36" s="64"/>
+      <c r="C36" s="64"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="85"/>
-      <c r="B37" s="85"/>
-      <c r="C37" s="85"/>
+      <c r="A37" s="64"/>
+      <c r="B37" s="64"/>
+      <c r="C37" s="64"/>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
@@ -7550,11 +7550,11 @@
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="81" t="s">
+      <c r="A43" s="63" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="81"/>
-      <c r="C43" s="81"/>
+      <c r="B43" s="63"/>
+      <c r="C43" s="63"/>
     </row>
     <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
@@ -7589,11 +7589,11 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="81" t="s">
+      <c r="A47" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="81"/>
-      <c r="C47" s="81"/>
+      <c r="B47" s="63"/>
+      <c r="C47" s="63"/>
     </row>
     <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
@@ -7617,11 +7617,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="81" t="s">
+      <c r="A50" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="81"/>
-      <c r="C50" s="81"/>
+      <c r="B50" s="63"/>
+      <c r="C50" s="63"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7645,11 +7645,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="82" t="s">
+      <c r="A53" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="82"/>
-      <c r="C53" s="82"/>
+      <c r="B53" s="65"/>
+      <c r="C53" s="65"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="17" t="s">
@@ -7726,11 +7726,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="82" t="s">
+      <c r="A61" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="B61" s="82"/>
-      <c r="C61" s="82"/>
+      <c r="B61" s="65"/>
+      <c r="C61" s="65"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="B62" s="7"/>
       <c r="C62" s="19">
-        <v>100</v>
+        <v>770.4</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="C64" s="19">
         <f>SUM(C62:C63)</f>
-        <v>100</v>
+        <v>770.4</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7780,91 +7780,91 @@
       <c r="B67" s="25"/>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="70" t="s">
+      <c r="A68" s="66" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="70"/>
-      <c r="C68" s="70"/>
-      <c r="D68" s="70"/>
-      <c r="E68" s="70"/>
+      <c r="B68" s="66"/>
+      <c r="C68" s="66"/>
+      <c r="D68" s="66"/>
+      <c r="E68" s="66"/>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="83" t="s">
+      <c r="A69" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="B69" s="83"/>
-      <c r="C69" s="83" t="s">
+      <c r="B69" s="67"/>
+      <c r="C69" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D69" s="83"/>
+      <c r="D69" s="67"/>
       <c r="E69" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="57" t="s">
+      <c r="A70" s="68" t="s">
         <v>107</v>
       </c>
-      <c r="B70" s="57"/>
-      <c r="C70" s="54"/>
-      <c r="D70" s="54"/>
+      <c r="B70" s="68"/>
+      <c r="C70" s="69"/>
+      <c r="D70" s="69"/>
       <c r="E70" s="48">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="73" t="s">
+      <c r="A71" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="73"/>
-      <c r="C71" s="72" t="s">
+      <c r="B71" s="70"/>
+      <c r="C71" s="71" t="s">
         <v>122</v>
       </c>
-      <c r="D71" s="72"/>
+      <c r="D71" s="71"/>
       <c r="E71" s="46">
         <v>600</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="73"/>
-      <c r="B72" s="73"/>
-      <c r="C72" s="104" t="s">
+      <c r="A72" s="70"/>
+      <c r="B72" s="70"/>
+      <c r="C72" s="72" t="s">
         <v>137</v>
       </c>
-      <c r="D72" s="71"/>
+      <c r="D72" s="73"/>
       <c r="E72" s="46">
         <v>1117.5</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="133" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="73"/>
-      <c r="B73" s="73"/>
-      <c r="C73" s="104" t="s">
+      <c r="A73" s="70"/>
+      <c r="B73" s="70"/>
+      <c r="C73" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="D73" s="79"/>
+      <c r="D73" s="74"/>
       <c r="E73" s="46">
         <v>506</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="73" t="s">
+      <c r="A74" s="70" t="s">
         <v>95</v>
       </c>
-      <c r="B74" s="73"/>
-      <c r="C74" s="74"/>
-      <c r="D74" s="74"/>
+      <c r="B74" s="70"/>
+      <c r="C74" s="75"/>
+      <c r="D74" s="75"/>
       <c r="E74" s="47">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C75" s="75" t="s">
+      <c r="C75" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="D75" s="75"/>
+      <c r="D75" s="76"/>
       <c r="E75" s="48">
         <f>(E15+E70)-SUM(E71:E74)</f>
         <v>26.599999999999909</v>
@@ -7872,100 +7872,100 @@
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="70" t="s">
+      <c r="A77" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="B77" s="70"/>
-      <c r="C77" s="70"/>
-      <c r="D77" s="70"/>
-      <c r="E77" s="70"/>
+      <c r="B77" s="66"/>
+      <c r="C77" s="66"/>
+      <c r="D77" s="66"/>
+      <c r="E77" s="66"/>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="70" t="s">
+      <c r="A78" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="B78" s="70"/>
-      <c r="C78" s="70" t="s">
+      <c r="B78" s="66"/>
+      <c r="C78" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="D78" s="70"/>
+      <c r="D78" s="66"/>
       <c r="E78" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="57" t="s">
+      <c r="A79" s="68" t="s">
         <v>108</v>
       </c>
-      <c r="B79" s="57"/>
-      <c r="C79" s="55"/>
-      <c r="D79" s="55"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="77"/>
+      <c r="D79" s="77"/>
       <c r="E79" s="48">
         <f>E75</f>
         <v>26.599999999999909</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="58" t="s">
+      <c r="A80" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B80" s="59"/>
-      <c r="C80" s="106" t="s">
+      <c r="B80" s="85"/>
+      <c r="C80" s="78" t="s">
         <v>139</v>
       </c>
-      <c r="D80" s="102"/>
+      <c r="D80" s="79"/>
       <c r="E80" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="60"/>
-      <c r="B81" s="61"/>
-      <c r="C81" s="72" t="s">
+      <c r="A81" s="86"/>
+      <c r="B81" s="87"/>
+      <c r="C81" s="71" t="s">
         <v>138</v>
       </c>
-      <c r="D81" s="72"/>
+      <c r="D81" s="71"/>
       <c r="E81" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="60"/>
-      <c r="B82" s="61"/>
-      <c r="C82" s="67" t="s">
+      <c r="A82" s="86"/>
+      <c r="B82" s="87"/>
+      <c r="C82" s="82" t="s">
         <v>132</v>
       </c>
-      <c r="D82" s="103"/>
+      <c r="D82" s="83"/>
       <c r="E82" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="62"/>
-      <c r="B83" s="63"/>
-      <c r="C83" s="103"/>
-      <c r="D83" s="103"/>
+      <c r="A83" s="88"/>
+      <c r="B83" s="89"/>
+      <c r="C83" s="83"/>
+      <c r="D83" s="83"/>
       <c r="E83" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="54" t="s">
+      <c r="A84" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="54"/>
-      <c r="C84" s="55"/>
-      <c r="D84" s="55"/>
+      <c r="B84" s="69"/>
+      <c r="C84" s="77"/>
+      <c r="D84" s="77"/>
       <c r="E84" s="46">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="56" t="s">
+      <c r="C85" s="80" t="s">
         <v>96</v>
       </c>
-      <c r="D85" s="56"/>
+      <c r="D85" s="80"/>
       <c r="E85" s="48">
         <f>(E21+E79)-SUM(E80:E84)</f>
         <v>1340.6</v>
@@ -7986,69 +7986,69 @@
       <c r="E87" s="50"/>
     </row>
     <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="69" t="s">
+      <c r="A88" s="81" t="s">
         <v>131</v>
       </c>
-      <c r="B88" s="69"/>
-      <c r="C88" s="69"/>
-      <c r="D88" s="69"/>
-      <c r="E88" s="69"/>
+      <c r="B88" s="81"/>
+      <c r="C88" s="81"/>
+      <c r="D88" s="81"/>
+      <c r="E88" s="81"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="70" t="s">
+      <c r="A89" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="70"/>
-      <c r="C89" s="70" t="s">
+      <c r="B89" s="66"/>
+      <c r="C89" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="70"/>
+      <c r="D89" s="66"/>
       <c r="E89" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="57" t="s">
+      <c r="A90" s="68" t="s">
         <v>109</v>
       </c>
-      <c r="B90" s="57"/>
-      <c r="C90" s="55"/>
-      <c r="D90" s="55"/>
+      <c r="B90" s="68"/>
+      <c r="C90" s="77"/>
+      <c r="D90" s="77"/>
       <c r="E90" s="48">
         <f>E85</f>
         <v>1340.6</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="54" t="s">
+      <c r="A91" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="54"/>
-      <c r="C91" s="72" t="s">
+      <c r="B91" s="69"/>
+      <c r="C91" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="D91" s="72"/>
+      <c r="D91" s="71"/>
       <c r="E91" s="46">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="54" t="s">
+      <c r="A92" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="54"/>
-      <c r="C92" s="55"/>
-      <c r="D92" s="55"/>
+      <c r="B92" s="69"/>
+      <c r="C92" s="77"/>
+      <c r="D92" s="77"/>
       <c r="E92" s="46">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="56" t="s">
+      <c r="C93" s="80" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="56"/>
+      <c r="D93" s="80"/>
       <c r="E93" s="48">
         <f>(E27+E90)-SUM(E91:E92)</f>
         <v>2654.6</v>
@@ -11800,45 +11800,13 @@
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A36:C37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="A71:B73"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
     <mergeCell ref="C80:D80"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="A88:E88"/>
@@ -11850,13 +11818,45 @@
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="C84:D84"/>
     <mergeCell ref="A80:B83"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="A71:B73"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="A36:C37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E70">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5BB5F4-128D-444B-A661-9FCBA1E671B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8A21E61-1E03-954C-949A-CF7F5CDA95A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -600,15 +600,6 @@
 ~ Round Trip to Kowloon East Hospital 31/08 - $4</t>
   </si>
   <si>
-    <t>~ OK Store buy additional 1 packet cigarette 20/07 - $78
-~ Additional transport fees for e-cigarette 20/07 - $40
-~ HKTVmall - Microsoft Office 365 1 year subscribtion 30/07 - $299
-~ Round Trip to Kowloon East Hospital 03/08 - $4
-~ Round Trip to Kwai Chung Eldery Hospital 05/08 - $3.5
-~ Round Trip to Kwai Chung Eldery Hospital 16/08 - $3.5
-~ OK Store buy additional 1 packet cigarette 18/08 - $78</t>
-  </si>
-  <si>
     <t>20th August 2026</t>
   </si>
   <si>
@@ -644,6 +635,16 @@
   <si>
     <t>~ Payback $100 to Mom
 ~ Payback $670.4 to Mom (HKTVmall Online Shopping)</t>
+  </si>
+  <si>
+    <t>~ OK Store buy additional 1 packet cigarette 20/07 - $78
+~ Additional transport fees for e-cigarette 20/07 - $40
+~ HKTVmall - Microsoft Office 365 1 year subscribtion 30/07 - $299
+~ Round Trip to Kowloon East Hospital 03/08 - $4
+~ Round Trip to Kwai Chung Eldery Hospital 05/08 - $3.5
+~ Round Trip to Kwai Chung Eldery Hospital 16/08 - $3.5
+~ OK Store buy additional 1 packet cigarette 18/08 - $78
+~ Single Trip from chuk yuen to Temple Mall 19/08 - $2</t>
   </si>
 </sst>
 </file>
@@ -1170,77 +1171,20 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1248,10 +1192,10 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1278,10 +1222,94 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1296,38 +1324,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1646,13 +1647,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1797,7 +1798,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="9">
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -1829,7 +1830,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>26.6</v>
+        <v>24.6</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1882,13 +1883,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1916,10 +1917,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="56"/>
+      <c r="D11" s="87"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1931,10 +1932,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="90" t="s">
+      <c r="C12" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="90"/>
+      <c r="D12" s="105"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1946,10 +1947,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="91" t="s">
+      <c r="C13" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="91"/>
+      <c r="D13" s="106"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1959,10 +1960,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="59"/>
+      <c r="D14" s="82"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -1972,10 +1973,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="59"/>
+      <c r="D15" s="82"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -1985,10 +1986,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="59"/>
+      <c r="D16" s="82"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2000,10 +2001,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="92" t="s">
+      <c r="C17" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="92"/>
+      <c r="D17" s="101"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2013,10 +2014,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="93" t="s">
+      <c r="C18" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="93"/>
+      <c r="D18" s="102"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2028,10 +2029,10 @@
       <c r="B19" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="94" t="s">
+      <c r="C19" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="94"/>
+      <c r="D19" s="103"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2052,13 +2053,13 @@
       <c r="B21" s="25"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2086,10 +2087,10 @@
       <c r="B23" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="95" t="s">
+      <c r="C23" s="104" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="95"/>
+      <c r="D23" s="104"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2101,10 +2102,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="59"/>
+      <c r="D24" s="82"/>
       <c r="E24" s="30">
         <v>2485</v>
       </c>
@@ -2116,10 +2117,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="59"/>
+      <c r="D25" s="82"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2129,10 +2130,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="89" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="92"/>
+      <c r="D26" s="101"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2144,10 +2145,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="93" t="s">
+      <c r="C27" s="102" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="93"/>
+      <c r="D27" s="102"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2157,10 +2158,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="96" t="s">
+      <c r="C28" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="96"/>
+      <c r="D28" s="90"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2182,13 +2183,13 @@
       <c r="B30" s="25"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="60" t="s">
+      <c r="A31" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="60"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
+      <c r="B31" s="84"/>
+      <c r="C31" s="84"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="84"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2216,10 +2217,10 @@
       <c r="B32" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="61" t="s">
+      <c r="C32" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="61"/>
+      <c r="D32" s="81"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2231,10 +2232,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="59"/>
+      <c r="D33" s="82"/>
       <c r="E33" s="34">
         <v>2485</v>
       </c>
@@ -2244,10 +2245,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="59" t="s">
+      <c r="C34" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="59"/>
+      <c r="D34" s="82"/>
       <c r="E34" s="34">
         <v>118</v>
       </c>
@@ -2257,10 +2258,10 @@
       <c r="B35" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="97" t="s">
+      <c r="C35" s="98" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="98"/>
+      <c r="D35" s="99"/>
       <c r="E35" s="34">
         <v>170</v>
       </c>
@@ -2270,10 +2271,10 @@
       <c r="B36" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="97" t="s">
+      <c r="C36" s="98" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="99"/>
+      <c r="D36" s="100"/>
       <c r="E36" s="34">
         <v>800</v>
       </c>
@@ -2283,10 +2284,10 @@
       <c r="B37" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="58" t="s">
+      <c r="C37" s="89" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="59"/>
+      <c r="D37" s="82"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2308,11 +2309,11 @@
       <c r="B39" s="25"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="62" t="s">
+      <c r="A40" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="62"/>
-      <c r="C40" s="62"/>
+      <c r="B40" s="83"/>
+      <c r="C40" s="83"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2327,11 +2328,11 @@
       <c r="D41" s="38"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="63" t="s">
+      <c r="A42" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="63"/>
-      <c r="C42" s="63"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="51" t="s">
@@ -2377,16 +2378,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="64" t="s">
+      <c r="A47" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="64"/>
-      <c r="C47" s="64"/>
+      <c r="B47" s="79"/>
+      <c r="C47" s="79"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="64"/>
-      <c r="B48" s="64"/>
-      <c r="C48" s="64"/>
+      <c r="A48" s="79"/>
+      <c r="B48" s="79"/>
+      <c r="C48" s="79"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2435,11 +2436,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="63" t="s">
+      <c r="A54" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="63"/>
-      <c r="C54" s="63"/>
+      <c r="B54" s="80"/>
+      <c r="C54" s="80"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2474,11 +2475,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="63" t="s">
+      <c r="A58" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="63"/>
-      <c r="C58" s="63"/>
+      <c r="B58" s="80"/>
+      <c r="C58" s="80"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2502,11 +2503,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="63" t="s">
+      <c r="A61" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="63"/>
-      <c r="C61" s="63"/>
+      <c r="B61" s="80"/>
+      <c r="C61" s="80"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2530,11 +2531,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="65" t="s">
+      <c r="A64" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="65"/>
-      <c r="C64" s="65"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="77"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2611,11 +2612,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="65" t="s">
+      <c r="A72" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="65"/>
-      <c r="C72" s="65"/>
+      <c r="B72" s="77"/>
+      <c r="C72" s="77"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2665,167 +2666,167 @@
       <c r="B78" s="25"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="66" t="s">
+      <c r="A79" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="B79" s="66"/>
-      <c r="C79" s="66"/>
-      <c r="D79" s="66"/>
-      <c r="E79" s="66"/>
+      <c r="B79" s="62"/>
+      <c r="C79" s="62"/>
+      <c r="D79" s="62"/>
+      <c r="E79" s="62"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="67" t="s">
+      <c r="A80" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="67"/>
-      <c r="C80" s="67" t="s">
+      <c r="B80" s="78"/>
+      <c r="C80" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="67"/>
+      <c r="D80" s="78"/>
       <c r="E80" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="100" t="s">
+      <c r="A81" s="94" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="100"/>
-      <c r="C81" s="69"/>
-      <c r="D81" s="69"/>
+      <c r="B81" s="94"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="69" t="s">
+      <c r="A82" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="69"/>
-      <c r="C82" s="101" t="s">
+      <c r="B82" s="57"/>
+      <c r="C82" s="95" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="101"/>
+      <c r="D82" s="95"/>
       <c r="E82" s="46">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="69"/>
-      <c r="B83" s="69"/>
-      <c r="C83" s="101" t="s">
+      <c r="A83" s="57"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="95" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="101"/>
+      <c r="D83" s="95"/>
       <c r="E83" s="46">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="69"/>
-      <c r="B84" s="69"/>
-      <c r="C84" s="101" t="s">
+      <c r="A84" s="57"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="95" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="101"/>
+      <c r="D84" s="95"/>
       <c r="E84" s="46">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="69"/>
-      <c r="B85" s="69"/>
-      <c r="C85" s="102" t="s">
+      <c r="A85" s="57"/>
+      <c r="B85" s="57"/>
+      <c r="C85" s="96" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="102"/>
+      <c r="D85" s="96"/>
       <c r="E85" s="46">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="69"/>
-      <c r="B86" s="69"/>
-      <c r="C86" s="74" t="s">
+      <c r="A86" s="57"/>
+      <c r="B86" s="57"/>
+      <c r="C86" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="74"/>
+      <c r="D86" s="75"/>
       <c r="E86" s="46">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="69"/>
-      <c r="B87" s="69"/>
-      <c r="C87" s="102" t="s">
+      <c r="A87" s="57"/>
+      <c r="B87" s="57"/>
+      <c r="C87" s="96" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="102"/>
+      <c r="D87" s="96"/>
       <c r="E87" s="46">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="69"/>
-      <c r="B88" s="69"/>
-      <c r="C88" s="101" t="s">
+      <c r="A88" s="57"/>
+      <c r="B88" s="57"/>
+      <c r="C88" s="95" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="101"/>
+      <c r="D88" s="95"/>
       <c r="E88" s="46">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="69"/>
-      <c r="B89" s="69"/>
-      <c r="C89" s="74" t="s">
+      <c r="A89" s="57"/>
+      <c r="B89" s="57"/>
+      <c r="C89" s="75" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="74"/>
+      <c r="D89" s="75"/>
       <c r="E89" s="46">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="69"/>
-      <c r="B90" s="69"/>
-      <c r="C90" s="74" t="s">
+      <c r="A90" s="57"/>
+      <c r="B90" s="57"/>
+      <c r="C90" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="74"/>
+      <c r="D90" s="75"/>
       <c r="E90" s="46">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="69"/>
-      <c r="B91" s="69"/>
-      <c r="C91" s="103" t="s">
+      <c r="A91" s="57"/>
+      <c r="B91" s="57"/>
+      <c r="C91" s="97" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="103"/>
+      <c r="D91" s="97"/>
       <c r="E91" s="46">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="70" t="s">
+      <c r="A92" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="70"/>
-      <c r="C92" s="75"/>
-      <c r="D92" s="75"/>
+      <c r="B92" s="72"/>
+      <c r="C92" s="76"/>
+      <c r="D92" s="76"/>
       <c r="E92" s="47">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="76" t="s">
+      <c r="C93" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="76"/>
+      <c r="D93" s="71"/>
       <c r="E93" s="48">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2833,113 +2834,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="66" t="s">
+      <c r="A95" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="B95" s="66"/>
-      <c r="C95" s="66"/>
-      <c r="D95" s="66"/>
-      <c r="E95" s="66"/>
+      <c r="B95" s="62"/>
+      <c r="C95" s="62"/>
+      <c r="D95" s="62"/>
+      <c r="E95" s="62"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="66" t="s">
+      <c r="A96" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="66"/>
-      <c r="C96" s="66" t="s">
+      <c r="B96" s="62"/>
+      <c r="C96" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="66"/>
+      <c r="D96" s="62"/>
       <c r="E96" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="68" t="s">
+      <c r="A97" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="68"/>
-      <c r="C97" s="77"/>
-      <c r="D97" s="77"/>
+      <c r="B97" s="55"/>
+      <c r="C97" s="56"/>
+      <c r="D97" s="56"/>
       <c r="E97" s="48">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="69" t="s">
+      <c r="A98" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="69"/>
-      <c r="C98" s="73" t="s">
+      <c r="B98" s="57"/>
+      <c r="C98" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="73"/>
+      <c r="D98" s="74"/>
       <c r="E98" s="49">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="69"/>
-      <c r="B99" s="69"/>
-      <c r="C99" s="71" t="s">
+      <c r="A99" s="57"/>
+      <c r="B99" s="57"/>
+      <c r="C99" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="71"/>
+      <c r="D99" s="58"/>
       <c r="E99" s="49">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="69"/>
-      <c r="B100" s="69"/>
-      <c r="C100" s="71" t="s">
+      <c r="A100" s="57"/>
+      <c r="B100" s="57"/>
+      <c r="C100" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="71"/>
+      <c r="D100" s="58"/>
       <c r="E100" s="49">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="69"/>
-      <c r="B101" s="69"/>
-      <c r="C101" s="71" t="s">
+      <c r="A101" s="57"/>
+      <c r="B101" s="57"/>
+      <c r="C101" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="71"/>
+      <c r="D101" s="58"/>
       <c r="E101" s="49">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="69"/>
-      <c r="B102" s="69"/>
-      <c r="C102" s="82" t="s">
+      <c r="A102" s="57"/>
+      <c r="B102" s="57"/>
+      <c r="C102" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="104"/>
+      <c r="D102" s="93"/>
       <c r="E102" s="49">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="69" t="s">
+      <c r="A103" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="69"/>
-      <c r="C103" s="77"/>
-      <c r="D103" s="77"/>
+      <c r="B103" s="57"/>
+      <c r="C103" s="56"/>
+      <c r="D103" s="56"/>
       <c r="E103" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="80" t="s">
+      <c r="C104" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="80"/>
+      <c r="D104" s="54"/>
       <c r="E104" s="48">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2960,91 +2961,91 @@
       <c r="E106" s="50"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="81" t="s">
+      <c r="A107" s="61" t="s">
         <v>128</v>
       </c>
-      <c r="B107" s="81"/>
-      <c r="C107" s="81"/>
-      <c r="D107" s="81"/>
-      <c r="E107" s="81"/>
+      <c r="B107" s="61"/>
+      <c r="C107" s="61"/>
+      <c r="D107" s="61"/>
+      <c r="E107" s="61"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="66" t="s">
+      <c r="A108" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="66"/>
-      <c r="C108" s="66" t="s">
+      <c r="B108" s="62"/>
+      <c r="C108" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="66"/>
+      <c r="D108" s="62"/>
       <c r="E108" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="68" t="s">
+      <c r="A109" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="68"/>
-      <c r="C109" s="77"/>
-      <c r="D109" s="77"/>
+      <c r="B109" s="55"/>
+      <c r="C109" s="56"/>
+      <c r="D109" s="56"/>
       <c r="E109" s="48">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="84" t="s">
+      <c r="A110" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="85"/>
-      <c r="C110" s="96" t="s">
+      <c r="B110" s="66"/>
+      <c r="C110" s="90" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="96"/>
+      <c r="D110" s="90"/>
       <c r="E110" s="46">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="86"/>
-      <c r="B111" s="87"/>
-      <c r="C111" s="105" t="s">
+      <c r="A111" s="67"/>
+      <c r="B111" s="68"/>
+      <c r="C111" s="91" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="106"/>
+      <c r="D111" s="92"/>
       <c r="E111" s="46">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="88"/>
-      <c r="B112" s="89"/>
-      <c r="C112" s="82" t="s">
+      <c r="A112" s="69"/>
+      <c r="B112" s="70"/>
+      <c r="C112" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="104"/>
+      <c r="D112" s="93"/>
       <c r="E112" s="46">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="69" t="s">
+      <c r="A113" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="69"/>
-      <c r="C113" s="77"/>
-      <c r="D113" s="77"/>
+      <c r="B113" s="57"/>
+      <c r="C113" s="56"/>
+      <c r="D113" s="56"/>
       <c r="E113" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="80" t="s">
+      <c r="C114" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="80"/>
+      <c r="D114" s="54"/>
       <c r="E114" s="48">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6796,35 +6797,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6838,42 +6846,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6913,13 +6914,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="85" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7069,7 +7070,7 @@
       </c>
       <c r="C7" s="9">
         <f>'April 2026 - June 2026'!C7</f>
-        <v>13.8</v>
+        <v>11.8</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -7101,7 +7102,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>26.6</v>
+        <v>24.6</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7154,13 +7155,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="86" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7188,10 +7189,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="56"/>
+      <c r="D11" s="87"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7203,10 +7204,10 @@
       <c r="B12" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="88" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="57"/>
+      <c r="D12" s="88"/>
       <c r="E12" s="53">
         <v>2485</v>
       </c>
@@ -7218,10 +7219,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="59"/>
+      <c r="D13" s="82"/>
       <c r="E13" s="30">
         <v>55</v>
       </c>
@@ -7233,10 +7234,10 @@
       <c r="B14" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="58" t="s">
-        <v>136</v>
-      </c>
-      <c r="D14" s="59"/>
+      <c r="C14" s="89" t="s">
+        <v>135</v>
+      </c>
+      <c r="D14" s="82"/>
       <c r="E14" s="30">
         <v>770.4</v>
       </c>
@@ -7257,13 +7258,13 @@
       <c r="B16" s="25"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="84" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
+      <c r="B17" s="84"/>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7291,25 +7292,25 @@
       <c r="B18" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="61"/>
+      <c r="D18" s="81"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="51" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="59"/>
+      <c r="D19" s="82"/>
       <c r="E19" s="30">
         <v>2485</v>
       </c>
@@ -7317,8 +7318,8 @@
     <row r="20" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
       <c r="E20" s="30">
         <v>0</v>
       </c>
@@ -7340,13 +7341,13 @@
       <c r="B22" s="25"/>
     </row>
     <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="60" t="s">
+      <c r="A23" s="84" t="s">
         <v>105</v>
       </c>
-      <c r="B23" s="60"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
+      <c r="B23" s="84"/>
+      <c r="C23" s="84"/>
+      <c r="D23" s="84"/>
+      <c r="E23" s="84"/>
       <c r="G23" s="11"/>
       <c r="H23" s="11"/>
       <c r="I23" s="11"/>
@@ -7374,25 +7375,25 @@
       <c r="B24" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="61" t="s">
+      <c r="C24" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="61"/>
+      <c r="D24" s="81"/>
       <c r="E24" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="51" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D25" s="59"/>
+      <c r="D25" s="82"/>
       <c r="E25" s="34">
         <v>2485</v>
       </c>
@@ -7400,8 +7401,8 @@
     <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
-      <c r="C26" s="59"/>
-      <c r="D26" s="59"/>
+      <c r="C26" s="82"/>
+      <c r="D26" s="82"/>
       <c r="E26" s="30">
         <v>0</v>
       </c>
@@ -7423,11 +7424,11 @@
       <c r="B28" s="25"/>
     </row>
     <row r="29" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="62" t="s">
+      <c r="A29" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="B29" s="62"/>
-      <c r="C29" s="62"/>
+      <c r="B29" s="83"/>
+      <c r="C29" s="83"/>
     </row>
     <row r="30" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -7442,11 +7443,11 @@
       <c r="D30" s="38"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
+      <c r="B31" s="80"/>
+      <c r="C31" s="80"/>
     </row>
     <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="51" t="s">
@@ -7492,16 +7493,16 @@
       </c>
     </row>
     <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="64" t="s">
+      <c r="A36" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="B36" s="64"/>
-      <c r="C36" s="64"/>
+      <c r="B36" s="79"/>
+      <c r="C36" s="79"/>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="64"/>
-      <c r="B37" s="64"/>
-      <c r="C37" s="64"/>
+      <c r="A37" s="79"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="79"/>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
@@ -7550,11 +7551,11 @@
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="63" t="s">
+      <c r="A43" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="B43" s="63"/>
-      <c r="C43" s="63"/>
+      <c r="B43" s="80"/>
+      <c r="C43" s="80"/>
     </row>
     <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
@@ -7589,11 +7590,11 @@
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="63" t="s">
+      <c r="A47" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="63"/>
-      <c r="C47" s="63"/>
+      <c r="B47" s="80"/>
+      <c r="C47" s="80"/>
     </row>
     <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
@@ -7617,11 +7618,11 @@
       </c>
     </row>
     <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="63" t="s">
+      <c r="A50" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="63"/>
-      <c r="C50" s="63"/>
+      <c r="B50" s="80"/>
+      <c r="C50" s="80"/>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
@@ -7645,11 +7646,11 @@
       </c>
     </row>
     <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="65" t="s">
+      <c r="A53" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="65"/>
-      <c r="C53" s="65"/>
+      <c r="B53" s="77"/>
+      <c r="C53" s="77"/>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="17" t="s">
@@ -7726,11 +7727,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="65" t="s">
+      <c r="A61" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="B61" s="65"/>
-      <c r="C61" s="65"/>
+      <c r="B61" s="77"/>
+      <c r="C61" s="77"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7" t="s">
@@ -7780,195 +7781,195 @@
       <c r="B67" s="25"/>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="66" t="s">
+      <c r="A68" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="B68" s="66"/>
-      <c r="C68" s="66"/>
-      <c r="D68" s="66"/>
-      <c r="E68" s="66"/>
+      <c r="B68" s="62"/>
+      <c r="C68" s="62"/>
+      <c r="D68" s="62"/>
+      <c r="E68" s="62"/>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="67" t="s">
+      <c r="A69" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="B69" s="67"/>
-      <c r="C69" s="67" t="s">
+      <c r="B69" s="78"/>
+      <c r="C69" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D69" s="67"/>
+      <c r="D69" s="78"/>
       <c r="E69" s="45" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="68" t="s">
+      <c r="A70" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="B70" s="68"/>
-      <c r="C70" s="69"/>
-      <c r="D70" s="69"/>
+      <c r="B70" s="55"/>
+      <c r="C70" s="57"/>
+      <c r="D70" s="57"/>
       <c r="E70" s="48">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="70" t="s">
+      <c r="A71" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="B71" s="70"/>
-      <c r="C71" s="71" t="s">
+      <c r="B71" s="72"/>
+      <c r="C71" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="D71" s="71"/>
+      <c r="D71" s="58"/>
       <c r="E71" s="46">
         <v>600</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="70"/>
-      <c r="B72" s="70"/>
-      <c r="C72" s="72" t="s">
-        <v>137</v>
-      </c>
-      <c r="D72" s="73"/>
+      <c r="A72" s="72"/>
+      <c r="B72" s="72"/>
+      <c r="C72" s="73" t="s">
+        <v>136</v>
+      </c>
+      <c r="D72" s="74"/>
       <c r="E72" s="46">
         <v>1117.5</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="133" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="70"/>
-      <c r="B73" s="70"/>
-      <c r="C73" s="72" t="s">
-        <v>133</v>
-      </c>
-      <c r="D73" s="74"/>
+    <row r="73" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="72"/>
+      <c r="B73" s="72"/>
+      <c r="C73" s="73" t="s">
+        <v>139</v>
+      </c>
+      <c r="D73" s="75"/>
       <c r="E73" s="46">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="70" t="s">
+      <c r="A74" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="B74" s="70"/>
-      <c r="C74" s="75"/>
-      <c r="D74" s="75"/>
+      <c r="B74" s="72"/>
+      <c r="C74" s="76"/>
+      <c r="D74" s="76"/>
       <c r="E74" s="47">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C75" s="76" t="s">
+      <c r="C75" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="D75" s="76"/>
+      <c r="D75" s="71"/>
       <c r="E75" s="48">
         <f>(E15+E70)-SUM(E71:E74)</f>
-        <v>26.599999999999909</v>
+        <v>24.599999999999909</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="66" t="s">
+      <c r="A77" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="B77" s="66"/>
-      <c r="C77" s="66"/>
-      <c r="D77" s="66"/>
-      <c r="E77" s="66"/>
+      <c r="B77" s="62"/>
+      <c r="C77" s="62"/>
+      <c r="D77" s="62"/>
+      <c r="E77" s="62"/>
     </row>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="66" t="s">
+      <c r="A78" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="B78" s="66"/>
-      <c r="C78" s="66" t="s">
+      <c r="B78" s="62"/>
+      <c r="C78" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D78" s="66"/>
+      <c r="D78" s="62"/>
       <c r="E78" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="68" t="s">
+      <c r="A79" s="55" t="s">
         <v>108</v>
       </c>
-      <c r="B79" s="68"/>
-      <c r="C79" s="77"/>
-      <c r="D79" s="77"/>
+      <c r="B79" s="55"/>
+      <c r="C79" s="56"/>
+      <c r="D79" s="56"/>
       <c r="E79" s="48">
         <f>E75</f>
-        <v>26.599999999999909</v>
+        <v>24.599999999999909</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="84" t="s">
+      <c r="A80" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B80" s="85"/>
-      <c r="C80" s="78" t="s">
-        <v>139</v>
-      </c>
-      <c r="D80" s="79"/>
+      <c r="B80" s="66"/>
+      <c r="C80" s="59" t="s">
+        <v>138</v>
+      </c>
+      <c r="D80" s="60"/>
       <c r="E80" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="86"/>
-      <c r="B81" s="87"/>
-      <c r="C81" s="71" t="s">
-        <v>138</v>
-      </c>
-      <c r="D81" s="71"/>
+      <c r="A81" s="67"/>
+      <c r="B81" s="68"/>
+      <c r="C81" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="D81" s="58"/>
       <c r="E81" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="86"/>
-      <c r="B82" s="87"/>
-      <c r="C82" s="82" t="s">
+      <c r="A82" s="67"/>
+      <c r="B82" s="68"/>
+      <c r="C82" s="63" t="s">
         <v>132</v>
       </c>
-      <c r="D82" s="83"/>
+      <c r="D82" s="64"/>
       <c r="E82" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="88"/>
-      <c r="B83" s="89"/>
-      <c r="C83" s="83"/>
-      <c r="D83" s="83"/>
+      <c r="A83" s="69"/>
+      <c r="B83" s="70"/>
+      <c r="C83" s="64"/>
+      <c r="D83" s="64"/>
       <c r="E83" s="49">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="69" t="s">
+      <c r="A84" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B84" s="69"/>
-      <c r="C84" s="77"/>
-      <c r="D84" s="77"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="56"/>
+      <c r="D84" s="56"/>
       <c r="E84" s="46">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C85" s="80" t="s">
+      <c r="C85" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="D85" s="80"/>
+      <c r="D85" s="54"/>
       <c r="E85" s="48">
         <f>(E21+E79)-SUM(E80:E84)</f>
-        <v>1340.6</v>
+        <v>1338.6</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7986,72 +7987,72 @@
       <c r="E87" s="50"/>
     </row>
     <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="81" t="s">
+      <c r="A88" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="B88" s="81"/>
-      <c r="C88" s="81"/>
-      <c r="D88" s="81"/>
-      <c r="E88" s="81"/>
+      <c r="B88" s="61"/>
+      <c r="C88" s="61"/>
+      <c r="D88" s="61"/>
+      <c r="E88" s="61"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="66" t="s">
+      <c r="A89" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="B89" s="66"/>
-      <c r="C89" s="66" t="s">
+      <c r="B89" s="62"/>
+      <c r="C89" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D89" s="66"/>
+      <c r="D89" s="62"/>
       <c r="E89" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="68" t="s">
+      <c r="A90" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="B90" s="68"/>
-      <c r="C90" s="77"/>
-      <c r="D90" s="77"/>
+      <c r="B90" s="55"/>
+      <c r="C90" s="56"/>
+      <c r="D90" s="56"/>
       <c r="E90" s="48">
         <f>E85</f>
-        <v>1340.6</v>
+        <v>1338.6</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="69" t="s">
+      <c r="A91" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B91" s="69"/>
-      <c r="C91" s="71" t="s">
+      <c r="B91" s="57"/>
+      <c r="C91" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="D91" s="71"/>
+      <c r="D91" s="58"/>
       <c r="E91" s="46">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="69" t="s">
+      <c r="A92" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="69"/>
-      <c r="C92" s="77"/>
-      <c r="D92" s="77"/>
+      <c r="B92" s="57"/>
+      <c r="C92" s="56"/>
+      <c r="D92" s="56"/>
       <c r="E92" s="46">
         <f>C65</f>
         <v>1171</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="80" t="s">
+      <c r="C93" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="80"/>
+      <c r="D93" s="54"/>
       <c r="E93" s="48">
         <f>(E27+E90)-SUM(E91:E92)</f>
-        <v>2654.6</v>
+        <v>2652.6</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11800,13 +11801,45 @@
     </row>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A36:C37"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="A71:B73"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A77:E77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
     <mergeCell ref="C80:D80"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="A88:E88"/>
@@ -11818,45 +11851,13 @@
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="C84:D84"/>
     <mergeCell ref="A80:B83"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:D78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A71:B73"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="A36:C37"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E70">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18C9A06-3C93-D543-82F9-FBD9CE17E28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A871E8-C30A-464F-AD22-FDE1345E5D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1172,7 +1172,103 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1181,29 +1277,23 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1223,118 +1313,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1654,13 +1654,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1890,13 +1890,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1924,10 +1924,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="86" t="s">
+      <c r="C11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="86"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1939,10 +1939,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="104" t="s">
+      <c r="C12" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="104"/>
+      <c r="D12" s="57"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1954,10 +1954,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="105" t="s">
+      <c r="C13" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="105"/>
+      <c r="D13" s="58"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1967,10 +1967,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="81" t="s">
+      <c r="C14" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="81"/>
+      <c r="D14" s="59"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -1980,10 +1980,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="81" t="s">
+      <c r="C15" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="81"/>
+      <c r="D15" s="59"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -1993,10 +1993,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="81" t="s">
+      <c r="C16" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="81"/>
+      <c r="D16" s="59"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2008,10 +2008,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="100" t="s">
+      <c r="C17" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="100"/>
+      <c r="D17" s="60"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2021,10 +2021,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="101" t="s">
+      <c r="C18" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="101"/>
+      <c r="D18" s="61"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2033,13 +2033,13 @@
       <c r="A19" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="106" t="s">
+      <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="102" t="s">
+      <c r="C19" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="102"/>
+      <c r="D19" s="62"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2060,13 +2060,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="83" t="s">
+      <c r="A22" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="83"/>
-      <c r="C22" s="83"/>
-      <c r="D22" s="83"/>
-      <c r="E22" s="83"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2094,10 +2094,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="103" t="s">
+      <c r="C23" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="103"/>
+      <c r="D23" s="64"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2109,10 +2109,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="81" t="s">
+      <c r="C24" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="81"/>
+      <c r="D24" s="59"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2124,10 +2124,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="81" t="s">
+      <c r="C25" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="81"/>
+      <c r="D25" s="59"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2137,10 +2137,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="88" t="s">
+      <c r="C26" s="65" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="100"/>
+      <c r="D26" s="60"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2152,10 +2152,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="101" t="s">
+      <c r="C27" s="61" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="101"/>
+      <c r="D27" s="61"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2165,10 +2165,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="89" t="s">
+      <c r="C28" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="89"/>
+      <c r="D28" s="66"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2190,13 +2190,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="83" t="s">
+      <c r="A31" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="83"/>
-      <c r="C31" s="83"/>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2224,10 +2224,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="80" t="s">
+      <c r="C32" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="80"/>
+      <c r="D32" s="67"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2239,10 +2239,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="81"/>
+      <c r="D33" s="59"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2252,10 +2252,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="81" t="s">
+      <c r="C34" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="81"/>
+      <c r="D34" s="59"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2265,10 +2265,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="97" t="s">
+      <c r="C35" s="68" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="98"/>
+      <c r="D35" s="69"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2278,10 +2278,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="97" t="s">
+      <c r="C36" s="68" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="99"/>
+      <c r="D36" s="70"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2291,10 +2291,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="88" t="s">
+      <c r="C37" s="65" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="81"/>
+      <c r="D37" s="59"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2316,11 +2316,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="82" t="s">
+      <c r="A40" s="71" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="82"/>
-      <c r="C40" s="82"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="71"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2335,11 +2335,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="79" t="s">
+      <c r="A42" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="79"/>
-      <c r="C42" s="79"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="72"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2385,16 +2385,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="78" t="s">
+      <c r="A47" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="78"/>
-      <c r="C47" s="78"/>
+      <c r="B47" s="73"/>
+      <c r="C47" s="73"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="78"/>
-      <c r="B48" s="78"/>
-      <c r="C48" s="78"/>
+      <c r="A48" s="73"/>
+      <c r="B48" s="73"/>
+      <c r="C48" s="73"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2443,11 +2443,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="79" t="s">
+      <c r="A54" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="79"/>
-      <c r="C54" s="79"/>
+      <c r="B54" s="72"/>
+      <c r="C54" s="72"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2482,11 +2482,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="79" t="s">
+      <c r="A58" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="79"/>
-      <c r="C58" s="79"/>
+      <c r="B58" s="72"/>
+      <c r="C58" s="72"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2510,11 +2510,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="79" t="s">
+      <c r="A61" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="79"/>
-      <c r="C61" s="79"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="72"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2538,11 +2538,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="76" t="s">
+      <c r="A64" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="76"/>
-      <c r="C64" s="76"/>
+      <c r="B64" s="74"/>
+      <c r="C64" s="74"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2619,11 +2619,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="76" t="s">
+      <c r="A72" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="76"/>
-      <c r="C72" s="76"/>
+      <c r="B72" s="74"/>
+      <c r="C72" s="74"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="B73" s="7"/>
       <c r="C73" s="19">
-        <v>770.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C75" s="19">
         <f>SUM(C73:C74)</f>
-        <v>770.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -2673,167 +2673,167 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="61" t="s">
+      <c r="A79" s="75" t="s">
         <v>126</v>
       </c>
-      <c r="B79" s="61"/>
-      <c r="C79" s="61"/>
-      <c r="D79" s="61"/>
-      <c r="E79" s="61"/>
+      <c r="B79" s="75"/>
+      <c r="C79" s="75"/>
+      <c r="D79" s="75"/>
+      <c r="E79" s="75"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="77" t="s">
+      <c r="A80" s="76" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="77"/>
-      <c r="C80" s="77" t="s">
+      <c r="B80" s="76"/>
+      <c r="C80" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="77"/>
+      <c r="D80" s="76"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="93" t="s">
+      <c r="A81" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="93"/>
-      <c r="C81" s="56"/>
-      <c r="D81" s="56"/>
+      <c r="B81" s="77"/>
+      <c r="C81" s="78"/>
+      <c r="D81" s="78"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="56" t="s">
+      <c r="A82" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="56"/>
-      <c r="C82" s="94" t="s">
+      <c r="B82" s="78"/>
+      <c r="C82" s="79" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="94"/>
+      <c r="D82" s="79"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="56"/>
-      <c r="B83" s="56"/>
-      <c r="C83" s="94" t="s">
+      <c r="A83" s="78"/>
+      <c r="B83" s="78"/>
+      <c r="C83" s="79" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="94"/>
+      <c r="D83" s="79"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="56"/>
-      <c r="B84" s="56"/>
-      <c r="C84" s="94" t="s">
+      <c r="A84" s="78"/>
+      <c r="B84" s="78"/>
+      <c r="C84" s="79" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="94"/>
+      <c r="D84" s="79"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="56"/>
-      <c r="B85" s="56"/>
-      <c r="C85" s="95" t="s">
+      <c r="A85" s="78"/>
+      <c r="B85" s="78"/>
+      <c r="C85" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="95"/>
+      <c r="D85" s="80"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="56"/>
-      <c r="B86" s="56"/>
-      <c r="C86" s="74" t="s">
+      <c r="A86" s="78"/>
+      <c r="B86" s="78"/>
+      <c r="C86" s="81" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="74"/>
+      <c r="D86" s="81"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="56"/>
-      <c r="B87" s="56"/>
-      <c r="C87" s="95" t="s">
+      <c r="A87" s="78"/>
+      <c r="B87" s="78"/>
+      <c r="C87" s="80" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="95"/>
+      <c r="D87" s="80"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="56"/>
-      <c r="B88" s="56"/>
-      <c r="C88" s="94" t="s">
+      <c r="A88" s="78"/>
+      <c r="B88" s="78"/>
+      <c r="C88" s="79" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="94"/>
+      <c r="D88" s="79"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="56"/>
-      <c r="B89" s="56"/>
-      <c r="C89" s="74" t="s">
+      <c r="A89" s="78"/>
+      <c r="B89" s="78"/>
+      <c r="C89" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="74"/>
+      <c r="D89" s="81"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="56"/>
-      <c r="B90" s="56"/>
-      <c r="C90" s="74" t="s">
+      <c r="A90" s="78"/>
+      <c r="B90" s="78"/>
+      <c r="C90" s="81" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="74"/>
+      <c r="D90" s="81"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="56"/>
-      <c r="B91" s="56"/>
-      <c r="C91" s="96" t="s">
+      <c r="A91" s="78"/>
+      <c r="B91" s="78"/>
+      <c r="C91" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="96"/>
+      <c r="D91" s="82"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="71" t="s">
+      <c r="A92" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="71"/>
-      <c r="C92" s="75"/>
-      <c r="D92" s="75"/>
+      <c r="B92" s="83"/>
+      <c r="C92" s="84"/>
+      <c r="D92" s="84"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="70" t="s">
+      <c r="C93" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="70"/>
+      <c r="D93" s="85"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2841,113 +2841,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="61" t="s">
+      <c r="A95" s="75" t="s">
         <v>127</v>
       </c>
-      <c r="B95" s="61"/>
-      <c r="C95" s="61"/>
-      <c r="D95" s="61"/>
-      <c r="E95" s="61"/>
+      <c r="B95" s="75"/>
+      <c r="C95" s="75"/>
+      <c r="D95" s="75"/>
+      <c r="E95" s="75"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="61" t="s">
+      <c r="A96" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="61"/>
-      <c r="C96" s="61" t="s">
+      <c r="B96" s="75"/>
+      <c r="C96" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="61"/>
+      <c r="D96" s="75"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="54" t="s">
+      <c r="A97" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="54"/>
-      <c r="C97" s="55"/>
-      <c r="D97" s="55"/>
+      <c r="B97" s="86"/>
+      <c r="C97" s="87"/>
+      <c r="D97" s="87"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="56" t="s">
+      <c r="A98" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="56"/>
-      <c r="C98" s="73" t="s">
+      <c r="B98" s="78"/>
+      <c r="C98" s="88" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="73"/>
+      <c r="D98" s="88"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="56"/>
-      <c r="B99" s="56"/>
-      <c r="C99" s="57" t="s">
+      <c r="A99" s="78"/>
+      <c r="B99" s="78"/>
+      <c r="C99" s="89" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="57"/>
+      <c r="D99" s="89"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="56"/>
-      <c r="B100" s="56"/>
-      <c r="C100" s="57" t="s">
+      <c r="A100" s="78"/>
+      <c r="B100" s="78"/>
+      <c r="C100" s="89" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="57"/>
+      <c r="D100" s="89"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="56"/>
-      <c r="B101" s="56"/>
-      <c r="C101" s="57" t="s">
+      <c r="A101" s="78"/>
+      <c r="B101" s="78"/>
+      <c r="C101" s="89" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="57"/>
+      <c r="D101" s="89"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="56"/>
-      <c r="B102" s="56"/>
-      <c r="C102" s="62" t="s">
+      <c r="A102" s="78"/>
+      <c r="B102" s="78"/>
+      <c r="C102" s="90" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="92"/>
+      <c r="D102" s="91"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="56" t="s">
+      <c r="A103" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="56"/>
-      <c r="C103" s="55"/>
-      <c r="D103" s="55"/>
+      <c r="B103" s="78"/>
+      <c r="C103" s="87"/>
+      <c r="D103" s="87"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="53" t="s">
+      <c r="C104" s="92" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="53"/>
+      <c r="D104" s="92"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2968,91 +2968,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="60" t="s">
+      <c r="A107" s="93" t="s">
         <v>128</v>
       </c>
-      <c r="B107" s="60"/>
-      <c r="C107" s="60"/>
-      <c r="D107" s="60"/>
-      <c r="E107" s="60"/>
+      <c r="B107" s="93"/>
+      <c r="C107" s="93"/>
+      <c r="D107" s="93"/>
+      <c r="E107" s="93"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="61" t="s">
+      <c r="A108" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="61"/>
-      <c r="C108" s="61" t="s">
+      <c r="B108" s="75"/>
+      <c r="C108" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="61"/>
+      <c r="D108" s="75"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="54" t="s">
+      <c r="A109" s="86" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="54"/>
-      <c r="C109" s="55"/>
-      <c r="D109" s="55"/>
+      <c r="B109" s="86"/>
+      <c r="C109" s="87"/>
+      <c r="D109" s="87"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="64" t="s">
+      <c r="A110" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="65"/>
-      <c r="C110" s="89" t="s">
+      <c r="B110" s="95"/>
+      <c r="C110" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="89"/>
+      <c r="D110" s="66"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="66"/>
-      <c r="B111" s="67"/>
-      <c r="C111" s="90" t="s">
+      <c r="A111" s="96"/>
+      <c r="B111" s="97"/>
+      <c r="C111" s="100" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="91"/>
+      <c r="D111" s="101"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="68"/>
-      <c r="B112" s="69"/>
-      <c r="C112" s="62" t="s">
+      <c r="A112" s="98"/>
+      <c r="B112" s="99"/>
+      <c r="C112" s="90" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="92"/>
+      <c r="D112" s="91"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="56" t="s">
+      <c r="A113" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="56"/>
-      <c r="C113" s="55"/>
-      <c r="D113" s="55"/>
+      <c r="B113" s="78"/>
+      <c r="C113" s="87"/>
+      <c r="D113" s="87"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="53" t="s">
+      <c r="C114" s="92" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="53"/>
+      <c r="D114" s="92"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6804,42 +6804,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6853,35 +6846,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6921,13 +6921,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -7162,13 +7162,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="85"/>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7196,10 +7196,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="86" t="s">
+      <c r="C11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="86"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7211,10 +7211,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="87" t="s">
+      <c r="C12" s="102" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="87"/>
+      <c r="D12" s="102"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7226,10 +7226,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="81" t="s">
+      <c r="C13" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="81"/>
+      <c r="D13" s="59"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7241,10 +7241,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="C14" s="65" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="81"/>
+      <c r="D14" s="59"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7265,13 +7265,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="83" t="s">
+      <c r="A17" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7299,10 +7299,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="80" t="s">
+      <c r="C18" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="80"/>
+      <c r="D18" s="67"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7314,10 +7314,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="81" t="s">
+      <c r="C19" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="81"/>
+      <c r="D19" s="59"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7329,10 +7329,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="107" t="s">
+      <c r="C20" s="103" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="98"/>
+      <c r="D20" s="69"/>
       <c r="E20" s="29">
         <v>50</v>
       </c>
@@ -7340,8 +7340,8 @@
     <row r="21" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
-      <c r="C21" s="81"/>
-      <c r="D21" s="81"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
       <c r="E21" s="29">
         <v>0</v>
       </c>
@@ -7363,13 +7363,13 @@
       <c r="B23" s="24"/>
     </row>
     <row r="24" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="83" t="s">
+      <c r="A24" s="63" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="83"/>
-      <c r="C24" s="83"/>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
+      <c r="B24" s="63"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="63"/>
+      <c r="E24" s="63"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
@@ -7397,10 +7397,10 @@
       <c r="B25" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="80" t="s">
+      <c r="C25" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="80"/>
+      <c r="D25" s="67"/>
       <c r="E25" s="2" t="s">
         <v>12</v>
       </c>
@@ -7412,10 +7412,10 @@
       <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="81" t="s">
+      <c r="C26" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="81"/>
+      <c r="D26" s="59"/>
       <c r="E26" s="33">
         <v>2485</v>
       </c>
@@ -7423,8 +7423,8 @@
     <row r="27" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
-      <c r="C27" s="81"/>
-      <c r="D27" s="81"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
       <c r="E27" s="29">
         <v>0</v>
       </c>
@@ -7446,11 +7446,11 @@
       <c r="B29" s="24"/>
     </row>
     <row r="30" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="82" t="s">
+      <c r="A30" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="82"/>
-      <c r="C30" s="82"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="71"/>
     </row>
     <row r="31" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
@@ -7465,11 +7465,11 @@
       <c r="D31" s="37"/>
     </row>
     <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="79" t="s">
+      <c r="A32" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="79"/>
-      <c r="C32" s="79"/>
+      <c r="B32" s="72"/>
+      <c r="C32" s="72"/>
     </row>
     <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="50" t="s">
@@ -7515,16 +7515,16 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="78" t="s">
+      <c r="A37" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="78"/>
-      <c r="C37" s="78"/>
+      <c r="B37" s="73"/>
+      <c r="C37" s="73"/>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="78"/>
-      <c r="B38" s="78"/>
-      <c r="C38" s="78"/>
+      <c r="A38" s="73"/>
+      <c r="B38" s="73"/>
+      <c r="C38" s="73"/>
     </row>
     <row r="39" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
@@ -7573,11 +7573,11 @@
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="79" t="s">
+      <c r="A44" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="B44" s="79"/>
-      <c r="C44" s="79"/>
+      <c r="B44" s="72"/>
+      <c r="C44" s="72"/>
     </row>
     <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
@@ -7612,11 +7612,11 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="79" t="s">
+      <c r="A48" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="79"/>
-      <c r="C48" s="79"/>
+      <c r="B48" s="72"/>
+      <c r="C48" s="72"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -7640,11 +7640,11 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="79" t="s">
+      <c r="A51" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="79"/>
-      <c r="C51" s="79"/>
+      <c r="B51" s="72"/>
+      <c r="C51" s="72"/>
     </row>
     <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
@@ -7668,11 +7668,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="76" t="s">
+      <c r="A54" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="76"/>
-      <c r="C54" s="76"/>
+      <c r="B54" s="74"/>
+      <c r="C54" s="74"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="17" t="s">
@@ -7749,11 +7749,11 @@
       </c>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="76" t="s">
+      <c r="A62" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="B62" s="76"/>
-      <c r="C62" s="76"/>
+      <c r="B62" s="74"/>
+      <c r="C62" s="74"/>
     </row>
     <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="B63" s="7"/>
       <c r="C63" s="19">
-        <v>770.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="C65" s="19">
         <f>SUM(C63:C64)</f>
-        <v>770.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -7803,91 +7803,91 @@
       <c r="B68" s="24"/>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="61" t="s">
+      <c r="A69" s="75" t="s">
         <v>129</v>
       </c>
-      <c r="B69" s="61"/>
-      <c r="C69" s="61"/>
-      <c r="D69" s="61"/>
-      <c r="E69" s="61"/>
+      <c r="B69" s="75"/>
+      <c r="C69" s="75"/>
+      <c r="D69" s="75"/>
+      <c r="E69" s="75"/>
     </row>
     <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="77" t="s">
+      <c r="A70" s="76" t="s">
         <v>83</v>
       </c>
-      <c r="B70" s="77"/>
-      <c r="C70" s="77" t="s">
+      <c r="B70" s="76"/>
+      <c r="C70" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="D70" s="77"/>
+      <c r="D70" s="76"/>
       <c r="E70" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="54" t="s">
+      <c r="A71" s="86" t="s">
         <v>107</v>
       </c>
-      <c r="B71" s="54"/>
-      <c r="C71" s="56"/>
-      <c r="D71" s="56"/>
+      <c r="B71" s="86"/>
+      <c r="C71" s="78"/>
+      <c r="D71" s="78"/>
       <c r="E71" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="71" t="s">
+      <c r="A72" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="B72" s="71"/>
-      <c r="C72" s="57" t="s">
+      <c r="B72" s="83"/>
+      <c r="C72" s="89" t="s">
         <v>122</v>
       </c>
-      <c r="D72" s="57"/>
+      <c r="D72" s="89"/>
       <c r="E72" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="71"/>
-      <c r="B73" s="71"/>
-      <c r="C73" s="72" t="s">
+      <c r="A73" s="83"/>
+      <c r="B73" s="83"/>
+      <c r="C73" s="104" t="s">
         <v>135</v>
       </c>
-      <c r="D73" s="73"/>
+      <c r="D73" s="88"/>
       <c r="E73" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="71"/>
-      <c r="B74" s="71"/>
-      <c r="C74" s="72" t="s">
+      <c r="A74" s="83"/>
+      <c r="B74" s="83"/>
+      <c r="C74" s="104" t="s">
         <v>137</v>
       </c>
-      <c r="D74" s="74"/>
+      <c r="D74" s="81"/>
       <c r="E74" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="71" t="s">
+      <c r="A75" s="83" t="s">
         <v>95</v>
       </c>
-      <c r="B75" s="71"/>
-      <c r="C75" s="75"/>
-      <c r="D75" s="75"/>
+      <c r="B75" s="83"/>
+      <c r="C75" s="84"/>
+      <c r="D75" s="84"/>
       <c r="E75" s="46">
         <f>C66</f>
         <v>1171</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C76" s="70" t="s">
+      <c r="C76" s="85" t="s">
         <v>96</v>
       </c>
-      <c r="D76" s="70"/>
+      <c r="D76" s="85"/>
       <c r="E76" s="47">
         <f>(E15+E71)-SUM(E72:E75)</f>
         <v>24.599999999999909</v>
@@ -7895,100 +7895,100 @@
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="61" t="s">
+      <c r="A78" s="75" t="s">
         <v>130</v>
       </c>
-      <c r="B78" s="61"/>
-      <c r="C78" s="61"/>
-      <c r="D78" s="61"/>
-      <c r="E78" s="61"/>
+      <c r="B78" s="75"/>
+      <c r="C78" s="75"/>
+      <c r="D78" s="75"/>
+      <c r="E78" s="75"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="61" t="s">
+      <c r="A79" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B79" s="61"/>
-      <c r="C79" s="61" t="s">
+      <c r="B79" s="75"/>
+      <c r="C79" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D79" s="61"/>
+      <c r="D79" s="75"/>
       <c r="E79" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="54" t="s">
+      <c r="A80" s="86" t="s">
         <v>108</v>
       </c>
-      <c r="B80" s="54"/>
-      <c r="C80" s="55"/>
-      <c r="D80" s="55"/>
+      <c r="B80" s="86"/>
+      <c r="C80" s="87"/>
+      <c r="D80" s="87"/>
       <c r="E80" s="47">
         <f>E76</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="64" t="s">
+      <c r="A81" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="B81" s="65"/>
-      <c r="C81" s="58" t="s">
+      <c r="B81" s="95"/>
+      <c r="C81" s="105" t="s">
         <v>136</v>
       </c>
-      <c r="D81" s="59"/>
+      <c r="D81" s="106"/>
       <c r="E81" s="48">
         <v>770.4</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="66"/>
-      <c r="B82" s="67"/>
-      <c r="C82" s="57" t="s">
+      <c r="A82" s="96"/>
+      <c r="B82" s="97"/>
+      <c r="C82" s="89" t="s">
         <v>138</v>
       </c>
-      <c r="D82" s="57"/>
+      <c r="D82" s="89"/>
       <c r="E82" s="48">
         <v>8.5</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="66"/>
-      <c r="B83" s="67"/>
-      <c r="C83" s="62" t="s">
+      <c r="A83" s="96"/>
+      <c r="B83" s="97"/>
+      <c r="C83" s="90" t="s">
         <v>140</v>
       </c>
-      <c r="D83" s="63"/>
+      <c r="D83" s="107"/>
       <c r="E83" s="48">
         <v>128</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="68"/>
-      <c r="B84" s="69"/>
-      <c r="C84" s="63"/>
-      <c r="D84" s="63"/>
+      <c r="A84" s="98"/>
+      <c r="B84" s="99"/>
+      <c r="C84" s="107"/>
+      <c r="D84" s="107"/>
       <c r="E84" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="56" t="s">
+      <c r="A85" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B85" s="56"/>
-      <c r="C85" s="55"/>
-      <c r="D85" s="55"/>
+      <c r="B85" s="78"/>
+      <c r="C85" s="87"/>
+      <c r="D85" s="87"/>
       <c r="E85" s="45">
         <f>C66</f>
         <v>1171</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C86" s="53" t="s">
+      <c r="C86" s="92" t="s">
         <v>96</v>
       </c>
-      <c r="D86" s="53"/>
+      <c r="D86" s="92"/>
       <c r="E86" s="47">
         <f>(E22+E80)-SUM(E81:E85)</f>
         <v>481.69999999999982</v>
@@ -8009,69 +8009,69 @@
       <c r="E88" s="49"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="60" t="s">
+      <c r="A89" s="93" t="s">
         <v>131</v>
       </c>
-      <c r="B89" s="60"/>
-      <c r="C89" s="60"/>
-      <c r="D89" s="60"/>
-      <c r="E89" s="60"/>
+      <c r="B89" s="93"/>
+      <c r="C89" s="93"/>
+      <c r="D89" s="93"/>
+      <c r="E89" s="93"/>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="61" t="s">
+      <c r="A90" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="B90" s="61"/>
-      <c r="C90" s="61" t="s">
+      <c r="B90" s="75"/>
+      <c r="C90" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="61"/>
+      <c r="D90" s="75"/>
       <c r="E90" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="54" t="s">
+      <c r="A91" s="86" t="s">
         <v>109</v>
       </c>
-      <c r="B91" s="54"/>
-      <c r="C91" s="55"/>
-      <c r="D91" s="55"/>
+      <c r="B91" s="86"/>
+      <c r="C91" s="87"/>
+      <c r="D91" s="87"/>
       <c r="E91" s="47">
         <f>E86</f>
         <v>481.69999999999982</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="56" t="s">
+      <c r="A92" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="B92" s="56"/>
-      <c r="C92" s="57" t="s">
+      <c r="B92" s="78"/>
+      <c r="C92" s="89" t="s">
         <v>118</v>
       </c>
-      <c r="D92" s="57"/>
+      <c r="D92" s="89"/>
       <c r="E92" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="56" t="s">
+      <c r="A93" s="78" t="s">
         <v>95</v>
       </c>
-      <c r="B93" s="56"/>
-      <c r="C93" s="55"/>
-      <c r="D93" s="55"/>
+      <c r="B93" s="78"/>
+      <c r="C93" s="87"/>
+      <c r="D93" s="87"/>
       <c r="E93" s="45">
         <f>C66</f>
         <v>1171</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C94" s="53" t="s">
+      <c r="C94" s="92" t="s">
         <v>96</v>
       </c>
-      <c r="D94" s="53"/>
+      <c r="D94" s="92"/>
       <c r="E94" s="47">
         <f>(E28+E91)-SUM(E92:E93)</f>
         <v>1795.6999999999998</v>
@@ -11823,46 +11823,13 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A37:C38"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="A72:B74"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:D93"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A89:E89"/>
@@ -11874,13 +11841,46 @@
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="A81:B84"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A72:B74"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="A37:C38"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E71">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A871E8-C30A-464F-AD22-FDE1345E5D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B282911-6185-C343-93E5-8DCAA0091D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
@@ -648,7 +648,8 @@
   </si>
   <si>
     <t>~ Debit For Octopus Card ($50). 20/08
-~ OK Store buy additional 1 packet cigarette 20/08 - $78</t>
+~ OK Store buy additional 1 packet cigarette 20/08 - $78
+~ Mail Chuk Yuen Post Office - $2.4</t>
   </si>
 </sst>
 </file>
@@ -1175,124 +1176,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1313,20 +1206,119 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1335,6 +1327,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1654,13 +1655,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1681,7 +1682,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="9">
-        <v>1332.9</v>
+        <v>1322.9</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1774,7 +1775,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="9">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -1805,7 +1806,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="9">
-        <v>61.8</v>
+        <v>6.8</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -1837,7 +1838,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>1436.7</v>
+        <v>1379.3</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1890,13 +1891,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1924,10 +1925,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="56"/>
+      <c r="D11" s="99"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1939,10 +1940,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="57"/>
+      <c r="D12" s="100"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1954,10 +1955,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="58"/>
+      <c r="D13" s="101"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1967,10 +1968,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="86" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="59"/>
+      <c r="D14" s="86"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -1980,10 +1981,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="59"/>
+      <c r="D15" s="86"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -1993,10 +1994,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="86" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="59"/>
+      <c r="D16" s="86"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2008,10 +2009,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="60" t="s">
+      <c r="C17" s="91" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="60"/>
+      <c r="D17" s="91"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2021,10 +2022,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="92" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="61"/>
+      <c r="D18" s="92"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2036,10 +2037,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="62" t="s">
+      <c r="C19" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="62"/>
+      <c r="D19" s="95"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2060,13 +2061,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="63" t="s">
+      <c r="A22" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="B22" s="93"/>
+      <c r="C22" s="93"/>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2094,10 +2095,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="64" t="s">
+      <c r="C23" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="64"/>
+      <c r="D23" s="96"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2109,10 +2110,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="59"/>
+      <c r="D24" s="86"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2124,10 +2125,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="59"/>
+      <c r="D25" s="86"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2137,10 +2138,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="65" t="s">
+      <c r="C26" s="90" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="60"/>
+      <c r="D26" s="91"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2152,10 +2153,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="61" t="s">
+      <c r="C27" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="61"/>
+      <c r="D27" s="92"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2165,10 +2166,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="66" t="s">
+      <c r="C28" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="66"/>
+      <c r="D28" s="64"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2190,13 +2191,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="63" t="s">
+      <c r="A31" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="63"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
-      <c r="E31" s="63"/>
+      <c r="B31" s="93"/>
+      <c r="C31" s="93"/>
+      <c r="D31" s="93"/>
+      <c r="E31" s="93"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2224,10 +2225,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="67" t="s">
+      <c r="C32" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="67"/>
+      <c r="D32" s="94"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2239,10 +2240,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="59"/>
+      <c r="D33" s="86"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2252,10 +2253,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="59" t="s">
+      <c r="C34" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="59"/>
+      <c r="D34" s="86"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2265,10 +2266,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="68" t="s">
+      <c r="C35" s="87" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="69"/>
+      <c r="D35" s="88"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2278,10 +2279,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="68" t="s">
+      <c r="C36" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="70"/>
+      <c r="D36" s="89"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2291,10 +2292,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="65" t="s">
+      <c r="C37" s="90" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="59"/>
+      <c r="D37" s="86"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2316,11 +2317,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="71" t="s">
+      <c r="A40" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="71"/>
-      <c r="C40" s="71"/>
+      <c r="B40" s="84"/>
+      <c r="C40" s="84"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2335,11 +2336,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="72" t="s">
+      <c r="A42" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="72"/>
-      <c r="C42" s="72"/>
+      <c r="B42" s="81"/>
+      <c r="C42" s="81"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2385,16 +2386,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="73" t="s">
+      <c r="A47" s="85" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="73"/>
-      <c r="C47" s="73"/>
+      <c r="B47" s="85"/>
+      <c r="C47" s="85"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="73"/>
-      <c r="B48" s="73"/>
-      <c r="C48" s="73"/>
+      <c r="A48" s="85"/>
+      <c r="B48" s="85"/>
+      <c r="C48" s="85"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2443,11 +2444,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="72" t="s">
+      <c r="A54" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="72"/>
-      <c r="C54" s="72"/>
+      <c r="B54" s="81"/>
+      <c r="C54" s="81"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2482,11 +2483,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="72" t="s">
+      <c r="A58" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="72"/>
-      <c r="C58" s="72"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="81"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2510,11 +2511,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="72" t="s">
+      <c r="A61" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="72"/>
-      <c r="C61" s="72"/>
+      <c r="B61" s="81"/>
+      <c r="C61" s="81"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2538,11 +2539,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="74" t="s">
+      <c r="A64" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="74"/>
-      <c r="C64" s="74"/>
+      <c r="B64" s="82"/>
+      <c r="C64" s="82"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2619,11 +2620,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="74" t="s">
+      <c r="A72" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="74"/>
-      <c r="C72" s="74"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="82"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2673,167 +2674,167 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="75" t="s">
+      <c r="A79" s="70" t="s">
         <v>126</v>
       </c>
-      <c r="B79" s="75"/>
-      <c r="C79" s="75"/>
-      <c r="D79" s="75"/>
-      <c r="E79" s="75"/>
+      <c r="B79" s="70"/>
+      <c r="C79" s="70"/>
+      <c r="D79" s="70"/>
+      <c r="E79" s="70"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="76" t="s">
+      <c r="A80" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="76"/>
-      <c r="C80" s="76" t="s">
+      <c r="B80" s="83"/>
+      <c r="C80" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="76"/>
+      <c r="D80" s="83"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="77" t="s">
+      <c r="A81" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="77"/>
-      <c r="C81" s="78"/>
-      <c r="D81" s="78"/>
+      <c r="B81" s="76"/>
+      <c r="C81" s="54"/>
+      <c r="D81" s="54"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="78" t="s">
+      <c r="A82" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="78"/>
-      <c r="C82" s="79" t="s">
+      <c r="B82" s="54"/>
+      <c r="C82" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="79"/>
+      <c r="D82" s="77"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="78"/>
-      <c r="B83" s="78"/>
-      <c r="C83" s="79" t="s">
+      <c r="A83" s="54"/>
+      <c r="B83" s="54"/>
+      <c r="C83" s="77" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="79"/>
+      <c r="D83" s="77"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="78"/>
-      <c r="B84" s="78"/>
-      <c r="C84" s="79" t="s">
+      <c r="A84" s="54"/>
+      <c r="B84" s="54"/>
+      <c r="C84" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="79"/>
+      <c r="D84" s="77"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="78"/>
-      <c r="B85" s="78"/>
-      <c r="C85" s="80" t="s">
+      <c r="A85" s="54"/>
+      <c r="B85" s="54"/>
+      <c r="C85" s="78" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="80"/>
+      <c r="D85" s="78"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="78"/>
-      <c r="B86" s="78"/>
-      <c r="C86" s="81" t="s">
+      <c r="A86" s="54"/>
+      <c r="B86" s="54"/>
+      <c r="C86" s="79" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="81"/>
+      <c r="D86" s="79"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="78"/>
-      <c r="B87" s="78"/>
-      <c r="C87" s="80" t="s">
+      <c r="A87" s="54"/>
+      <c r="B87" s="54"/>
+      <c r="C87" s="78" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="80"/>
+      <c r="D87" s="78"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="78"/>
-      <c r="B88" s="78"/>
-      <c r="C88" s="79" t="s">
+      <c r="A88" s="54"/>
+      <c r="B88" s="54"/>
+      <c r="C88" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="79"/>
+      <c r="D88" s="77"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="78"/>
-      <c r="B89" s="78"/>
-      <c r="C89" s="81" t="s">
+      <c r="A89" s="54"/>
+      <c r="B89" s="54"/>
+      <c r="C89" s="79" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="81"/>
+      <c r="D89" s="79"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="78"/>
-      <c r="B90" s="78"/>
-      <c r="C90" s="81" t="s">
+      <c r="A90" s="54"/>
+      <c r="B90" s="54"/>
+      <c r="C90" s="79" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="81"/>
+      <c r="D90" s="79"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="78"/>
-      <c r="B91" s="78"/>
-      <c r="C91" s="82" t="s">
+      <c r="A91" s="54"/>
+      <c r="B91" s="54"/>
+      <c r="C91" s="80" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="82"/>
+      <c r="D91" s="80"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="83" t="s">
+      <c r="A92" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="83"/>
-      <c r="C92" s="84"/>
-      <c r="D92" s="84"/>
+      <c r="B92" s="73"/>
+      <c r="C92" s="74"/>
+      <c r="D92" s="74"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="85" t="s">
+      <c r="C93" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="85"/>
+      <c r="D93" s="75"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2841,113 +2842,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="75" t="s">
+      <c r="A95" s="70" t="s">
         <v>127</v>
       </c>
-      <c r="B95" s="75"/>
-      <c r="C95" s="75"/>
-      <c r="D95" s="75"/>
-      <c r="E95" s="75"/>
+      <c r="B95" s="70"/>
+      <c r="C95" s="70"/>
+      <c r="D95" s="70"/>
+      <c r="E95" s="70"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="75" t="s">
+      <c r="A96" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="75"/>
-      <c r="C96" s="75" t="s">
+      <c r="B96" s="70"/>
+      <c r="C96" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="75"/>
+      <c r="D96" s="70"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="86" t="s">
+      <c r="A97" s="57" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="86"/>
-      <c r="C97" s="87"/>
-      <c r="D97" s="87"/>
+      <c r="B97" s="57"/>
+      <c r="C97" s="55"/>
+      <c r="D97" s="55"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="78" t="s">
+      <c r="A98" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="78"/>
-      <c r="C98" s="88" t="s">
+      <c r="B98" s="54"/>
+      <c r="C98" s="71" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="88"/>
+      <c r="D98" s="71"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="78"/>
-      <c r="B99" s="78"/>
-      <c r="C99" s="89" t="s">
+      <c r="A99" s="54"/>
+      <c r="B99" s="54"/>
+      <c r="C99" s="72" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="89"/>
+      <c r="D99" s="72"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="78"/>
-      <c r="B100" s="78"/>
-      <c r="C100" s="89" t="s">
+      <c r="A100" s="54"/>
+      <c r="B100" s="54"/>
+      <c r="C100" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="89"/>
+      <c r="D100" s="72"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="78"/>
-      <c r="B101" s="78"/>
-      <c r="C101" s="89" t="s">
+      <c r="A101" s="54"/>
+      <c r="B101" s="54"/>
+      <c r="C101" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="89"/>
+      <c r="D101" s="72"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="78"/>
-      <c r="B102" s="78"/>
-      <c r="C102" s="90" t="s">
+      <c r="A102" s="54"/>
+      <c r="B102" s="54"/>
+      <c r="C102" s="67" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="91"/>
+      <c r="D102" s="68"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="78" t="s">
+      <c r="A103" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="78"/>
-      <c r="C103" s="87"/>
-      <c r="D103" s="87"/>
+      <c r="B103" s="54"/>
+      <c r="C103" s="55"/>
+      <c r="D103" s="55"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="92" t="s">
+      <c r="C104" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="92"/>
+      <c r="D104" s="56"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2968,91 +2969,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="93" t="s">
+      <c r="A107" s="69" t="s">
         <v>128</v>
       </c>
-      <c r="B107" s="93"/>
-      <c r="C107" s="93"/>
-      <c r="D107" s="93"/>
-      <c r="E107" s="93"/>
+      <c r="B107" s="69"/>
+      <c r="C107" s="69"/>
+      <c r="D107" s="69"/>
+      <c r="E107" s="69"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="75" t="s">
+      <c r="A108" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="75"/>
-      <c r="C108" s="75" t="s">
+      <c r="B108" s="70"/>
+      <c r="C108" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="75"/>
+      <c r="D108" s="70"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="86" t="s">
+      <c r="A109" s="57" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="86"/>
-      <c r="C109" s="87"/>
-      <c r="D109" s="87"/>
+      <c r="B109" s="57"/>
+      <c r="C109" s="55"/>
+      <c r="D109" s="55"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="94" t="s">
+      <c r="A110" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="95"/>
-      <c r="C110" s="66" t="s">
+      <c r="B110" s="59"/>
+      <c r="C110" s="64" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="66"/>
+      <c r="D110" s="64"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="96"/>
-      <c r="B111" s="97"/>
-      <c r="C111" s="100" t="s">
+      <c r="A111" s="60"/>
+      <c r="B111" s="61"/>
+      <c r="C111" s="65" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="101"/>
+      <c r="D111" s="66"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="98"/>
-      <c r="B112" s="99"/>
-      <c r="C112" s="90" t="s">
+      <c r="A112" s="62"/>
+      <c r="B112" s="63"/>
+      <c r="C112" s="67" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="91"/>
+      <c r="D112" s="68"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="78" t="s">
+      <c r="A113" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="78"/>
-      <c r="C113" s="87"/>
-      <c r="D113" s="87"/>
+      <c r="B113" s="54"/>
+      <c r="C113" s="55"/>
+      <c r="D113" s="55"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="92" t="s">
+      <c r="C114" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="92"/>
+      <c r="D114" s="56"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6804,35 +6805,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6846,42 +6854,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6921,13 +6922,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="97" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -6949,7 +6950,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>1332.9</v>
+        <v>1322.9</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -7045,7 +7046,7 @@
       </c>
       <c r="C6" s="9">
         <f>'April 2026 - June 2026'!C6</f>
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -7077,7 +7078,7 @@
       </c>
       <c r="C7" s="9">
         <f>'April 2026 - June 2026'!C7</f>
-        <v>61.8</v>
+        <v>6.8</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -7109,7 +7110,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>1436.7</v>
+        <v>1379.3</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7162,13 +7163,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="98" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7196,10 +7197,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="56"/>
+      <c r="D11" s="99"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7211,10 +7212,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="102" t="s">
+      <c r="C12" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="102"/>
+      <c r="D12" s="107"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7226,10 +7227,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="86" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="59"/>
+      <c r="D13" s="86"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7241,10 +7242,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="90" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="59"/>
+      <c r="D14" s="86"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7265,13 +7266,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="63" t="s">
+      <c r="A17" s="93" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
+      <c r="B17" s="93"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="93"/>
+      <c r="E17" s="93"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7299,10 +7300,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="67" t="s">
+      <c r="C18" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="67"/>
+      <c r="D18" s="94"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7314,10 +7315,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="59"/>
+      <c r="D19" s="86"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7329,10 +7330,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="103" t="s">
+      <c r="C20" s="106" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="69"/>
+      <c r="D20" s="88"/>
       <c r="E20" s="29">
         <v>50</v>
       </c>
@@ -7340,8 +7341,8 @@
     <row r="21" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
+      <c r="C21" s="86"/>
+      <c r="D21" s="86"/>
       <c r="E21" s="29">
         <v>0</v>
       </c>
@@ -7363,13 +7364,13 @@
       <c r="B23" s="24"/>
     </row>
     <row r="24" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="63" t="s">
+      <c r="A24" s="93" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="63"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="63"/>
+      <c r="B24" s="93"/>
+      <c r="C24" s="93"/>
+      <c r="D24" s="93"/>
+      <c r="E24" s="93"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
@@ -7397,10 +7398,10 @@
       <c r="B25" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="67"/>
+      <c r="D25" s="94"/>
       <c r="E25" s="2" t="s">
         <v>12</v>
       </c>
@@ -7412,10 +7413,10 @@
       <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="59" t="s">
+      <c r="C26" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="59"/>
+      <c r="D26" s="86"/>
       <c r="E26" s="33">
         <v>2485</v>
       </c>
@@ -7423,8 +7424,8 @@
     <row r="27" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
+      <c r="C27" s="86"/>
+      <c r="D27" s="86"/>
       <c r="E27" s="29">
         <v>0</v>
       </c>
@@ -7446,11 +7447,11 @@
       <c r="B29" s="24"/>
     </row>
     <row r="30" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="71" t="s">
+      <c r="A30" s="84" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
+      <c r="B30" s="84"/>
+      <c r="C30" s="84"/>
     </row>
     <row r="31" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
@@ -7465,11 +7466,11 @@
       <c r="D31" s="37"/>
     </row>
     <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="72" t="s">
+      <c r="A32" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="72"/>
-      <c r="C32" s="72"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
     </row>
     <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="50" t="s">
@@ -7515,16 +7516,16 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="73" t="s">
+      <c r="A37" s="85" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="73"/>
-      <c r="C37" s="73"/>
+      <c r="B37" s="85"/>
+      <c r="C37" s="85"/>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="73"/>
-      <c r="B38" s="73"/>
-      <c r="C38" s="73"/>
+      <c r="A38" s="85"/>
+      <c r="B38" s="85"/>
+      <c r="C38" s="85"/>
     </row>
     <row r="39" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
@@ -7573,11 +7574,11 @@
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="72" t="s">
+      <c r="A44" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="B44" s="72"/>
-      <c r="C44" s="72"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="81"/>
     </row>
     <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
@@ -7612,11 +7613,11 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="72" t="s">
+      <c r="A48" s="81" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="72"/>
-      <c r="C48" s="72"/>
+      <c r="B48" s="81"/>
+      <c r="C48" s="81"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -7640,11 +7641,11 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="72" t="s">
+      <c r="A51" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="72"/>
-      <c r="C51" s="72"/>
+      <c r="B51" s="81"/>
+      <c r="C51" s="81"/>
     </row>
     <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
@@ -7668,11 +7669,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="74" t="s">
+      <c r="A54" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="74"/>
-      <c r="C54" s="74"/>
+      <c r="B54" s="82"/>
+      <c r="C54" s="82"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="17" t="s">
@@ -7749,11 +7750,11 @@
       </c>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="74" t="s">
+      <c r="A62" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="B62" s="74"/>
-      <c r="C62" s="74"/>
+      <c r="B62" s="82"/>
+      <c r="C62" s="82"/>
     </row>
     <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
@@ -7803,91 +7804,91 @@
       <c r="B68" s="24"/>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="75" t="s">
+      <c r="A69" s="70" t="s">
         <v>129</v>
       </c>
-      <c r="B69" s="75"/>
-      <c r="C69" s="75"/>
-      <c r="D69" s="75"/>
-      <c r="E69" s="75"/>
+      <c r="B69" s="70"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="70"/>
+      <c r="E69" s="70"/>
     </row>
     <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="76" t="s">
+      <c r="A70" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="B70" s="76"/>
-      <c r="C70" s="76" t="s">
+      <c r="B70" s="83"/>
+      <c r="C70" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="D70" s="76"/>
+      <c r="D70" s="83"/>
       <c r="E70" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="86" t="s">
+      <c r="A71" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="B71" s="86"/>
-      <c r="C71" s="78"/>
-      <c r="D71" s="78"/>
+      <c r="B71" s="57"/>
+      <c r="C71" s="54"/>
+      <c r="D71" s="54"/>
       <c r="E71" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="83" t="s">
+      <c r="A72" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="B72" s="83"/>
-      <c r="C72" s="89" t="s">
+      <c r="B72" s="73"/>
+      <c r="C72" s="72" t="s">
         <v>122</v>
       </c>
-      <c r="D72" s="89"/>
+      <c r="D72" s="72"/>
       <c r="E72" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="83"/>
-      <c r="B73" s="83"/>
-      <c r="C73" s="104" t="s">
+      <c r="A73" s="73"/>
+      <c r="B73" s="73"/>
+      <c r="C73" s="105" t="s">
         <v>135</v>
       </c>
-      <c r="D73" s="88"/>
+      <c r="D73" s="71"/>
       <c r="E73" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="83"/>
-      <c r="B74" s="83"/>
-      <c r="C74" s="104" t="s">
+      <c r="A74" s="73"/>
+      <c r="B74" s="73"/>
+      <c r="C74" s="105" t="s">
         <v>137</v>
       </c>
-      <c r="D74" s="81"/>
+      <c r="D74" s="79"/>
       <c r="E74" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="83" t="s">
+      <c r="A75" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="B75" s="83"/>
-      <c r="C75" s="84"/>
-      <c r="D75" s="84"/>
+      <c r="B75" s="73"/>
+      <c r="C75" s="74"/>
+      <c r="D75" s="74"/>
       <c r="E75" s="46">
         <f>C66</f>
         <v>1171</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C76" s="85" t="s">
+      <c r="C76" s="75" t="s">
         <v>96</v>
       </c>
-      <c r="D76" s="85"/>
+      <c r="D76" s="75"/>
       <c r="E76" s="47">
         <f>(E15+E71)-SUM(E72:E75)</f>
         <v>24.599999999999909</v>
@@ -7895,103 +7896,103 @@
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="75" t="s">
+      <c r="A78" s="70" t="s">
         <v>130</v>
       </c>
-      <c r="B78" s="75"/>
-      <c r="C78" s="75"/>
-      <c r="D78" s="75"/>
-      <c r="E78" s="75"/>
+      <c r="B78" s="70"/>
+      <c r="C78" s="70"/>
+      <c r="D78" s="70"/>
+      <c r="E78" s="70"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="75" t="s">
+      <c r="A79" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="B79" s="75"/>
-      <c r="C79" s="75" t="s">
+      <c r="B79" s="70"/>
+      <c r="C79" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="D79" s="75"/>
+      <c r="D79" s="70"/>
       <c r="E79" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="86" t="s">
+      <c r="A80" s="57" t="s">
         <v>108</v>
       </c>
-      <c r="B80" s="86"/>
-      <c r="C80" s="87"/>
-      <c r="D80" s="87"/>
+      <c r="B80" s="57"/>
+      <c r="C80" s="55"/>
+      <c r="D80" s="55"/>
       <c r="E80" s="47">
         <f>E76</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="94" t="s">
+      <c r="A81" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="B81" s="95"/>
-      <c r="C81" s="105" t="s">
+      <c r="B81" s="59"/>
+      <c r="C81" s="102" t="s">
         <v>136</v>
       </c>
-      <c r="D81" s="106"/>
+      <c r="D81" s="103"/>
       <c r="E81" s="48">
         <v>770.4</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="96"/>
-      <c r="B82" s="97"/>
-      <c r="C82" s="89" t="s">
+      <c r="A82" s="60"/>
+      <c r="B82" s="61"/>
+      <c r="C82" s="72" t="s">
         <v>138</v>
       </c>
-      <c r="D82" s="89"/>
+      <c r="D82" s="72"/>
       <c r="E82" s="48">
         <v>8.5</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="96"/>
-      <c r="B83" s="97"/>
-      <c r="C83" s="90" t="s">
+    <row r="83" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="60"/>
+      <c r="B83" s="61"/>
+      <c r="C83" s="67" t="s">
         <v>140</v>
       </c>
-      <c r="D83" s="107"/>
+      <c r="D83" s="104"/>
       <c r="E83" s="48">
-        <v>128</v>
+        <v>130.4</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="98"/>
-      <c r="B84" s="99"/>
-      <c r="C84" s="107"/>
-      <c r="D84" s="107"/>
+      <c r="A84" s="62"/>
+      <c r="B84" s="63"/>
+      <c r="C84" s="104"/>
+      <c r="D84" s="104"/>
       <c r="E84" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="78" t="s">
+      <c r="A85" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="B85" s="78"/>
-      <c r="C85" s="87"/>
-      <c r="D85" s="87"/>
+      <c r="B85" s="54"/>
+      <c r="C85" s="55"/>
+      <c r="D85" s="55"/>
       <c r="E85" s="45">
         <f>C66</f>
         <v>1171</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C86" s="92" t="s">
+      <c r="C86" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D86" s="92"/>
+      <c r="D86" s="56"/>
       <c r="E86" s="47">
         <f>(E22+E80)-SUM(E81:E85)</f>
-        <v>481.69999999999982</v>
+        <v>479.29999999999973</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8009,72 +8010,72 @@
       <c r="E88" s="49"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="93" t="s">
+      <c r="A89" s="69" t="s">
         <v>131</v>
       </c>
-      <c r="B89" s="93"/>
-      <c r="C89" s="93"/>
-      <c r="D89" s="93"/>
-      <c r="E89" s="93"/>
+      <c r="B89" s="69"/>
+      <c r="C89" s="69"/>
+      <c r="D89" s="69"/>
+      <c r="E89" s="69"/>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="75" t="s">
+      <c r="A90" s="70" t="s">
         <v>83</v>
       </c>
-      <c r="B90" s="75"/>
-      <c r="C90" s="75" t="s">
+      <c r="B90" s="70"/>
+      <c r="C90" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="75"/>
+      <c r="D90" s="70"/>
       <c r="E90" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="86" t="s">
+      <c r="A91" s="57" t="s">
         <v>109</v>
       </c>
-      <c r="B91" s="86"/>
-      <c r="C91" s="87"/>
-      <c r="D91" s="87"/>
+      <c r="B91" s="57"/>
+      <c r="C91" s="55"/>
+      <c r="D91" s="55"/>
       <c r="E91" s="47">
         <f>E86</f>
-        <v>481.69999999999982</v>
+        <v>479.29999999999973</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="78" t="s">
+      <c r="A92" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="B92" s="78"/>
-      <c r="C92" s="89" t="s">
+      <c r="B92" s="54"/>
+      <c r="C92" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="D92" s="89"/>
+      <c r="D92" s="72"/>
       <c r="E92" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="78" t="s">
+      <c r="A93" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="B93" s="78"/>
-      <c r="C93" s="87"/>
-      <c r="D93" s="87"/>
+      <c r="B93" s="54"/>
+      <c r="C93" s="55"/>
+      <c r="D93" s="55"/>
       <c r="E93" s="45">
         <f>C66</f>
         <v>1171</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C94" s="92" t="s">
+      <c r="C94" s="56" t="s">
         <v>96</v>
       </c>
-      <c r="D94" s="92"/>
+      <c r="D94" s="56"/>
       <c r="E94" s="47">
         <f>(E28+E91)-SUM(E92:E93)</f>
-        <v>1795.6999999999998</v>
+        <v>1793.2999999999997</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11823,13 +11824,46 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A37:C38"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="A72:B74"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A89:E89"/>
@@ -11841,46 +11875,13 @@
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="A81:B84"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A72:B74"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="A37:C38"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:D93"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E71">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B282911-6185-C343-93E5-8DCAA0091D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24202E8-395F-BC4A-99CB-7B465633410A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,8 @@
   <si>
     <t>~ Debit For Octopus Card ($50). 20/08
 ~ OK Store buy additional 1 packet cigarette 20/08 - $78
-~ Mail Chuk Yuen Post Office - $2.4</t>
+~ Mail Chuk Yuen Post Office - $2.4
+~ Additional transport fees for e-cigarette 20/08 - $50</t>
   </si>
 </sst>
 </file>
@@ -1176,17 +1177,101 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1206,41 +1291,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1251,92 +1327,17 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1655,13 +1656,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1682,7 +1683,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="9">
-        <v>1322.9</v>
+        <v>380.5</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1775,7 +1776,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="9">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -1838,7 +1839,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>1379.3</v>
+        <v>429.3</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1891,13 +1892,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="98" t="s">
+      <c r="A10" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1925,10 +1926,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="99" t="s">
+      <c r="C11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="99"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1940,10 +1941,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="100" t="s">
+      <c r="C12" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="100"/>
+      <c r="D12" s="92"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1955,10 +1956,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="101" t="s">
+      <c r="C13" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="101"/>
+      <c r="D13" s="93"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1968,10 +1969,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="86" t="s">
+      <c r="C14" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="86"/>
+      <c r="D14" s="59"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -1981,10 +1982,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="86" t="s">
+      <c r="C15" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="86"/>
+      <c r="D15" s="59"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -1994,10 +1995,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="86" t="s">
+      <c r="C16" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="86"/>
+      <c r="D16" s="59"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2009,10 +2010,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="91" t="s">
+      <c r="C17" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="91"/>
+      <c r="D17" s="94"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2022,10 +2023,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="92" t="s">
+      <c r="C18" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="92"/>
+      <c r="D18" s="95"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2037,10 +2038,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="95" t="s">
+      <c r="C19" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="95"/>
+      <c r="D19" s="96"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2061,13 +2062,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="93" t="s">
+      <c r="A22" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="93"/>
-      <c r="C22" s="93"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="93"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2095,10 +2096,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="96" t="s">
+      <c r="C23" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="96"/>
+      <c r="D23" s="97"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2110,10 +2111,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="86" t="s">
+      <c r="C24" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="86"/>
+      <c r="D24" s="59"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2125,10 +2126,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="86"/>
+      <c r="D25" s="59"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2138,10 +2139,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="90" t="s">
+      <c r="C26" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="91"/>
+      <c r="D26" s="94"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2153,10 +2154,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="92" t="s">
+      <c r="C27" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="92"/>
+      <c r="D27" s="95"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2166,10 +2167,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="64" t="s">
+      <c r="C28" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="64"/>
+      <c r="D28" s="98"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2191,13 +2192,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="93" t="s">
+      <c r="A31" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="93"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="93"/>
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2225,10 +2226,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="94" t="s">
+      <c r="C32" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="94"/>
+      <c r="D32" s="61"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2240,10 +2241,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="86" t="s">
+      <c r="C33" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="86"/>
+      <c r="D33" s="59"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2253,10 +2254,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="86" t="s">
+      <c r="C34" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="86"/>
+      <c r="D34" s="59"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2266,10 +2267,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="87" t="s">
+      <c r="C35" s="99" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="88"/>
+      <c r="D35" s="63"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2279,10 +2280,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="87" t="s">
+      <c r="C36" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="89"/>
+      <c r="D36" s="100"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2292,10 +2293,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="90" t="s">
+      <c r="C37" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="86"/>
+      <c r="D37" s="59"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2317,11 +2318,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="84" t="s">
+      <c r="A40" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="84"/>
-      <c r="C40" s="84"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="64"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2336,11 +2337,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="81" t="s">
+      <c r="A42" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="81"/>
-      <c r="C42" s="81"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2386,16 +2387,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="85" t="s">
+      <c r="A47" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="85"/>
-      <c r="C47" s="85"/>
+      <c r="B47" s="66"/>
+      <c r="C47" s="66"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="85"/>
-      <c r="B48" s="85"/>
-      <c r="C48" s="85"/>
+      <c r="A48" s="66"/>
+      <c r="B48" s="66"/>
+      <c r="C48" s="66"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2444,11 +2445,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="81" t="s">
+      <c r="A54" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="81"/>
-      <c r="C54" s="81"/>
+      <c r="B54" s="65"/>
+      <c r="C54" s="65"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2483,11 +2484,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="81" t="s">
+      <c r="A58" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="81"/>
-      <c r="C58" s="81"/>
+      <c r="B58" s="65"/>
+      <c r="C58" s="65"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2511,11 +2512,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="81" t="s">
+      <c r="A61" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="81"/>
-      <c r="C61" s="81"/>
+      <c r="B61" s="65"/>
+      <c r="C61" s="65"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2539,11 +2540,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="82" t="s">
+      <c r="A64" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="82"/>
-      <c r="C64" s="82"/>
+      <c r="B64" s="67"/>
+      <c r="C64" s="67"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2620,11 +2621,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="82" t="s">
+      <c r="A72" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="82"/>
-      <c r="C72" s="82"/>
+      <c r="B72" s="67"/>
+      <c r="C72" s="67"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2674,167 +2675,167 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="70" t="s">
+      <c r="A79" s="68" t="s">
         <v>126</v>
       </c>
-      <c r="B79" s="70"/>
-      <c r="C79" s="70"/>
-      <c r="D79" s="70"/>
-      <c r="E79" s="70"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="68"/>
+      <c r="D79" s="68"/>
+      <c r="E79" s="68"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="83" t="s">
+      <c r="A80" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="83"/>
-      <c r="C80" s="83" t="s">
+      <c r="B80" s="69"/>
+      <c r="C80" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="83"/>
+      <c r="D80" s="69"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="76" t="s">
+      <c r="A81" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="76"/>
-      <c r="C81" s="54"/>
-      <c r="D81" s="54"/>
+      <c r="B81" s="101"/>
+      <c r="C81" s="71"/>
+      <c r="D81" s="71"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="54" t="s">
+      <c r="A82" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="54"/>
-      <c r="C82" s="77" t="s">
+      <c r="B82" s="71"/>
+      <c r="C82" s="102" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="77"/>
+      <c r="D82" s="102"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="54"/>
-      <c r="B83" s="54"/>
-      <c r="C83" s="77" t="s">
+      <c r="A83" s="71"/>
+      <c r="B83" s="71"/>
+      <c r="C83" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="77"/>
+      <c r="D83" s="102"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="54"/>
-      <c r="B84" s="54"/>
-      <c r="C84" s="77" t="s">
+      <c r="A84" s="71"/>
+      <c r="B84" s="71"/>
+      <c r="C84" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="77"/>
+      <c r="D84" s="102"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="54"/>
-      <c r="B85" s="54"/>
-      <c r="C85" s="78" t="s">
+      <c r="A85" s="71"/>
+      <c r="B85" s="71"/>
+      <c r="C85" s="103" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="78"/>
+      <c r="D85" s="103"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="54"/>
-      <c r="B86" s="54"/>
-      <c r="C86" s="79" t="s">
+      <c r="A86" s="71"/>
+      <c r="B86" s="71"/>
+      <c r="C86" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="79"/>
+      <c r="D86" s="76"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="54"/>
-      <c r="B87" s="54"/>
-      <c r="C87" s="78" t="s">
+      <c r="A87" s="71"/>
+      <c r="B87" s="71"/>
+      <c r="C87" s="103" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="78"/>
+      <c r="D87" s="103"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="54"/>
-      <c r="B88" s="54"/>
-      <c r="C88" s="77" t="s">
+      <c r="A88" s="71"/>
+      <c r="B88" s="71"/>
+      <c r="C88" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="77"/>
+      <c r="D88" s="102"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="54"/>
-      <c r="B89" s="54"/>
-      <c r="C89" s="79" t="s">
+      <c r="A89" s="71"/>
+      <c r="B89" s="71"/>
+      <c r="C89" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="79"/>
+      <c r="D89" s="76"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="54"/>
-      <c r="B90" s="54"/>
-      <c r="C90" s="79" t="s">
+      <c r="A90" s="71"/>
+      <c r="B90" s="71"/>
+      <c r="C90" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="79"/>
+      <c r="D90" s="76"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="54"/>
-      <c r="B91" s="54"/>
-      <c r="C91" s="80" t="s">
+      <c r="A91" s="71"/>
+      <c r="B91" s="71"/>
+      <c r="C91" s="104" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="80"/>
+      <c r="D91" s="104"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="73" t="s">
+      <c r="A92" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="B92" s="73"/>
-      <c r="C92" s="74"/>
-      <c r="D92" s="74"/>
+      <c r="B92" s="72"/>
+      <c r="C92" s="77"/>
+      <c r="D92" s="77"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="75" t="s">
+      <c r="C93" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="75"/>
+      <c r="D93" s="78"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2842,113 +2843,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="70" t="s">
+      <c r="A95" s="68" t="s">
         <v>127</v>
       </c>
-      <c r="B95" s="70"/>
-      <c r="C95" s="70"/>
-      <c r="D95" s="70"/>
-      <c r="E95" s="70"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="68"/>
+      <c r="D95" s="68"/>
+      <c r="E95" s="68"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="70" t="s">
+      <c r="A96" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="70"/>
-      <c r="C96" s="70" t="s">
+      <c r="B96" s="68"/>
+      <c r="C96" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="70"/>
+      <c r="D96" s="68"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="57" t="s">
+      <c r="A97" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="57"/>
-      <c r="C97" s="55"/>
-      <c r="D97" s="55"/>
+      <c r="B97" s="70"/>
+      <c r="C97" s="79"/>
+      <c r="D97" s="79"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="54" t="s">
+      <c r="A98" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="54"/>
-      <c r="C98" s="71" t="s">
+      <c r="B98" s="71"/>
+      <c r="C98" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="71"/>
+      <c r="D98" s="75"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="54"/>
-      <c r="B99" s="54"/>
-      <c r="C99" s="72" t="s">
+      <c r="A99" s="71"/>
+      <c r="B99" s="71"/>
+      <c r="C99" s="73" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="72"/>
+      <c r="D99" s="73"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="54"/>
-      <c r="B100" s="54"/>
-      <c r="C100" s="72" t="s">
+      <c r="A100" s="71"/>
+      <c r="B100" s="71"/>
+      <c r="C100" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="72"/>
+      <c r="D100" s="73"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="54"/>
-      <c r="B101" s="54"/>
-      <c r="C101" s="72" t="s">
+      <c r="A101" s="71"/>
+      <c r="B101" s="71"/>
+      <c r="C101" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="72"/>
+      <c r="D101" s="73"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="54"/>
-      <c r="B102" s="54"/>
-      <c r="C102" s="67" t="s">
+      <c r="A102" s="71"/>
+      <c r="B102" s="71"/>
+      <c r="C102" s="84" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="68"/>
+      <c r="D102" s="105"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="54" t="s">
+      <c r="A103" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="54"/>
-      <c r="C103" s="55"/>
-      <c r="D103" s="55"/>
+      <c r="B103" s="71"/>
+      <c r="C103" s="79"/>
+      <c r="D103" s="79"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="56" t="s">
+      <c r="C104" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="56"/>
+      <c r="D104" s="82"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2969,91 +2970,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="69" t="s">
+      <c r="A107" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="B107" s="69"/>
-      <c r="C107" s="69"/>
-      <c r="D107" s="69"/>
-      <c r="E107" s="69"/>
+      <c r="B107" s="83"/>
+      <c r="C107" s="83"/>
+      <c r="D107" s="83"/>
+      <c r="E107" s="83"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="70" t="s">
+      <c r="A108" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="70"/>
-      <c r="C108" s="70" t="s">
+      <c r="B108" s="68"/>
+      <c r="C108" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="70"/>
+      <c r="D108" s="68"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="57" t="s">
+      <c r="A109" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="57"/>
-      <c r="C109" s="55"/>
-      <c r="D109" s="55"/>
+      <c r="B109" s="70"/>
+      <c r="C109" s="79"/>
+      <c r="D109" s="79"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="58" t="s">
+      <c r="A110" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="59"/>
-      <c r="C110" s="64" t="s">
+      <c r="B110" s="87"/>
+      <c r="C110" s="98" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="64"/>
+      <c r="D110" s="98"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="60"/>
-      <c r="B111" s="61"/>
-      <c r="C111" s="65" t="s">
+      <c r="A111" s="88"/>
+      <c r="B111" s="89"/>
+      <c r="C111" s="106" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="66"/>
+      <c r="D111" s="107"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="62"/>
-      <c r="B112" s="63"/>
-      <c r="C112" s="67" t="s">
+      <c r="A112" s="90"/>
+      <c r="B112" s="91"/>
+      <c r="C112" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="68"/>
+      <c r="D112" s="105"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="54" t="s">
+      <c r="A113" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="54"/>
-      <c r="C113" s="55"/>
-      <c r="D113" s="55"/>
+      <c r="B113" s="71"/>
+      <c r="C113" s="79"/>
+      <c r="D113" s="79"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="56" t="s">
+      <c r="C114" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="56"/>
+      <c r="D114" s="82"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6805,42 +6806,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6854,35 +6848,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6922,13 +6923,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="97" t="s">
+      <c r="A1" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -6950,7 +6951,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>1322.9</v>
+        <v>380.5</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -7046,7 +7047,7 @@
       </c>
       <c r="C6" s="9">
         <f>'April 2026 - June 2026'!C6</f>
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -7110,7 +7111,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>1379.3</v>
+        <v>429.3</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7163,13 +7164,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="98" t="s">
+      <c r="A10" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="98"/>
-      <c r="C10" s="98"/>
-      <c r="D10" s="98"/>
-      <c r="E10" s="98"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7197,10 +7198,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="99" t="s">
+      <c r="C11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="99"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7212,10 +7213,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="107" t="s">
+      <c r="C12" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="107"/>
+      <c r="D12" s="57"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7227,10 +7228,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="C13" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="86"/>
+      <c r="D13" s="59"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7242,10 +7243,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="90" t="s">
+      <c r="C14" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="86"/>
+      <c r="D14" s="59"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7266,13 +7267,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="93" t="s">
+      <c r="A17" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="93"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="93"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7300,10 +7301,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="94" t="s">
+      <c r="C18" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="94"/>
+      <c r="D18" s="61"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7315,10 +7316,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="86" t="s">
+      <c r="C19" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="86"/>
+      <c r="D19" s="59"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7330,10 +7331,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="106" t="s">
+      <c r="C20" s="62" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="88"/>
+      <c r="D20" s="63"/>
       <c r="E20" s="29">
         <v>50</v>
       </c>
@@ -7341,8 +7342,8 @@
     <row r="21" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="86"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
       <c r="E21" s="29">
         <v>0</v>
       </c>
@@ -7364,13 +7365,13 @@
       <c r="B23" s="24"/>
     </row>
     <row r="24" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="93" t="s">
+      <c r="A24" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="93"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="93"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
@@ -7398,10 +7399,10 @@
       <c r="B25" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="94" t="s">
+      <c r="C25" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="94"/>
+      <c r="D25" s="61"/>
       <c r="E25" s="2" t="s">
         <v>12</v>
       </c>
@@ -7413,10 +7414,10 @@
       <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="86" t="s">
+      <c r="C26" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="86"/>
+      <c r="D26" s="59"/>
       <c r="E26" s="33">
         <v>2485</v>
       </c>
@@ -7424,8 +7425,8 @@
     <row r="27" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
-      <c r="C27" s="86"/>
-      <c r="D27" s="86"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
       <c r="E27" s="29">
         <v>0</v>
       </c>
@@ -7447,11 +7448,11 @@
       <c r="B29" s="24"/>
     </row>
     <row r="30" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="84" t="s">
+      <c r="A30" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="84"/>
-      <c r="C30" s="84"/>
+      <c r="B30" s="64"/>
+      <c r="C30" s="64"/>
     </row>
     <row r="31" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
@@ -7466,11 +7467,11 @@
       <c r="D31" s="37"/>
     </row>
     <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="81" t="s">
+      <c r="A32" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="81"/>
-      <c r="C32" s="81"/>
+      <c r="B32" s="65"/>
+      <c r="C32" s="65"/>
     </row>
     <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="50" t="s">
@@ -7516,16 +7517,16 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="85" t="s">
+      <c r="A37" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="85"/>
-      <c r="C37" s="85"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="66"/>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="85"/>
-      <c r="B38" s="85"/>
-      <c r="C38" s="85"/>
+      <c r="A38" s="66"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
     </row>
     <row r="39" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
@@ -7574,11 +7575,11 @@
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="81" t="s">
+      <c r="A44" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B44" s="81"/>
-      <c r="C44" s="81"/>
+      <c r="B44" s="65"/>
+      <c r="C44" s="65"/>
     </row>
     <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
@@ -7613,11 +7614,11 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="81" t="s">
+      <c r="A48" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="81"/>
-      <c r="C48" s="81"/>
+      <c r="B48" s="65"/>
+      <c r="C48" s="65"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -7641,11 +7642,11 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="81" t="s">
+      <c r="A51" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="81"/>
-      <c r="C51" s="81"/>
+      <c r="B51" s="65"/>
+      <c r="C51" s="65"/>
     </row>
     <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
@@ -7669,11 +7670,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="82" t="s">
+      <c r="A54" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="82"/>
-      <c r="C54" s="82"/>
+      <c r="B54" s="67"/>
+      <c r="C54" s="67"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="17" t="s">
@@ -7750,11 +7751,11 @@
       </c>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="82" t="s">
+      <c r="A62" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="B62" s="82"/>
-      <c r="C62" s="82"/>
+      <c r="B62" s="67"/>
+      <c r="C62" s="67"/>
     </row>
     <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
@@ -7804,91 +7805,91 @@
       <c r="B68" s="24"/>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="70" t="s">
+      <c r="A69" s="68" t="s">
         <v>129</v>
       </c>
-      <c r="B69" s="70"/>
-      <c r="C69" s="70"/>
-      <c r="D69" s="70"/>
-      <c r="E69" s="70"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="68"/>
+      <c r="D69" s="68"/>
+      <c r="E69" s="68"/>
     </row>
     <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="83" t="s">
+      <c r="A70" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="B70" s="83"/>
-      <c r="C70" s="83" t="s">
+      <c r="B70" s="69"/>
+      <c r="C70" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D70" s="83"/>
+      <c r="D70" s="69"/>
       <c r="E70" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="57" t="s">
+      <c r="A71" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="B71" s="57"/>
-      <c r="C71" s="54"/>
-      <c r="D71" s="54"/>
+      <c r="B71" s="70"/>
+      <c r="C71" s="71"/>
+      <c r="D71" s="71"/>
       <c r="E71" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="73" t="s">
+      <c r="A72" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="B72" s="73"/>
-      <c r="C72" s="72" t="s">
+      <c r="B72" s="72"/>
+      <c r="C72" s="73" t="s">
         <v>122</v>
       </c>
-      <c r="D72" s="72"/>
+      <c r="D72" s="73"/>
       <c r="E72" s="45">
         <v>600</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="73"/>
-      <c r="B73" s="73"/>
-      <c r="C73" s="105" t="s">
+      <c r="A73" s="72"/>
+      <c r="B73" s="72"/>
+      <c r="C73" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="D73" s="71"/>
+      <c r="D73" s="75"/>
       <c r="E73" s="45">
         <v>1117.5</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="73"/>
-      <c r="B74" s="73"/>
-      <c r="C74" s="105" t="s">
+      <c r="A74" s="72"/>
+      <c r="B74" s="72"/>
+      <c r="C74" s="74" t="s">
         <v>137</v>
       </c>
-      <c r="D74" s="79"/>
+      <c r="D74" s="76"/>
       <c r="E74" s="45">
         <v>508</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="73" t="s">
+      <c r="A75" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="B75" s="73"/>
-      <c r="C75" s="74"/>
-      <c r="D75" s="74"/>
+      <c r="B75" s="72"/>
+      <c r="C75" s="77"/>
+      <c r="D75" s="77"/>
       <c r="E75" s="46">
         <f>C66</f>
         <v>1171</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C76" s="75" t="s">
+      <c r="C76" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D76" s="75"/>
+      <c r="D76" s="78"/>
       <c r="E76" s="47">
         <f>(E15+E71)-SUM(E72:E75)</f>
         <v>24.599999999999909</v>
@@ -7896,103 +7897,103 @@
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="70" t="s">
+      <c r="A78" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="B78" s="70"/>
-      <c r="C78" s="70"/>
-      <c r="D78" s="70"/>
-      <c r="E78" s="70"/>
+      <c r="B78" s="68"/>
+      <c r="C78" s="68"/>
+      <c r="D78" s="68"/>
+      <c r="E78" s="68"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="70" t="s">
+      <c r="A79" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="B79" s="70"/>
-      <c r="C79" s="70" t="s">
+      <c r="B79" s="68"/>
+      <c r="C79" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D79" s="70"/>
+      <c r="D79" s="68"/>
       <c r="E79" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="57" t="s">
+      <c r="A80" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="B80" s="57"/>
-      <c r="C80" s="55"/>
-      <c r="D80" s="55"/>
+      <c r="B80" s="70"/>
+      <c r="C80" s="79"/>
+      <c r="D80" s="79"/>
       <c r="E80" s="47">
         <f>E76</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="58" t="s">
+      <c r="A81" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="B81" s="59"/>
-      <c r="C81" s="102" t="s">
+      <c r="B81" s="87"/>
+      <c r="C81" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="D81" s="103"/>
+      <c r="D81" s="81"/>
       <c r="E81" s="48">
         <v>770.4</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="60"/>
-      <c r="B82" s="61"/>
-      <c r="C82" s="72" t="s">
+      <c r="A82" s="88"/>
+      <c r="B82" s="89"/>
+      <c r="C82" s="73" t="s">
         <v>138</v>
       </c>
-      <c r="D82" s="72"/>
+      <c r="D82" s="73"/>
       <c r="E82" s="48">
         <v>8.5</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="59" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="60"/>
-      <c r="B83" s="61"/>
-      <c r="C83" s="67" t="s">
+    <row r="83" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="88"/>
+      <c r="B83" s="89"/>
+      <c r="C83" s="84" t="s">
         <v>140</v>
       </c>
-      <c r="D83" s="104"/>
+      <c r="D83" s="85"/>
       <c r="E83" s="48">
-        <v>130.4</v>
+        <v>180.4</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="62"/>
-      <c r="B84" s="63"/>
-      <c r="C84" s="104"/>
-      <c r="D84" s="104"/>
+      <c r="A84" s="90"/>
+      <c r="B84" s="91"/>
+      <c r="C84" s="85"/>
+      <c r="D84" s="85"/>
       <c r="E84" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="54" t="s">
+      <c r="A85" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="B85" s="54"/>
-      <c r="C85" s="55"/>
-      <c r="D85" s="55"/>
+      <c r="B85" s="71"/>
+      <c r="C85" s="79"/>
+      <c r="D85" s="79"/>
       <c r="E85" s="45">
         <f>C66</f>
         <v>1171</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C86" s="56" t="s">
+      <c r="C86" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="D86" s="56"/>
+      <c r="D86" s="82"/>
       <c r="E86" s="47">
         <f>(E22+E80)-SUM(E81:E85)</f>
-        <v>479.29999999999973</v>
+        <v>429.29999999999973</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8010,72 +8011,72 @@
       <c r="E88" s="49"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="69" t="s">
+      <c r="A89" s="83" t="s">
         <v>131</v>
       </c>
-      <c r="B89" s="69"/>
-      <c r="C89" s="69"/>
-      <c r="D89" s="69"/>
-      <c r="E89" s="69"/>
+      <c r="B89" s="83"/>
+      <c r="C89" s="83"/>
+      <c r="D89" s="83"/>
+      <c r="E89" s="83"/>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="70" t="s">
+      <c r="A90" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="B90" s="70"/>
-      <c r="C90" s="70" t="s">
+      <c r="B90" s="68"/>
+      <c r="C90" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="70"/>
+      <c r="D90" s="68"/>
       <c r="E90" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="57" t="s">
+      <c r="A91" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="B91" s="57"/>
-      <c r="C91" s="55"/>
-      <c r="D91" s="55"/>
+      <c r="B91" s="70"/>
+      <c r="C91" s="79"/>
+      <c r="D91" s="79"/>
       <c r="E91" s="47">
         <f>E86</f>
-        <v>479.29999999999973</v>
+        <v>429.29999999999973</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="54" t="s">
+      <c r="A92" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B92" s="54"/>
-      <c r="C92" s="72" t="s">
+      <c r="B92" s="71"/>
+      <c r="C92" s="73" t="s">
         <v>118</v>
       </c>
-      <c r="D92" s="72"/>
+      <c r="D92" s="73"/>
       <c r="E92" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="54" t="s">
+      <c r="A93" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="B93" s="54"/>
-      <c r="C93" s="55"/>
-      <c r="D93" s="55"/>
+      <c r="B93" s="71"/>
+      <c r="C93" s="79"/>
+      <c r="D93" s="79"/>
       <c r="E93" s="45">
         <f>C66</f>
         <v>1171</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C94" s="56" t="s">
+      <c r="C94" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="D94" s="56"/>
+      <c r="D94" s="82"/>
       <c r="E94" s="47">
         <f>(E28+E91)-SUM(E92:E93)</f>
-        <v>1793.2999999999997</v>
+        <v>1743.2999999999997</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11824,46 +11825,13 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A37:C38"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="A72:B74"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:D93"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A89:E89"/>
@@ -11875,13 +11843,46 @@
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="A81:B84"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A72:B74"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="A37:C38"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E71">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B24202E8-395F-BC4A-99CB-7B465633410A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC0A926-547E-8346-974E-00D4A62E0292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -650,7 +650,8 @@
     <t>~ Debit For Octopus Card ($50). 20/08
 ~ OK Store buy additional 1 packet cigarette 20/08 - $78
 ~ Mail Chuk Yuen Post Office - $2.4
-~ Additional transport fees for e-cigarette 20/08 - $50</t>
+~ Additional transport fees for e-cigarette 20/08 - $50
+~ Paid Water Supplies Fees 20/08 - $74.1</t>
   </si>
 </sst>
 </file>
@@ -1177,83 +1178,20 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1261,10 +1199,10 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1291,10 +1229,97 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1309,35 +1334,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1656,13 +1657,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1683,7 +1684,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="9">
-        <v>380.5</v>
+        <v>306.39999999999998</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1839,7 +1840,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>429.3</v>
+        <v>355.2</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1892,13 +1893,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="88" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1926,10 +1927,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="56"/>
+      <c r="D11" s="89"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1941,10 +1942,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="92" t="s">
+      <c r="C12" s="106" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="92"/>
+      <c r="D12" s="106"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1956,10 +1957,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="93" t="s">
+      <c r="C13" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="93"/>
+      <c r="D13" s="107"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1969,10 +1970,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="59" t="s">
+      <c r="C14" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="59"/>
+      <c r="D14" s="82"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -1982,10 +1983,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="59" t="s">
+      <c r="C15" s="82" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="59"/>
+      <c r="D15" s="82"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -1995,10 +1996,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="59" t="s">
+      <c r="C16" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="59"/>
+      <c r="D16" s="82"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2010,10 +2011,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="94" t="s">
+      <c r="C17" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="94"/>
+      <c r="D17" s="102"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2023,10 +2024,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="95" t="s">
+      <c r="C18" s="103" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="95"/>
+      <c r="D18" s="103"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2038,10 +2039,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="96" t="s">
+      <c r="C19" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="96"/>
+      <c r="D19" s="104"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2062,13 +2063,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="60" t="s">
+      <c r="A22" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="84"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2096,10 +2097,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="97" t="s">
+      <c r="C23" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="97"/>
+      <c r="D23" s="105"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2111,10 +2112,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="59"/>
+      <c r="D24" s="82"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2126,10 +2127,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="59" t="s">
+      <c r="C25" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="59"/>
+      <c r="D25" s="82"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2139,10 +2140,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="91" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="94"/>
+      <c r="D26" s="102"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2154,10 +2155,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="95" t="s">
+      <c r="C27" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="95"/>
+      <c r="D27" s="103"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2167,10 +2168,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="98" t="s">
+      <c r="C28" s="92" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="98"/>
+      <c r="D28" s="92"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2192,13 +2193,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="60" t="s">
+      <c r="A31" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="60"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="60"/>
-      <c r="E31" s="60"/>
+      <c r="B31" s="84"/>
+      <c r="C31" s="84"/>
+      <c r="D31" s="84"/>
+      <c r="E31" s="84"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2226,10 +2227,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="61" t="s">
+      <c r="C32" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="61"/>
+      <c r="D32" s="81"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2241,10 +2242,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="59" t="s">
+      <c r="C33" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="59"/>
+      <c r="D33" s="82"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2254,10 +2255,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="59" t="s">
+      <c r="C34" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="59"/>
+      <c r="D34" s="82"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2267,10 +2268,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="99" t="s">
+      <c r="C35" s="100" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="63"/>
+      <c r="D35" s="86"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2280,10 +2281,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="99" t="s">
+      <c r="C36" s="100" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="100"/>
+      <c r="D36" s="101"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2293,10 +2294,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="58" t="s">
+      <c r="C37" s="91" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="59"/>
+      <c r="D37" s="82"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2318,11 +2319,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="64" t="s">
+      <c r="A40" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="64"/>
-      <c r="C40" s="64"/>
+      <c r="B40" s="83"/>
+      <c r="C40" s="83"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2337,11 +2338,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="65" t="s">
+      <c r="A42" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="65"/>
-      <c r="C42" s="65"/>
+      <c r="B42" s="80"/>
+      <c r="C42" s="80"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2387,16 +2388,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="66" t="s">
+      <c r="A47" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="66"/>
-      <c r="C47" s="66"/>
+      <c r="B47" s="79"/>
+      <c r="C47" s="79"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="66"/>
-      <c r="B48" s="66"/>
-      <c r="C48" s="66"/>
+      <c r="A48" s="79"/>
+      <c r="B48" s="79"/>
+      <c r="C48" s="79"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2445,11 +2446,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="65" t="s">
+      <c r="A54" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="65"/>
-      <c r="C54" s="65"/>
+      <c r="B54" s="80"/>
+      <c r="C54" s="80"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2484,11 +2485,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="65" t="s">
+      <c r="A58" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="65"/>
-      <c r="C58" s="65"/>
+      <c r="B58" s="80"/>
+      <c r="C58" s="80"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2512,11 +2513,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="65" t="s">
+      <c r="A61" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="65"/>
-      <c r="C61" s="65"/>
+      <c r="B61" s="80"/>
+      <c r="C61" s="80"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2540,11 +2541,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="67" t="s">
+      <c r="A64" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="67"/>
-      <c r="C64" s="67"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="77"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2621,11 +2622,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="67" t="s">
+      <c r="A72" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="67"/>
-      <c r="C72" s="67"/>
+      <c r="B72" s="77"/>
+      <c r="C72" s="77"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2675,146 +2676,146 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="68" t="s">
+      <c r="A79" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="B79" s="68"/>
-      <c r="C79" s="68"/>
-      <c r="D79" s="68"/>
-      <c r="E79" s="68"/>
+      <c r="B79" s="62"/>
+      <c r="C79" s="62"/>
+      <c r="D79" s="62"/>
+      <c r="E79" s="62"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="69" t="s">
+      <c r="A80" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="69"/>
-      <c r="C80" s="69" t="s">
+      <c r="B80" s="78"/>
+      <c r="C80" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="69"/>
+      <c r="D80" s="78"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="101" t="s">
+      <c r="A81" s="96" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="101"/>
-      <c r="C81" s="71"/>
-      <c r="D81" s="71"/>
+      <c r="B81" s="96"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="71" t="s">
+      <c r="A82" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="71"/>
-      <c r="C82" s="102" t="s">
+      <c r="B82" s="57"/>
+      <c r="C82" s="97" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="102"/>
+      <c r="D82" s="97"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="71"/>
-      <c r="B83" s="71"/>
-      <c r="C83" s="102" t="s">
+      <c r="A83" s="57"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="97" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="102"/>
+      <c r="D83" s="97"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="71"/>
-      <c r="B84" s="71"/>
-      <c r="C84" s="102" t="s">
+      <c r="A84" s="57"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="102"/>
+      <c r="D84" s="97"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="71"/>
-      <c r="B85" s="71"/>
-      <c r="C85" s="103" t="s">
+      <c r="A85" s="57"/>
+      <c r="B85" s="57"/>
+      <c r="C85" s="98" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="103"/>
+      <c r="D85" s="98"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="71"/>
-      <c r="B86" s="71"/>
-      <c r="C86" s="76" t="s">
+      <c r="A86" s="57"/>
+      <c r="B86" s="57"/>
+      <c r="C86" s="75" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="76"/>
+      <c r="D86" s="75"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="71"/>
-      <c r="B87" s="71"/>
-      <c r="C87" s="103" t="s">
+      <c r="A87" s="57"/>
+      <c r="B87" s="57"/>
+      <c r="C87" s="98" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="103"/>
+      <c r="D87" s="98"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="71"/>
-      <c r="B88" s="71"/>
-      <c r="C88" s="102" t="s">
+      <c r="A88" s="57"/>
+      <c r="B88" s="57"/>
+      <c r="C88" s="97" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="102"/>
+      <c r="D88" s="97"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="71"/>
-      <c r="B89" s="71"/>
-      <c r="C89" s="76" t="s">
+      <c r="A89" s="57"/>
+      <c r="B89" s="57"/>
+      <c r="C89" s="75" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="76"/>
+      <c r="D89" s="75"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="71"/>
-      <c r="B90" s="71"/>
-      <c r="C90" s="76" t="s">
+      <c r="A90" s="57"/>
+      <c r="B90" s="57"/>
+      <c r="C90" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="76"/>
+      <c r="D90" s="75"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="71"/>
-      <c r="B91" s="71"/>
-      <c r="C91" s="104" t="s">
+      <c r="A91" s="57"/>
+      <c r="B91" s="57"/>
+      <c r="C91" s="99" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="104"/>
+      <c r="D91" s="99"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
@@ -2824,18 +2825,18 @@
         <v>95</v>
       </c>
       <c r="B92" s="72"/>
-      <c r="C92" s="77"/>
-      <c r="D92" s="77"/>
+      <c r="C92" s="76"/>
+      <c r="D92" s="76"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="78" t="s">
+      <c r="C93" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="78"/>
+      <c r="D93" s="71"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2843,113 +2844,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="68" t="s">
+      <c r="A95" s="62" t="s">
         <v>127</v>
       </c>
-      <c r="B95" s="68"/>
-      <c r="C95" s="68"/>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
+      <c r="B95" s="62"/>
+      <c r="C95" s="62"/>
+      <c r="D95" s="62"/>
+      <c r="E95" s="62"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="68" t="s">
+      <c r="A96" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="68"/>
-      <c r="C96" s="68" t="s">
+      <c r="B96" s="62"/>
+      <c r="C96" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="68"/>
+      <c r="D96" s="62"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="70" t="s">
+      <c r="A97" s="55" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="70"/>
-      <c r="C97" s="79"/>
-      <c r="D97" s="79"/>
+      <c r="B97" s="55"/>
+      <c r="C97" s="56"/>
+      <c r="D97" s="56"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="71" t="s">
+      <c r="A98" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="71"/>
-      <c r="C98" s="75" t="s">
+      <c r="B98" s="57"/>
+      <c r="C98" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="75"/>
+      <c r="D98" s="74"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="71"/>
-      <c r="B99" s="71"/>
-      <c r="C99" s="73" t="s">
+      <c r="A99" s="57"/>
+      <c r="B99" s="57"/>
+      <c r="C99" s="58" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="73"/>
+      <c r="D99" s="58"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="71"/>
-      <c r="B100" s="71"/>
-      <c r="C100" s="73" t="s">
+      <c r="A100" s="57"/>
+      <c r="B100" s="57"/>
+      <c r="C100" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="73"/>
+      <c r="D100" s="58"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="71"/>
-      <c r="B101" s="71"/>
-      <c r="C101" s="73" t="s">
+      <c r="A101" s="57"/>
+      <c r="B101" s="57"/>
+      <c r="C101" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="73"/>
+      <c r="D101" s="58"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="71"/>
-      <c r="B102" s="71"/>
-      <c r="C102" s="84" t="s">
+      <c r="A102" s="57"/>
+      <c r="B102" s="57"/>
+      <c r="C102" s="63" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="105"/>
+      <c r="D102" s="95"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="71" t="s">
+      <c r="A103" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="71"/>
-      <c r="C103" s="79"/>
-      <c r="D103" s="79"/>
+      <c r="B103" s="57"/>
+      <c r="C103" s="56"/>
+      <c r="D103" s="56"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="82" t="s">
+      <c r="C104" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="82"/>
+      <c r="D104" s="54"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2970,91 +2971,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="83" t="s">
+      <c r="A107" s="61" t="s">
         <v>128</v>
       </c>
-      <c r="B107" s="83"/>
-      <c r="C107" s="83"/>
-      <c r="D107" s="83"/>
-      <c r="E107" s="83"/>
+      <c r="B107" s="61"/>
+      <c r="C107" s="61"/>
+      <c r="D107" s="61"/>
+      <c r="E107" s="61"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="68" t="s">
+      <c r="A108" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="68"/>
-      <c r="C108" s="68" t="s">
+      <c r="B108" s="62"/>
+      <c r="C108" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="68"/>
+      <c r="D108" s="62"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="70" t="s">
+      <c r="A109" s="55" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="70"/>
-      <c r="C109" s="79"/>
-      <c r="D109" s="79"/>
+      <c r="B109" s="55"/>
+      <c r="C109" s="56"/>
+      <c r="D109" s="56"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="86" t="s">
+      <c r="A110" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="87"/>
-      <c r="C110" s="98" t="s">
+      <c r="B110" s="66"/>
+      <c r="C110" s="92" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="98"/>
+      <c r="D110" s="92"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="88"/>
-      <c r="B111" s="89"/>
-      <c r="C111" s="106" t="s">
+      <c r="A111" s="67"/>
+      <c r="B111" s="68"/>
+      <c r="C111" s="93" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="107"/>
+      <c r="D111" s="94"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="90"/>
-      <c r="B112" s="91"/>
-      <c r="C112" s="84" t="s">
+      <c r="A112" s="69"/>
+      <c r="B112" s="70"/>
+      <c r="C112" s="63" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="105"/>
+      <c r="D112" s="95"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="71" t="s">
+      <c r="A113" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="71"/>
-      <c r="C113" s="79"/>
-      <c r="D113" s="79"/>
+      <c r="B113" s="57"/>
+      <c r="C113" s="56"/>
+      <c r="D113" s="56"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="82" t="s">
+      <c r="C114" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="82"/>
+      <c r="D114" s="54"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6806,35 +6807,42 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6848,42 +6856,35 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6923,13 +6924,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="87" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -6951,7 +6952,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>380.5</v>
+        <v>306.39999999999998</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -7111,7 +7112,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>429.3</v>
+        <v>355.2</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7164,13 +7165,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="88" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
+      <c r="B10" s="88"/>
+      <c r="C10" s="88"/>
+      <c r="D10" s="88"/>
+      <c r="E10" s="88"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7198,10 +7199,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="56"/>
+      <c r="D11" s="89"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7213,10 +7214,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="57"/>
+      <c r="D12" s="90"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7228,10 +7229,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="59" t="s">
+      <c r="C13" s="82" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="59"/>
+      <c r="D13" s="82"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7243,10 +7244,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="91" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="59"/>
+      <c r="D14" s="82"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7267,13 +7268,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="60" t="s">
+      <c r="A17" s="84" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="60"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="60"/>
-      <c r="E17" s="60"/>
+      <c r="B17" s="84"/>
+      <c r="C17" s="84"/>
+      <c r="D17" s="84"/>
+      <c r="E17" s="84"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7301,10 +7302,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="61" t="s">
+      <c r="C18" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="61"/>
+      <c r="D18" s="81"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7316,10 +7317,10 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="59"/>
+      <c r="D19" s="82"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
@@ -7331,10 +7332,10 @@
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="62" t="s">
+      <c r="C20" s="85" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="63"/>
+      <c r="D20" s="86"/>
       <c r="E20" s="29">
         <v>50</v>
       </c>
@@ -7342,8 +7343,8 @@
     <row r="21" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
+      <c r="C21" s="82"/>
+      <c r="D21" s="82"/>
       <c r="E21" s="29">
         <v>0</v>
       </c>
@@ -7365,13 +7366,13 @@
       <c r="B23" s="24"/>
     </row>
     <row r="24" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="60" t="s">
+      <c r="A24" s="84" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="60"/>
-      <c r="C24" s="60"/>
-      <c r="D24" s="60"/>
-      <c r="E24" s="60"/>
+      <c r="B24" s="84"/>
+      <c r="C24" s="84"/>
+      <c r="D24" s="84"/>
+      <c r="E24" s="84"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
       <c r="I24" s="11"/>
@@ -7399,10 +7400,10 @@
       <c r="B25" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="61" t="s">
+      <c r="C25" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="61"/>
+      <c r="D25" s="81"/>
       <c r="E25" s="2" t="s">
         <v>12</v>
       </c>
@@ -7414,10 +7415,10 @@
       <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="59" t="s">
+      <c r="C26" s="82" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="59"/>
+      <c r="D26" s="82"/>
       <c r="E26" s="33">
         <v>2485</v>
       </c>
@@ -7425,8 +7426,8 @@
     <row r="27" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
-      <c r="C27" s="59"/>
-      <c r="D27" s="59"/>
+      <c r="C27" s="82"/>
+      <c r="D27" s="82"/>
       <c r="E27" s="29">
         <v>0</v>
       </c>
@@ -7448,11 +7449,11 @@
       <c r="B29" s="24"/>
     </row>
     <row r="30" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="64" t="s">
+      <c r="A30" s="83" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="64"/>
-      <c r="C30" s="64"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="83"/>
     </row>
     <row r="31" spans="1:25" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
@@ -7467,11 +7468,11 @@
       <c r="D31" s="37"/>
     </row>
     <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="65" t="s">
+      <c r="A32" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="65"/>
-      <c r="C32" s="65"/>
+      <c r="B32" s="80"/>
+      <c r="C32" s="80"/>
     </row>
     <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="50" t="s">
@@ -7517,16 +7518,16 @@
       </c>
     </row>
     <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="66" t="s">
+      <c r="A37" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="66"/>
-      <c r="C37" s="66"/>
+      <c r="B37" s="79"/>
+      <c r="C37" s="79"/>
     </row>
     <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="66"/>
-      <c r="B38" s="66"/>
-      <c r="C38" s="66"/>
+      <c r="A38" s="79"/>
+      <c r="B38" s="79"/>
+      <c r="C38" s="79"/>
     </row>
     <row r="39" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
@@ -7575,11 +7576,11 @@
       </c>
     </row>
     <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="65" t="s">
+      <c r="A44" s="80" t="s">
         <v>53</v>
       </c>
-      <c r="B44" s="65"/>
-      <c r="C44" s="65"/>
+      <c r="B44" s="80"/>
+      <c r="C44" s="80"/>
     </row>
     <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
@@ -7614,11 +7615,11 @@
       </c>
     </row>
     <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="65" t="s">
+      <c r="A48" s="80" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="65"/>
-      <c r="C48" s="65"/>
+      <c r="B48" s="80"/>
+      <c r="C48" s="80"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -7642,11 +7643,11 @@
       </c>
     </row>
     <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="65" t="s">
+      <c r="A51" s="80" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="65"/>
-      <c r="C51" s="65"/>
+      <c r="B51" s="80"/>
+      <c r="C51" s="80"/>
     </row>
     <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
@@ -7670,11 +7671,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="67" t="s">
+      <c r="A54" s="77" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="67"/>
-      <c r="C54" s="67"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="77"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="17" t="s">
@@ -7751,11 +7752,11 @@
       </c>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="67" t="s">
+      <c r="A62" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="B62" s="67"/>
-      <c r="C62" s="67"/>
+      <c r="B62" s="77"/>
+      <c r="C62" s="77"/>
     </row>
     <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="7" t="s">
@@ -7805,34 +7806,34 @@
       <c r="B68" s="24"/>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="68" t="s">
+      <c r="A69" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68"/>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
+      <c r="B69" s="62"/>
+      <c r="C69" s="62"/>
+      <c r="D69" s="62"/>
+      <c r="E69" s="62"/>
     </row>
     <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="69" t="s">
+      <c r="A70" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="B70" s="69"/>
-      <c r="C70" s="69" t="s">
+      <c r="B70" s="78"/>
+      <c r="C70" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="D70" s="69"/>
+      <c r="D70" s="78"/>
       <c r="E70" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="70" t="s">
+      <c r="A71" s="55" t="s">
         <v>107</v>
       </c>
-      <c r="B71" s="70"/>
-      <c r="C71" s="71"/>
-      <c r="D71" s="71"/>
+      <c r="B71" s="55"/>
+      <c r="C71" s="57"/>
+      <c r="D71" s="57"/>
       <c r="E71" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
@@ -7843,10 +7844,10 @@
         <v>67</v>
       </c>
       <c r="B72" s="72"/>
-      <c r="C72" s="73" t="s">
+      <c r="C72" s="58" t="s">
         <v>122</v>
       </c>
-      <c r="D72" s="73"/>
+      <c r="D72" s="58"/>
       <c r="E72" s="45">
         <v>600</v>
       </c>
@@ -7854,10 +7855,10 @@
     <row r="73" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="72"/>
       <c r="B73" s="72"/>
-      <c r="C73" s="74" t="s">
+      <c r="C73" s="73" t="s">
         <v>135</v>
       </c>
-      <c r="D73" s="75"/>
+      <c r="D73" s="74"/>
       <c r="E73" s="45">
         <v>1117.5</v>
       </c>
@@ -7865,10 +7866,10 @@
     <row r="74" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="72"/>
       <c r="B74" s="72"/>
-      <c r="C74" s="74" t="s">
+      <c r="C74" s="73" t="s">
         <v>137</v>
       </c>
-      <c r="D74" s="76"/>
+      <c r="D74" s="75"/>
       <c r="E74" s="45">
         <v>508</v>
       </c>
@@ -7878,18 +7879,18 @@
         <v>95</v>
       </c>
       <c r="B75" s="72"/>
-      <c r="C75" s="77"/>
-      <c r="D75" s="77"/>
+      <c r="C75" s="76"/>
+      <c r="D75" s="76"/>
       <c r="E75" s="46">
         <f>C66</f>
         <v>1171</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C76" s="78" t="s">
+      <c r="C76" s="71" t="s">
         <v>96</v>
       </c>
-      <c r="D76" s="78"/>
+      <c r="D76" s="71"/>
       <c r="E76" s="47">
         <f>(E15+E71)-SUM(E72:E75)</f>
         <v>24.599999999999909</v>
@@ -7897,103 +7898,103 @@
     </row>
     <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="68" t="s">
+      <c r="A78" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="B78" s="68"/>
-      <c r="C78" s="68"/>
-      <c r="D78" s="68"/>
-      <c r="E78" s="68"/>
+      <c r="B78" s="62"/>
+      <c r="C78" s="62"/>
+      <c r="D78" s="62"/>
+      <c r="E78" s="62"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="68" t="s">
+      <c r="A79" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="B79" s="68"/>
-      <c r="C79" s="68" t="s">
+      <c r="B79" s="62"/>
+      <c r="C79" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D79" s="68"/>
+      <c r="D79" s="62"/>
       <c r="E79" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="70" t="s">
+      <c r="A80" s="55" t="s">
         <v>108</v>
       </c>
-      <c r="B80" s="70"/>
-      <c r="C80" s="79"/>
-      <c r="D80" s="79"/>
+      <c r="B80" s="55"/>
+      <c r="C80" s="56"/>
+      <c r="D80" s="56"/>
       <c r="E80" s="47">
         <f>E76</f>
         <v>24.599999999999909</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="86" t="s">
+      <c r="A81" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B81" s="87"/>
-      <c r="C81" s="80" t="s">
+      <c r="B81" s="66"/>
+      <c r="C81" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="D81" s="81"/>
+      <c r="D81" s="60"/>
       <c r="E81" s="48">
         <v>770.4</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="88"/>
-      <c r="B82" s="89"/>
-      <c r="C82" s="73" t="s">
+      <c r="A82" s="67"/>
+      <c r="B82" s="68"/>
+      <c r="C82" s="58" t="s">
         <v>138</v>
       </c>
-      <c r="D82" s="73"/>
+      <c r="D82" s="58"/>
       <c r="E82" s="48">
         <v>8.5</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="88"/>
-      <c r="B83" s="89"/>
-      <c r="C83" s="84" t="s">
+    <row r="83" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="67"/>
+      <c r="B83" s="68"/>
+      <c r="C83" s="63" t="s">
         <v>140</v>
       </c>
-      <c r="D83" s="85"/>
+      <c r="D83" s="64"/>
       <c r="E83" s="48">
-        <v>180.4</v>
+        <v>254.5</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="90"/>
-      <c r="B84" s="91"/>
-      <c r="C84" s="85"/>
-      <c r="D84" s="85"/>
+      <c r="A84" s="69"/>
+      <c r="B84" s="70"/>
+      <c r="C84" s="64"/>
+      <c r="D84" s="64"/>
       <c r="E84" s="48">
         <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="71" t="s">
+      <c r="A85" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B85" s="71"/>
-      <c r="C85" s="79"/>
-      <c r="D85" s="79"/>
+      <c r="B85" s="57"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="56"/>
       <c r="E85" s="45">
         <f>C66</f>
         <v>1171</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C86" s="82" t="s">
+      <c r="C86" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="D86" s="82"/>
+      <c r="D86" s="54"/>
       <c r="E86" s="47">
         <f>(E22+E80)-SUM(E81:E85)</f>
-        <v>429.29999999999973</v>
+        <v>355.19999999999982</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -8011,72 +8012,72 @@
       <c r="E88" s="49"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="83" t="s">
+      <c r="A89" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="B89" s="83"/>
-      <c r="C89" s="83"/>
-      <c r="D89" s="83"/>
-      <c r="E89" s="83"/>
+      <c r="B89" s="61"/>
+      <c r="C89" s="61"/>
+      <c r="D89" s="61"/>
+      <c r="E89" s="61"/>
     </row>
     <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="68" t="s">
+      <c r="A90" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="B90" s="68"/>
-      <c r="C90" s="68" t="s">
+      <c r="B90" s="62"/>
+      <c r="C90" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="68"/>
+      <c r="D90" s="62"/>
       <c r="E90" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="70" t="s">
+      <c r="A91" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="B91" s="70"/>
-      <c r="C91" s="79"/>
-      <c r="D91" s="79"/>
+      <c r="B91" s="55"/>
+      <c r="C91" s="56"/>
+      <c r="D91" s="56"/>
       <c r="E91" s="47">
         <f>E86</f>
-        <v>429.29999999999973</v>
+        <v>355.19999999999982</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="71" t="s">
+      <c r="A92" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B92" s="71"/>
-      <c r="C92" s="73" t="s">
+      <c r="B92" s="57"/>
+      <c r="C92" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="D92" s="73"/>
+      <c r="D92" s="58"/>
       <c r="E92" s="45">
         <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="71" t="s">
+      <c r="A93" s="57" t="s">
         <v>95</v>
       </c>
-      <c r="B93" s="71"/>
-      <c r="C93" s="79"/>
-      <c r="D93" s="79"/>
+      <c r="B93" s="57"/>
+      <c r="C93" s="56"/>
+      <c r="D93" s="56"/>
       <c r="E93" s="45">
         <f>C66</f>
         <v>1171</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C94" s="82" t="s">
+      <c r="C94" s="54" t="s">
         <v>96</v>
       </c>
-      <c r="D94" s="82"/>
+      <c r="D94" s="54"/>
       <c r="E94" s="47">
         <f>(E28+E91)-SUM(E92:E93)</f>
-        <v>1743.2999999999997</v>
+        <v>1669.1999999999998</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -11825,13 +11826,46 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A37:C38"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A69:E69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="A72:B74"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="C86:D86"/>
     <mergeCell ref="A89:E89"/>
@@ -11843,46 +11877,13 @@
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="C85:D85"/>
     <mergeCell ref="A81:B84"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="A72:B74"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="A37:C38"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:D93"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E71">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">

--- a/Alan Tang_s Income Expense.xlsx
+++ b/Alan Tang_s Income Expense.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tangsinglun/private-repository/Income And Expense Forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC0A926-547E-8346-974E-00D4A62E0292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C1255F-868D-4140-AC3D-913A0D5D6570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="26400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="April 2026 - June 2026" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="145">
   <si>
     <t>Alan Tang's Income Expense For the Forecast Year 2026 April - June 2026</t>
   </si>
@@ -652,6 +652,18 @@
 ~ Mail Chuk Yuen Post Office - $2.4
 ~ Additional transport fees for e-cigarette 20/08 - $50
 ~ Paid Water Supplies Fees 20/08 - $74.1</t>
+  </si>
+  <si>
+    <t>23rd August 2026</t>
+  </si>
+  <si>
+    <t>Alipay</t>
+  </si>
+  <si>
+    <t>A discount of $3.08 for iHerb payment</t>
+  </si>
+  <si>
+    <t>~ iHerb Aveeno Lotion 23/08 - $136.64</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1029,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1178,20 +1190,83 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1199,10 +1274,10 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1229,97 +1304,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1334,10 +1322,45 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1657,13 +1680,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -1684,7 +1707,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="9">
-        <v>306.39999999999998</v>
+        <v>169.76</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -1777,7 +1800,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="9">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -1840,7 +1863,7 @@
       </c>
       <c r="C8" s="9">
         <f>SUM(C3:C7)</f>
-        <v>355.2</v>
+        <v>221.64000000000001</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -1893,13 +1916,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="88" t="s">
+      <c r="A10" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="88"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -1927,10 +1950,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="89" t="s">
+      <c r="C11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="89"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -1942,10 +1965,10 @@
       <c r="B12" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="106" t="s">
+      <c r="C12" s="92" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="106"/>
+      <c r="D12" s="92"/>
       <c r="E12" s="16">
         <v>2485</v>
       </c>
@@ -1957,10 +1980,10 @@
       <c r="B13" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="107" t="s">
+      <c r="C13" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="107"/>
+      <c r="D13" s="93"/>
       <c r="E13" s="18">
         <v>12</v>
       </c>
@@ -1970,10 +1993,10 @@
       <c r="B14" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="82" t="s">
+      <c r="C14" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="D14" s="82"/>
+      <c r="D14" s="59"/>
       <c r="E14" s="19">
         <v>900</v>
       </c>
@@ -1983,10 +2006,10 @@
       <c r="B15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="82" t="s">
+      <c r="C15" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="82"/>
+      <c r="D15" s="59"/>
       <c r="E15" s="19">
         <v>1050</v>
       </c>
@@ -1996,10 +2019,10 @@
       <c r="B16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="82" t="s">
+      <c r="C16" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="82"/>
+      <c r="D16" s="59"/>
       <c r="E16" s="19">
         <v>700</v>
       </c>
@@ -2011,10 +2034,10 @@
       <c r="B17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="102" t="s">
+      <c r="C17" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="D17" s="102"/>
+      <c r="D17" s="94"/>
       <c r="E17" s="21">
         <v>187.6</v>
       </c>
@@ -2024,10 +2047,10 @@
       <c r="B18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="103" t="s">
+      <c r="C18" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="103"/>
+      <c r="D18" s="95"/>
       <c r="E18" s="19">
         <v>118</v>
       </c>
@@ -2039,10 +2062,10 @@
       <c r="B19" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="104" t="s">
+      <c r="C19" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="104"/>
+      <c r="D19" s="96"/>
       <c r="E19" s="21">
         <v>50</v>
       </c>
@@ -2063,13 +2086,13 @@
       <c r="B21" s="24"/>
     </row>
     <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="84"/>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
+      <c r="B22" s="60"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="60"/>
+      <c r="E22" s="60"/>
       <c r="G22" s="11"/>
       <c r="H22" s="11"/>
       <c r="I22" s="11"/>
@@ -2097,10 +2120,10 @@
       <c r="B23" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="105" t="s">
+      <c r="C23" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="105"/>
+      <c r="D23" s="97"/>
       <c r="E23" s="3" t="s">
         <v>12</v>
       </c>
@@ -2112,10 +2135,10 @@
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="82" t="s">
+      <c r="C24" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="82"/>
+      <c r="D24" s="59"/>
       <c r="E24" s="29">
         <v>2485</v>
       </c>
@@ -2127,10 +2150,10 @@
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="82" t="s">
+      <c r="C25" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="82"/>
+      <c r="D25" s="59"/>
       <c r="E25" s="19">
         <v>2140</v>
       </c>
@@ -2140,10 +2163,10 @@
       <c r="B26" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="91" t="s">
+      <c r="C26" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="102"/>
+      <c r="D26" s="94"/>
       <c r="E26" s="19">
         <v>227.3</v>
       </c>
@@ -2155,10 +2178,10 @@
       <c r="B27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="103" t="s">
+      <c r="C27" s="95" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="103"/>
+      <c r="D27" s="95"/>
       <c r="E27" s="19">
         <v>205</v>
       </c>
@@ -2168,10 +2191,10 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="92" t="s">
+      <c r="C28" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="92"/>
+      <c r="D28" s="98"/>
       <c r="E28" s="19">
         <v>150</v>
       </c>
@@ -2193,13 +2216,13 @@
       <c r="B30" s="24"/>
     </row>
     <row r="31" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="84" t="s">
+      <c r="A31" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="84"/>
-      <c r="C31" s="84"/>
-      <c r="D31" s="84"/>
-      <c r="E31" s="84"/>
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
       <c r="G31" s="11"/>
       <c r="H31" s="11"/>
       <c r="I31" s="11"/>
@@ -2227,10 +2250,10 @@
       <c r="B32" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="81" t="s">
+      <c r="C32" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="81"/>
+      <c r="D32" s="61"/>
       <c r="E32" s="2" t="s">
         <v>12</v>
       </c>
@@ -2242,10 +2265,10 @@
       <c r="B33" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="82" t="s">
+      <c r="C33" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D33" s="82"/>
+      <c r="D33" s="59"/>
       <c r="E33" s="33">
         <v>2485</v>
       </c>
@@ -2255,10 +2278,10 @@
       <c r="B34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="82" t="s">
+      <c r="C34" s="59" t="s">
         <v>39</v>
       </c>
-      <c r="D34" s="82"/>
+      <c r="D34" s="59"/>
       <c r="E34" s="33">
         <v>118</v>
       </c>
@@ -2268,10 +2291,10 @@
       <c r="B35" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="100" t="s">
+      <c r="C35" s="99" t="s">
         <v>119</v>
       </c>
-      <c r="D35" s="86"/>
+      <c r="D35" s="63"/>
       <c r="E35" s="33">
         <v>170</v>
       </c>
@@ -2281,10 +2304,10 @@
       <c r="B36" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="100" t="s">
+      <c r="C36" s="99" t="s">
         <v>115</v>
       </c>
-      <c r="D36" s="101"/>
+      <c r="D36" s="100"/>
       <c r="E36" s="33">
         <v>800</v>
       </c>
@@ -2294,10 +2317,10 @@
       <c r="B37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="91" t="s">
+      <c r="C37" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="D37" s="82"/>
+      <c r="D37" s="59"/>
       <c r="E37" s="19">
         <v>200</v>
       </c>
@@ -2319,11 +2342,11 @@
       <c r="B39" s="24"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="83" t="s">
+      <c r="A40" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="83"/>
-      <c r="C40" s="83"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="64"/>
     </row>
     <row r="41" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
@@ -2338,11 +2361,11 @@
       <c r="D41" s="37"/>
     </row>
     <row r="42" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="80" t="s">
+      <c r="A42" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="80"/>
-      <c r="C42" s="80"/>
+      <c r="B42" s="65"/>
+      <c r="C42" s="65"/>
     </row>
     <row r="43" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="50" t="s">
@@ -2388,16 +2411,16 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="79" t="s">
+      <c r="A47" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="79"/>
-      <c r="C47" s="79"/>
+      <c r="B47" s="66"/>
+      <c r="C47" s="66"/>
     </row>
     <row r="48" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="79"/>
-      <c r="B48" s="79"/>
-      <c r="C48" s="79"/>
+      <c r="A48" s="66"/>
+      <c r="B48" s="66"/>
+      <c r="C48" s="66"/>
     </row>
     <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
@@ -2446,11 +2469,11 @@
       </c>
     </row>
     <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="80" t="s">
+      <c r="A54" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B54" s="80"/>
-      <c r="C54" s="80"/>
+      <c r="B54" s="65"/>
+      <c r="C54" s="65"/>
     </row>
     <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6" t="s">
@@ -2485,11 +2508,11 @@
       </c>
     </row>
     <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="80" t="s">
+      <c r="A58" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="80"/>
-      <c r="C58" s="80"/>
+      <c r="B58" s="65"/>
+      <c r="C58" s="65"/>
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
@@ -2513,11 +2536,11 @@
       </c>
     </row>
     <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="80" t="s">
+      <c r="A61" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="B61" s="80"/>
-      <c r="C61" s="80"/>
+      <c r="B61" s="65"/>
+      <c r="C61" s="65"/>
     </row>
     <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="6" t="s">
@@ -2541,11 +2564,11 @@
       </c>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="77" t="s">
+      <c r="A64" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="77"/>
-      <c r="C64" s="77"/>
+      <c r="B64" s="67"/>
+      <c r="C64" s="67"/>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="17" t="s">
@@ -2622,11 +2645,11 @@
       </c>
     </row>
     <row r="72" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="77" t="s">
+      <c r="A72" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="B72" s="77"/>
-      <c r="C72" s="77"/>
+      <c r="B72" s="67"/>
+      <c r="C72" s="67"/>
     </row>
     <row r="73" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="s">
@@ -2676,146 +2699,146 @@
       <c r="B78" s="24"/>
     </row>
     <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="62" t="s">
+      <c r="A79" s="68" t="s">
         <v>126</v>
       </c>
-      <c r="B79" s="62"/>
-      <c r="C79" s="62"/>
-      <c r="D79" s="62"/>
-      <c r="E79" s="62"/>
+      <c r="B79" s="68"/>
+      <c r="C79" s="68"/>
+      <c r="D79" s="68"/>
+      <c r="E79" s="68"/>
     </row>
     <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="78" t="s">
+      <c r="A80" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="B80" s="78"/>
-      <c r="C80" s="78" t="s">
+      <c r="B80" s="69"/>
+      <c r="C80" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="78"/>
+      <c r="D80" s="69"/>
       <c r="E80" s="44" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="96" t="s">
+      <c r="A81" s="101" t="s">
         <v>84</v>
       </c>
-      <c r="B81" s="96"/>
-      <c r="C81" s="57"/>
-      <c r="D81" s="57"/>
+      <c r="B81" s="101"/>
+      <c r="C81" s="71"/>
+      <c r="D81" s="71"/>
       <c r="E81" s="7">
         <v>21.98</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A82" s="57" t="s">
+      <c r="A82" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B82" s="57"/>
-      <c r="C82" s="97" t="s">
+      <c r="B82" s="71"/>
+      <c r="C82" s="102" t="s">
         <v>85</v>
       </c>
-      <c r="D82" s="97"/>
+      <c r="D82" s="102"/>
       <c r="E82" s="45">
         <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="220.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="57"/>
-      <c r="B83" s="57"/>
-      <c r="C83" s="97" t="s">
+      <c r="A83" s="71"/>
+      <c r="B83" s="71"/>
+      <c r="C83" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="D83" s="97"/>
+      <c r="D83" s="102"/>
       <c r="E83" s="45">
         <v>507.7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A84" s="57"/>
-      <c r="B84" s="57"/>
-      <c r="C84" s="97" t="s">
+      <c r="A84" s="71"/>
+      <c r="B84" s="71"/>
+      <c r="C84" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="D84" s="97"/>
+      <c r="D84" s="102"/>
       <c r="E84" s="45">
         <v>1728</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="57"/>
-      <c r="B85" s="57"/>
-      <c r="C85" s="98" t="s">
+      <c r="A85" s="71"/>
+      <c r="B85" s="71"/>
+      <c r="C85" s="103" t="s">
         <v>88</v>
       </c>
-      <c r="D85" s="98"/>
+      <c r="D85" s="103"/>
       <c r="E85" s="45">
         <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="57"/>
-      <c r="B86" s="57"/>
-      <c r="C86" s="75" t="s">
+      <c r="A86" s="71"/>
+      <c r="B86" s="71"/>
+      <c r="C86" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="D86" s="75"/>
+      <c r="D86" s="76"/>
       <c r="E86" s="45">
         <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="57"/>
-      <c r="B87" s="57"/>
-      <c r="C87" s="98" t="s">
+      <c r="A87" s="71"/>
+      <c r="B87" s="71"/>
+      <c r="C87" s="103" t="s">
         <v>90</v>
       </c>
-      <c r="D87" s="98"/>
+      <c r="D87" s="103"/>
       <c r="E87" s="45">
         <v>697</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="57"/>
-      <c r="B88" s="57"/>
-      <c r="C88" s="97" t="s">
+      <c r="A88" s="71"/>
+      <c r="B88" s="71"/>
+      <c r="C88" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="D88" s="97"/>
+      <c r="D88" s="102"/>
       <c r="E88" s="45">
         <v>5.4</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="57"/>
-      <c r="B89" s="57"/>
-      <c r="C89" s="75" t="s">
+      <c r="A89" s="71"/>
+      <c r="B89" s="71"/>
+      <c r="C89" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="D89" s="75"/>
+      <c r="D89" s="76"/>
       <c r="E89" s="45">
         <v>136</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="57"/>
-      <c r="B90" s="57"/>
-      <c r="C90" s="75" t="s">
+      <c r="A90" s="71"/>
+      <c r="B90" s="71"/>
+      <c r="C90" s="76" t="s">
         <v>93</v>
       </c>
-      <c r="D90" s="75"/>
+      <c r="D90" s="76"/>
       <c r="E90" s="45">
         <v>112.3</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="57"/>
-      <c r="B91" s="57"/>
-      <c r="C91" s="99" t="s">
+      <c r="A91" s="71"/>
+      <c r="B91" s="71"/>
+      <c r="C91" s="104" t="s">
         <v>94</v>
       </c>
-      <c r="D91" s="99"/>
+      <c r="D91" s="104"/>
       <c r="E91" s="45">
         <v>366.38</v>
       </c>
@@ -2825,18 +2848,18 @@
         <v>95</v>
       </c>
       <c r="B92" s="72"/>
-      <c r="C92" s="76"/>
-      <c r="D92" s="76"/>
+      <c r="C92" s="77"/>
+      <c r="D92" s="77"/>
       <c r="E92" s="46">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C93" s="71" t="s">
+      <c r="C93" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D93" s="71"/>
+      <c r="D93" s="78"/>
       <c r="E93" s="47">
         <f>(E20+E81)-SUM(E82:E92)</f>
         <v>-31.199999999999818</v>
@@ -2844,113 +2867,113 @@
     </row>
     <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="62" t="s">
+      <c r="A95" s="68" t="s">
         <v>127</v>
       </c>
-      <c r="B95" s="62"/>
-      <c r="C95" s="62"/>
-      <c r="D95" s="62"/>
-      <c r="E95" s="62"/>
+      <c r="B95" s="68"/>
+      <c r="C95" s="68"/>
+      <c r="D95" s="68"/>
+      <c r="E95" s="68"/>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="62" t="s">
+      <c r="A96" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="B96" s="62"/>
-      <c r="C96" s="62" t="s">
+      <c r="B96" s="68"/>
+      <c r="C96" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D96" s="62"/>
+      <c r="D96" s="68"/>
       <c r="E96" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="55" t="s">
+      <c r="A97" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="B97" s="55"/>
-      <c r="C97" s="56"/>
-      <c r="D97" s="56"/>
+      <c r="B97" s="70"/>
+      <c r="C97" s="79"/>
+      <c r="D97" s="79"/>
       <c r="E97" s="47">
         <f>E93</f>
         <v>-31.199999999999818</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="57" t="s">
+      <c r="A98" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="57"/>
-      <c r="C98" s="74" t="s">
+      <c r="B98" s="71"/>
+      <c r="C98" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="D98" s="74"/>
+      <c r="D98" s="75"/>
       <c r="E98" s="48">
         <v>747.6</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="57"/>
-      <c r="B99" s="57"/>
-      <c r="C99" s="58" t="s">
+      <c r="A99" s="71"/>
+      <c r="B99" s="71"/>
+      <c r="C99" s="73" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="58"/>
+      <c r="D99" s="73"/>
       <c r="E99" s="48">
         <v>900.2</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="57"/>
-      <c r="B100" s="57"/>
-      <c r="C100" s="58" t="s">
+      <c r="A100" s="71"/>
+      <c r="B100" s="71"/>
+      <c r="C100" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="D100" s="58"/>
+      <c r="D100" s="73"/>
       <c r="E100" s="48">
         <v>656.4</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="118.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="57"/>
-      <c r="B101" s="57"/>
-      <c r="C101" s="58" t="s">
+      <c r="A101" s="71"/>
+      <c r="B101" s="71"/>
+      <c r="C101" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="D101" s="58"/>
+      <c r="D101" s="73"/>
       <c r="E101" s="48">
         <v>167.4</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="57"/>
-      <c r="B102" s="57"/>
-      <c r="C102" s="63" t="s">
+      <c r="A102" s="71"/>
+      <c r="B102" s="71"/>
+      <c r="C102" s="84" t="s">
         <v>99</v>
       </c>
-      <c r="D102" s="95"/>
+      <c r="D102" s="105"/>
       <c r="E102" s="48">
         <v>1109</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="57" t="s">
+      <c r="A103" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="B103" s="57"/>
-      <c r="C103" s="56"/>
-      <c r="D103" s="56"/>
+      <c r="B103" s="71"/>
+      <c r="C103" s="79"/>
+      <c r="D103" s="79"/>
       <c r="E103" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C104" s="54" t="s">
+      <c r="C104" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="D104" s="54"/>
+      <c r="D104" s="82"/>
       <c r="E104" s="47">
         <f>(E29+E97)-SUM(E98:E103)</f>
         <v>228.5</v>
@@ -2971,91 +2994,91 @@
       <c r="E106" s="49"/>
     </row>
     <row r="107" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="61" t="s">
+      <c r="A107" s="83" t="s">
         <v>128</v>
       </c>
-      <c r="B107" s="61"/>
-      <c r="C107" s="61"/>
-      <c r="D107" s="61"/>
-      <c r="E107" s="61"/>
+      <c r="B107" s="83"/>
+      <c r="C107" s="83"/>
+      <c r="D107" s="83"/>
+      <c r="E107" s="83"/>
     </row>
     <row r="108" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="62" t="s">
+      <c r="A108" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="B108" s="62"/>
-      <c r="C108" s="62" t="s">
+      <c r="B108" s="68"/>
+      <c r="C108" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D108" s="62"/>
+      <c r="D108" s="68"/>
       <c r="E108" s="43" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="55" t="s">
+      <c r="A109" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="B109" s="55"/>
-      <c r="C109" s="56"/>
-      <c r="D109" s="56"/>
+      <c r="B109" s="70"/>
+      <c r="C109" s="79"/>
+      <c r="D109" s="79"/>
       <c r="E109" s="47">
         <f>E104</f>
         <v>228.5</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="333" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="65" t="s">
+      <c r="A110" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="B110" s="66"/>
-      <c r="C110" s="92" t="s">
+      <c r="B110" s="87"/>
+      <c r="C110" s="98" t="s">
         <v>117</v>
       </c>
-      <c r="D110" s="92"/>
+      <c r="D110" s="98"/>
       <c r="E110" s="45">
         <v>870.3</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="67"/>
-      <c r="B111" s="68"/>
-      <c r="C111" s="93" t="s">
+      <c r="A111" s="88"/>
+      <c r="B111" s="89"/>
+      <c r="C111" s="106" t="s">
         <v>116</v>
       </c>
-      <c r="D111" s="94"/>
+      <c r="D111" s="107"/>
       <c r="E111" s="45">
         <v>1428</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="151" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="69"/>
-      <c r="B112" s="70"/>
-      <c r="C112" s="63" t="s">
+      <c r="A112" s="90"/>
+      <c r="B112" s="91"/>
+      <c r="C112" s="84" t="s">
         <v>121</v>
       </c>
-      <c r="D112" s="95"/>
+      <c r="D112" s="105"/>
       <c r="E112" s="45">
         <v>225.5</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="57" t="s">
+      <c r="A113" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="B113" s="57"/>
-      <c r="C113" s="56"/>
-      <c r="D113" s="56"/>
+      <c r="B113" s="71"/>
+      <c r="C113" s="79"/>
+      <c r="D113" s="79"/>
       <c r="E113" s="45">
         <f>C76</f>
         <v>1367</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C114" s="54" t="s">
+      <c r="C114" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="D114" s="54"/>
+      <c r="D114" s="82"/>
       <c r="E114" s="47">
         <f>(E38+E109)-SUM(E110:E113)</f>
         <v>110.69999999999982</v>
@@ -6807,42 +6830,35 @@
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A47:C48"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="A109:B109"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A110:B112"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="A108:B108"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="A98:B102"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="C96:D96"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="C81:D81"/>
     <mergeCell ref="A82:B91"/>
@@ -6856,35 +6872,42 @@
     <mergeCell ref="C89:D89"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="C93:D93"/>
-    <mergeCell ref="A95:E95"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:D96"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:D97"/>
-    <mergeCell ref="A98:B102"/>
-    <mergeCell ref="C98:D98"/>
-    <mergeCell ref="C99:D99"/>
-    <mergeCell ref="C100:D100"/>
-    <mergeCell ref="C101:D101"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="C104:D104"/>
-    <mergeCell ref="A107:E107"/>
-    <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="C113:D113"/>
-    <mergeCell ref="C114:D114"/>
-    <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A110:B112"/>
-    <mergeCell ref="C110:D110"/>
-    <mergeCell ref="C111:D111"/>
-    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C48"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C8 E81">
     <cfRule type="cellIs" dxfId="7" priority="2" operator="greaterThanOrEqual">
@@ -6909,7 +6932,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y1030"/>
+  <dimension ref="A1:Y1031"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.33203125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.5" customWidth="1"/>
@@ -6924,13 +6947,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
@@ -6952,7 +6975,7 @@
       </c>
       <c r="C3" s="9">
         <f>'April 2026 - June 2026'!C3</f>
-        <v>306.39999999999998</v>
+        <v>169.76</v>
       </c>
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
@@ -7048,7 +7071,7 @@
       </c>
       <c r="C6" s="9">
         <f>'April 2026 - June 2026'!C6</f>
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="10"/>
@@ -7112,7 +7135,7 @@
       </c>
       <c r="C8" s="9">
         <f>'April 2026 - June 2026'!C8</f>
-        <v>355.2</v>
+        <v>221.64000000000001</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -7165,13 +7188,13 @@
       <c r="Y9" s="11"/>
     </row>
     <row r="10" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="88" t="s">
+      <c r="A10" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="B10" s="88"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="11"/>
@@ -7199,10 +7222,10 @@
       <c r="B11" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="89" t="s">
+      <c r="C11" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="89"/>
+      <c r="D11" s="56"/>
       <c r="E11" s="4" t="s">
         <v>12</v>
       </c>
@@ -7214,10 +7237,10 @@
       <c r="B12" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="90" t="s">
+      <c r="C12" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="90"/>
+      <c r="D12" s="57"/>
       <c r="E12" s="52">
         <v>2485</v>
       </c>
@@ -7229,10 +7252,10 @@
       <c r="B13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="82" t="s">
+      <c r="C13" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="82"/>
+      <c r="D13" s="59"/>
       <c r="E13" s="29">
         <v>55</v>
       </c>
@@ -7244,10 +7267,10 @@
       <c r="B14" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="91" t="s">
+      <c r="C14" s="58" t="s">
         <v>134</v>
       </c>
-      <c r="D14" s="82"/>
+      <c r="D14" s="59"/>
       <c r="E14" s="29">
         <v>770.4</v>
       </c>
@@ -7268,13 +7291,13 @@
       <c r="B16" s="24"/>
     </row>
     <row r="17" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="84" t="s">
+      <c r="A17" s="60" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="84"/>
-      <c r="C17" s="84"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="84"/>
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
@@ -7302,10 +7325,10 @@
       <c r="B18" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="81" t="s">
+      <c r="C18" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="81"/>
+      <c r="D18" s="61"/>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
@@ -7317,239 +7340,245 @@
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="82" t="s">
+      <c r="C19" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="82"/>
+      <c r="D19" s="59"/>
       <c r="E19" s="29">
         <v>2485</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="50" t="s">
         <v>132</v>
       </c>
       <c r="B20" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="85" t="s">
+      <c r="C20" s="62" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="86"/>
+      <c r="D20" s="63"/>
       <c r="E20" s="29">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="82"/>
-      <c r="D21" s="82"/>
+    <row r="21" spans="1:25" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="109" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" s="109" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" s="111" t="s">
+        <v>143</v>
+      </c>
+      <c r="D21" s="110"/>
       <c r="E21" s="29">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="108"/>
+      <c r="E22" s="29">
         <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="26">
-        <f>SUM(E19:E21)</f>
-        <v>2535</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="24"/>
       <c r="B23" s="24"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="26">
+        <f>SUM(E19:E22)</f>
+        <v>2538.08</v>
+      </c>
     </row>
     <row r="24" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="84" t="s">
+      <c r="A24" s="24"/>
+      <c r="B24" s="24"/>
+    </row>
+    <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="60" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="84"/>
-      <c r="C24" s="84"/>
-      <c r="D24" s="84"/>
-      <c r="E24" s="84"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="11"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
-      <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
-      <c r="S24" s="11"/>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
-      <c r="V24" s="11"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="11"/>
-    </row>
-    <row r="25" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="31" t="s">
+      <c r="B25" s="60"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="60"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="11"/>
+      <c r="V25" s="11"/>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="11"/>
+    </row>
+    <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="32" t="s">
+      <c r="B26" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="81" t="s">
+      <c r="C26" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="81"/>
-      <c r="E25" s="2" t="s">
+      <c r="D26" s="61"/>
+      <c r="E26" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="50" t="s">
+    <row r="27" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="82" t="s">
+      <c r="C27" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="82"/>
-      <c r="E26" s="33">
+      <c r="D27" s="59"/>
+      <c r="E27" s="33">
         <v>2485</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="82"/>
-      <c r="D27" s="82"/>
-      <c r="E27" s="29">
+    <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="29">
         <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="24"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="35">
-        <f>SUM(E26:E27)</f>
-        <v>2485</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="24"/>
       <c r="B29" s="24"/>
-    </row>
-    <row r="30" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="83" t="s">
+      <c r="C29" s="5"/>
+      <c r="D29" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E29" s="35">
+        <f>SUM(E27:E28)</f>
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+    </row>
+    <row r="31" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="64" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="83"/>
-      <c r="C30" s="83"/>
-    </row>
-    <row r="31" spans="1:25" ht="17" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
+    </row>
+    <row r="32" spans="1:25" ht="17" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C32" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="37"/>
-    </row>
-    <row r="32" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="80" t="s">
+      <c r="D32" s="37"/>
+    </row>
+    <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="80"/>
-      <c r="C32" s="80"/>
-    </row>
-    <row r="33" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="50" t="s">
+      <c r="B33" s="65"/>
+      <c r="C33" s="65"/>
+    </row>
+    <row r="34" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="50" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="50" t="s">
+      <c r="B34" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C34" s="33">
         <v>78</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="38">
-        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B36" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="38">
+      <c r="C36" s="38">
         <v>138</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="7"/>
-      <c r="B36" s="6" t="s">
+    <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="7"/>
+      <c r="B37" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C36" s="39">
-        <f>SUM(C33:C35)</f>
+      <c r="C37" s="39">
+        <f>SUM(C34:C36)</f>
         <v>216</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="79" t="s">
+    <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="B37" s="79"/>
-      <c r="C37" s="79"/>
-    </row>
-    <row r="38" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="79"/>
-      <c r="B38" s="79"/>
-      <c r="C38" s="79"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
     </row>
     <row r="39" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="29">
-        <v>0</v>
-      </c>
+      <c r="A39" s="66"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="66"/>
     </row>
     <row r="40" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B40" s="6"/>
-      <c r="C40" s="19">
+      <c r="C40" s="29">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="19">
@@ -7558,7 +7587,7 @@
     </row>
     <row r="42" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="19">
@@ -7566,156 +7595,154 @@
       </c>
     </row>
     <row r="43" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6" t="s">
+      <c r="A43" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C43" s="39">
-        <f>SUM(C39:C42)</f>
+      <c r="C44" s="39">
+        <f>SUM(C40:C43)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="80" t="s">
+    <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="B44" s="80"/>
-      <c r="C44" s="80"/>
-    </row>
-    <row r="45" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" s="33">
-        <v>0</v>
-      </c>
+      <c r="B45" s="65"/>
+      <c r="C45" s="65"/>
     </row>
     <row r="46" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C46" s="33">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="6"/>
+      <c r="A47" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="B47" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C47" s="39">
-        <f>SUM(C45:C46)</f>
+      <c r="C48" s="39">
+        <f>SUM(C46:C47)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="80" t="s">
+    <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="B48" s="80"/>
-      <c r="C48" s="80"/>
-    </row>
-    <row r="49" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="6" t="s">
+      <c r="B49" s="65"/>
+      <c r="C49" s="65"/>
+    </row>
+    <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B50" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17" t="s">
+    <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="17"/>
+      <c r="B51" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C50" s="39">
-        <f>SUM(C49)</f>
+      <c r="C51" s="39">
+        <f>SUM(C50)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="80" t="s">
+    <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="B51" s="80"/>
-      <c r="C51" s="80"/>
-    </row>
-    <row r="52" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
+      <c r="B52" s="65"/>
+      <c r="C52" s="65"/>
+    </row>
+    <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B53" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6" t="s">
+    <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C53" s="39">
-        <f>SUM(C52)</f>
+      <c r="C54" s="39">
+        <f>SUM(C53)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="77" t="s">
+    <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="77"/>
-      <c r="C54" s="77"/>
-    </row>
-    <row r="55" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="17" t="s">
+      <c r="B55" s="67"/>
+      <c r="C55" s="67"/>
+    </row>
+    <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B56" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C55" s="40">
+      <c r="C56" s="40">
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="6" t="s">
+    <row r="57" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B57" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <v>900</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="32" x14ac:dyDescent="0.2">
-      <c r="A57" s="6" t="s">
+    <row r="58" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A58" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B58" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="C57" s="29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="C58" s="29">
         <v>0</v>
@@ -7723,53 +7750,55 @@
     </row>
     <row r="59" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C59" s="29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B59" s="6"/>
-      <c r="C59" s="29">
+      <c r="B60" s="6"/>
+      <c r="C60" s="29">
         <v>55</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="7" t="s">
+    <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B61" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C60" s="19">
+      <c r="C61" s="19">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="7"/>
-      <c r="B61" s="7" t="s">
+    <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="7"/>
+      <c r="B62" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="C61" s="39">
-        <f>SUM(C55:C60)</f>
+      <c r="C62" s="39">
+        <f>SUM(C56:C61)</f>
         <v>955</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="77" t="s">
+    <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="B62" s="77"/>
-      <c r="C62" s="77"/>
-    </row>
-    <row r="63" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B63" s="7"/>
-      <c r="C63" s="19">
-        <v>0</v>
-      </c>
+      <c r="B63" s="67"/>
+      <c r="C63" s="67"/>
     </row>
     <row r="64" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="B64" s="7"/>
       <c r="C64" s="19">
@@ -7777,232 +7806,236 @@
       </c>
     </row>
     <row r="65" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="7"/>
-      <c r="B65" s="7" t="s">
+      <c r="A65" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="7"/>
+      <c r="C65" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="7"/>
+      <c r="B66" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C65" s="19">
-        <f>SUM(C63:C64)</f>
+      <c r="C66" s="19">
+        <f>SUM(C64:C65)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="6"/>
-      <c r="B66" s="34" t="s">
+    <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="6"/>
+      <c r="B67" s="34" t="s">
         <v>82</v>
       </c>
-      <c r="C66" s="41">
-        <f>C36+C43+C47+C50+C53+C61</f>
+      <c r="C67" s="41">
+        <f>C37+C44+C48+C51+C54+C62</f>
         <v>1171</v>
       </c>
-      <c r="H66" s="42"/>
-    </row>
-    <row r="67" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="24"/>
-      <c r="B67" s="24"/>
+      <c r="H67" s="42"/>
     </row>
     <row r="68" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="24"/>
       <c r="B68" s="24"/>
     </row>
     <row r="69" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="62" t="s">
+      <c r="A69" s="24"/>
+      <c r="B69" s="24"/>
+    </row>
+    <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="68" t="s">
         <v>129</v>
       </c>
-      <c r="B69" s="62"/>
-      <c r="C69" s="62"/>
-      <c r="D69" s="62"/>
-      <c r="E69" s="62"/>
-    </row>
-    <row r="70" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="78" t="s">
+      <c r="B70" s="68"/>
+      <c r="C70" s="68"/>
+      <c r="D70" s="68"/>
+      <c r="E70" s="68"/>
+    </row>
+    <row r="71" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="B70" s="78"/>
-      <c r="C70" s="78" t="s">
+      <c r="B71" s="69"/>
+      <c r="C71" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="D70" s="78"/>
-      <c r="E70" s="44" t="s">
+      <c r="D71" s="69"/>
+      <c r="E71" s="44" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="55" t="s">
+    <row r="72" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="70" t="s">
         <v>107</v>
       </c>
-      <c r="B71" s="55"/>
-      <c r="C71" s="57"/>
-      <c r="D71" s="57"/>
-      <c r="E71" s="47">
+      <c r="B72" s="70"/>
+      <c r="C72" s="71"/>
+      <c r="D72" s="71"/>
+      <c r="E72" s="47">
         <f>'April 2026 - June 2026'!E114</f>
         <v>110.69999999999982</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="72" t="s">
+    <row r="73" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="B72" s="72"/>
-      <c r="C72" s="58" t="s">
-        <v>122</v>
-      </c>
-      <c r="D72" s="58"/>
-      <c r="E72" s="45">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="72"/>
       <c r="B73" s="72"/>
       <c r="C73" s="73" t="s">
-        <v>135</v>
-      </c>
-      <c r="D73" s="74"/>
+        <v>122</v>
+      </c>
+      <c r="D73" s="73"/>
       <c r="E73" s="45">
-        <v>1117.5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="259" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="72"/>
       <c r="B74" s="72"/>
-      <c r="C74" s="73" t="s">
-        <v>137</v>
+      <c r="C74" s="74" t="s">
+        <v>135</v>
       </c>
       <c r="D74" s="75"/>
       <c r="E74" s="45">
+        <v>1117.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="146" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="72"/>
+      <c r="B75" s="72"/>
+      <c r="C75" s="74" t="s">
+        <v>137</v>
+      </c>
+      <c r="D75" s="76"/>
+      <c r="E75" s="45">
         <v>508</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="72" t="s">
+    <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="72" t="s">
         <v>95</v>
       </c>
-      <c r="B75" s="72"/>
-      <c r="C75" s="76"/>
-      <c r="D75" s="76"/>
-      <c r="E75" s="46">
-        <f>C66</f>
+      <c r="B76" s="72"/>
+      <c r="C76" s="77"/>
+      <c r="D76" s="77"/>
+      <c r="E76" s="46">
+        <f>C67</f>
         <v>1171</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C76" s="71" t="s">
+    <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C77" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="D76" s="71"/>
-      <c r="E76" s="47">
-        <f>(E15+E71)-SUM(E72:E75)</f>
+      <c r="D77" s="78"/>
+      <c r="E77" s="47">
+        <f>(E15+E72)-SUM(E73:E76)</f>
         <v>24.599999999999909</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="62" t="s">
+    <row r="78" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="B78" s="62"/>
-      <c r="C78" s="62"/>
-      <c r="D78" s="62"/>
-      <c r="E78" s="62"/>
-    </row>
-    <row r="79" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="62" t="s">
+      <c r="B79" s="68"/>
+      <c r="C79" s="68"/>
+      <c r="D79" s="68"/>
+      <c r="E79" s="68"/>
+    </row>
+    <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="B79" s="62"/>
-      <c r="C79" s="62" t="s">
+      <c r="B80" s="68"/>
+      <c r="C80" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D79" s="62"/>
-      <c r="E79" s="43" t="s">
+      <c r="D80" s="68"/>
+      <c r="E80" s="43" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="55" t="s">
+    <row r="81" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="B80" s="55"/>
-      <c r="C80" s="56"/>
-      <c r="D80" s="56"/>
-      <c r="E80" s="47">
-        <f>E76</f>
+      <c r="B81" s="70"/>
+      <c r="C81" s="79"/>
+      <c r="D81" s="79"/>
+      <c r="E81" s="47">
+        <f>E77</f>
         <v>24.599999999999909</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="65" t="s">
+    <row r="82" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="B81" s="66"/>
-      <c r="C81" s="59" t="s">
+      <c r="B82" s="87"/>
+      <c r="C82" s="80" t="s">
         <v>136</v>
       </c>
-      <c r="D81" s="60"/>
-      <c r="E81" s="48">
+      <c r="D82" s="81"/>
+      <c r="E82" s="48">
         <v>770.4</v>
       </c>
     </row>
-    <row r="82" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="67"/>
-      <c r="B82" s="68"/>
-      <c r="C82" s="58" t="s">
+    <row r="83" spans="1:5" ht="76" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="88"/>
+      <c r="B83" s="89"/>
+      <c r="C83" s="73" t="s">
         <v>138</v>
       </c>
-      <c r="D82" s="58"/>
-      <c r="E82" s="48">
+      <c r="D83" s="73"/>
+      <c r="E83" s="48">
         <v>8.5</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="67"/>
-      <c r="B83" s="68"/>
-      <c r="C83" s="63" t="s">
+    <row r="84" spans="1:5" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="88"/>
+      <c r="B84" s="89"/>
+      <c r="C84" s="84" t="s">
         <v>140</v>
       </c>
-      <c r="D83" s="64"/>
-      <c r="E83" s="48">
+      <c r="D84" s="85"/>
+      <c r="E84" s="48">
         <v>254.5</v>
       </c>
     </row>
-    <row r="84" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="69"/>
-      <c r="B84" s="70"/>
-      <c r="C84" s="64"/>
-      <c r="D84" s="64"/>
-      <c r="E84" s="48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="57" t="s">
+    <row r="85" spans="1:5" ht="13" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="90"/>
+      <c r="B85" s="91"/>
+      <c r="C85" s="112" t="s">
+        <v>144</v>
+      </c>
+      <c r="D85" s="85"/>
+      <c r="E85" s="48">
+        <v>136.63999999999999</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="B85" s="57"/>
-      <c r="C85" s="56"/>
-      <c r="D85" s="56"/>
-      <c r="E85" s="45">
-        <f>C66</f>
+      <c r="B86" s="71"/>
+      <c r="C86" s="79"/>
+      <c r="D86" s="79"/>
+      <c r="E86" s="45">
+        <f>C67</f>
         <v>1171</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C86" s="54" t="s">
+    <row r="87" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C87" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="D86" s="54"/>
-      <c r="E86" s="47">
-        <f>(E22+E80)-SUM(E81:E85)</f>
-        <v>355.19999999999982</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="49"/>
-      <c r="B87" s="49"/>
-      <c r="C87" s="49"/>
-      <c r="D87" s="49"/>
-      <c r="E87" s="49"/>
+      <c r="D87" s="82"/>
+      <c r="E87" s="47">
+        <f>(E23+E81)-SUM(E82:E86)</f>
+        <v>221.63999999999987</v>
+      </c>
     </row>
     <row r="88" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="49"/>
@@ -8012,77 +8045,80 @@
       <c r="E88" s="49"/>
     </row>
     <row r="89" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="61" t="s">
+      <c r="A89" s="49"/>
+      <c r="B89" s="49"/>
+      <c r="C89" s="49"/>
+      <c r="D89" s="49"/>
+      <c r="E89" s="49"/>
+    </row>
+    <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="83" t="s">
         <v>131</v>
       </c>
-      <c r="B89" s="61"/>
-      <c r="C89" s="61"/>
-      <c r="D89" s="61"/>
-      <c r="E89" s="61"/>
-    </row>
-    <row r="90" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="62" t="s">
+      <c r="B90" s="83"/>
+      <c r="C90" s="83"/>
+      <c r="D90" s="83"/>
+      <c r="E90" s="83"/>
+    </row>
+    <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="68" t="s">
         <v>83</v>
       </c>
-      <c r="B90" s="62"/>
-      <c r="C90" s="62" t="s">
+      <c r="B91" s="68"/>
+      <c r="C91" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="D90" s="62"/>
-      <c r="E90" s="43" t="s">
+      <c r="D91" s="68"/>
+      <c r="E91" s="43" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="55" t="s">
+    <row r="92" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="70" t="s">
         <v>109</v>
       </c>
-      <c r="B91" s="55"/>
-      <c r="C91" s="56"/>
-      <c r="D91" s="56"/>
-      <c r="E91" s="47">
-        <f>E86</f>
-        <v>355.19999999999982</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="57" t="s">
+      <c r="B92" s="70"/>
+      <c r="C92" s="79"/>
+      <c r="D92" s="79"/>
+      <c r="E92" s="47">
+        <f>E87</f>
+        <v>221.63999999999987</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="B92" s="57"/>
-      <c r="C92" s="58" t="s">
+      <c r="B93" s="71"/>
+      <c r="C93" s="73" t="s">
         <v>118</v>
       </c>
-      <c r="D92" s="58"/>
-      <c r="E92" s="45">
+      <c r="D93" s="73"/>
+      <c r="E93" s="45">
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="57" t="s">
+    <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="71" t="s">
         <v>95</v>
       </c>
-      <c r="B93" s="57"/>
-      <c r="C93" s="56"/>
-      <c r="D93" s="56"/>
-      <c r="E93" s="45">
-        <f>C66</f>
+      <c r="B94" s="71"/>
+      <c r="C94" s="79"/>
+      <c r="D94" s="79"/>
+      <c r="E94" s="45">
+        <f>C67</f>
         <v>1171</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C94" s="54" t="s">
+    <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C95" s="82" t="s">
         <v>96</v>
       </c>
-      <c r="D94" s="54"/>
-      <c r="E94" s="47">
-        <f>(E28+E91)-SUM(E92:E93)</f>
-        <v>1669.1999999999998</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="24"/>
-      <c r="B95" s="24"/>
+      <c r="D95" s="82"/>
+      <c r="E95" s="47">
+        <f>(E29+E92)-SUM(E93:E94)</f>
+        <v>1535.6399999999999</v>
+      </c>
     </row>
     <row r="96" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="24"/>
@@ -11824,68 +11860,72 @@
       <c r="A1030" s="24"/>
       <c r="B1030" s="24"/>
     </row>
+    <row r="1031" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1031" s="24"/>
+      <c r="B1031" s="24"/>
+    </row>
   </sheetData>
   <mergeCells count="58">
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="A82:B85"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="A73:B75"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="A38:C39"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A37:C38"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:D71"/>
-    <mergeCell ref="A72:B74"/>
-    <mergeCell ref="C72:D72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="C74:D74"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="C75:D75"/>
-    <mergeCell ref="C76:D76"/>
-    <mergeCell ref="A78:E78"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:D79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:D80"/>
-    <mergeCell ref="C81:D81"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="A89:E89"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="C84:D84"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="C85:D85"/>
-    <mergeCell ref="A81:B84"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:D91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:D92"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:D93"/>
   </mergeCells>
-  <conditionalFormatting sqref="C7:C8 E71">
+  <conditionalFormatting sqref="C7:C8 E72">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
@@ -11893,7 +11933,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E76 E80 E86 E91 E94">
+  <conditionalFormatting sqref="E77 E81 E87 E92 E95">
     <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThanOrEqual">
       <formula>0</formula>
     </cfRule>
